--- a/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
+++ b/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\indst\IECCpUAEU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\IECCpUAEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBC3E67-205D-4B5E-A078-77723FE107F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D8BEB0-1EC6-4DE8-91A8-15757244A839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30135" yWindow="960" windowWidth="21600" windowHeight="11175" firstSheet="3" activeTab="8" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
+    <workbookView xWindow="-28410" yWindow="390" windowWidth="22785" windowHeight="14010" tabRatio="762" firstSheet="3" activeTab="10" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,9 @@
     <sheet name="Machine Drive" sheetId="5" r:id="rId6"/>
     <sheet name="Electrochemical" sheetId="6" r:id="rId7"/>
     <sheet name="Other" sheetId="10" r:id="rId8"/>
-    <sheet name="IECCpUAEU" sheetId="2" r:id="rId9"/>
+    <sheet name="Other (mobile)" sheetId="11" r:id="rId9"/>
+    <sheet name="IECCpUAEU" sheetId="2" r:id="rId10"/>
+    <sheet name="IECCpUAEU-mobile" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="450">
   <si>
     <t>Sources:</t>
   </si>
@@ -1294,16 +1296,158 @@
   <si>
     <t>low carbon hydrogen if</t>
   </si>
+  <si>
+    <t>Diesel</t>
+  </si>
+  <si>
+    <t>Ag tractors</t>
+  </si>
+  <si>
+    <t>from https://environmentaldevices.com/wp-content/uploads/2023/09/Impacts-of-electrifying-agricultural-tractors.pdf</t>
+  </si>
+  <si>
+    <t>DT #1</t>
+  </si>
+  <si>
+    <t>DT #2</t>
+  </si>
+  <si>
+    <t>DT #3</t>
+  </si>
+  <si>
+    <t>Capital costs</t>
+  </si>
+  <si>
+    <t>eT</t>
+  </si>
+  <si>
+    <t>Tank capacity (gal)</t>
+  </si>
+  <si>
+    <t>Battery capacity (kWh)</t>
+  </si>
+  <si>
+    <t>Runtime/tank (hr)</t>
+  </si>
+  <si>
+    <t>Energy content/tank</t>
+  </si>
+  <si>
+    <t>Energy content:</t>
+  </si>
+  <si>
+    <t>BTU/gal diesel</t>
+  </si>
+  <si>
+    <t>https://afdc.energy.gov/fuels/properties</t>
+  </si>
+  <si>
+    <t>E Intensity (BTU/hr)</t>
+  </si>
+  <si>
+    <t>from https://www.cadeogroup.com/wp-content/uploads/2022/04/PNW-Tractor-Electrification-Study.pdf</t>
+  </si>
+  <si>
+    <t>Energy reservoir (kWh)</t>
+  </si>
+  <si>
+    <t>diesel</t>
+  </si>
+  <si>
+    <t>battery</t>
+  </si>
+  <si>
+    <t>from https://pub.epsilon.slu.se/id/document/20368600</t>
+  </si>
+  <si>
+    <t>example 1</t>
+  </si>
+  <si>
+    <t>example 2</t>
+  </si>
+  <si>
+    <t>% energy consumption (bev vs diesel)</t>
+  </si>
+  <si>
+    <t>from https://static1.squarespace.com/static/5eab584a296dca09a66e85a6/t/627946f6c12c786debe434c7/1652115191705/TCO_report_May%2B2022.pdf</t>
+  </si>
+  <si>
+    <t>e-tractor</t>
+  </si>
+  <si>
+    <t>IC</t>
+  </si>
+  <si>
+    <t>capital cost</t>
+  </si>
+  <si>
+    <t>operating hours/yr</t>
+  </si>
+  <si>
+    <t>Annual energy (gal)</t>
+  </si>
+  <si>
+    <t>Annual energy (kWh)</t>
+  </si>
+  <si>
+    <t>** costs in table 3</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>Annual usage (hr)</t>
+  </si>
+  <si>
+    <t>2022 to 2012 USD</t>
+  </si>
+  <si>
+    <t>PIFURfE for ag tractors (other processes)</t>
+  </si>
+  <si>
+    <t>Electric</t>
+  </si>
+  <si>
+    <t>price ($)</t>
+  </si>
+  <si>
+    <t>annual E</t>
+  </si>
+  <si>
+    <t>Assumed annual usage (hours)</t>
+  </si>
+  <si>
+    <t>E intensity (BTU/hr)</t>
+  </si>
+  <si>
+    <t>^assuming equal distribution of tasks</t>
+  </si>
+  <si>
+    <t>Annual BTUs</t>
+  </si>
+  <si>
+    <t>2021 to 2012 USD</t>
+  </si>
+  <si>
+    <t>Annual BTU</t>
+  </si>
+  <si>
+    <t>Diesel tractor price $/BTU</t>
+  </si>
+  <si>
+    <t>Electric tractor price $/BTU</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1383,7 +1527,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1447,6 +1591,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1541,7 +1691,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1626,6 +1776,12 @@
     <xf numFmtId="11" fontId="8" fillId="11" borderId="3" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="9" fontId="8" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2754,6 +2910,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2761,7 +2918,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3472,6 +3628,187 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>675943</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>88899</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2B59920-8ABB-1873-C7FA-CDD37215352D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="7429499"/>
+          <a:ext cx="4889168" cy="2752725"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>12504</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D28FB0B8-005B-4E65-A536-DC3EBE8AE389}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5934075" y="7429500"/>
+          <a:ext cx="4410075" cy="3254179"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>610454</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>76742</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2043415-C480-F862-EB46-E9D9439E8102}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="16002000"/>
+          <a:ext cx="6115904" cy="3886742"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>320866</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>38159</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39C0BD5E-985B-0A39-B21D-7CCDBBB09B7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="133350" y="13011150"/>
+          <a:ext cx="3721291" cy="1143059"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3842,7 +4179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC3CA314-6128-4FC9-9CED-BF85AF9DB226}">
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B149"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="76.42578125" customWidth="1"/>
@@ -4351,24 +4688,66 @@
         <v>157</v>
       </c>
     </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B134" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>186</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>138490</v>
+      </c>
+      <c r="B143" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>3412.14</v>
+      </c>
+      <c r="B145" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>0.78452102304761584</v>
+      </c>
+      <c r="B148" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>0.84730412960844359</v>
+      </c>
+      <c r="B149" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -4392,6 +4771,651 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId17"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC78963D-3265-44FA-8138-35C2A57258D3}">
+  <sheetPr>
+    <tabColor theme="3" tint="0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:M44"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="11" width="13.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="12">
+        <f>Boilers!$A$18</f>
+        <v>5.6711966224873446E-5</v>
+      </c>
+      <c r="C2" s="12">
+        <f>Boilers!$G$43</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="D2" s="12">
+        <f>Boilers!A39</f>
+        <v>1.5989491110961776E-5</v>
+      </c>
+      <c r="E2" s="10">
+        <f>C2</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="F2" s="12">
+        <f>Boilers!$G$44</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="G2" s="40">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10">
+        <f>F2</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="I2" s="10">
+        <f>F2</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="J2" s="10">
+        <f>F2</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="K2" s="12">
+        <f>Boilers!A60</f>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="L2" s="12">
+        <f>K2</f>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="M2" s="12">
+        <f t="shared" ref="M2:M9" si="0">L2</f>
+        <v>2.3984236666442662E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="10">
+        <f>B2</f>
+        <v>5.6711966224873446E-5</v>
+      </c>
+      <c r="C3" s="10">
+        <f t="shared" ref="C3:K3" si="1">C2</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="D3" s="10">
+        <f t="shared" si="1"/>
+        <v>1.5989491110961776E-5</v>
+      </c>
+      <c r="E3" s="10">
+        <f t="shared" si="1"/>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="F3" s="10">
+        <f t="shared" si="1"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="G3" s="40">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H3" s="10">
+        <f t="shared" si="1"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="I3" s="10">
+        <f t="shared" si="1"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="J3" s="10">
+        <f t="shared" si="1"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="K3" s="10">
+        <f t="shared" si="1"/>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="L3" s="10">
+        <f t="shared" ref="L3" si="2">K3</f>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="M3" s="10">
+        <f t="shared" si="0"/>
+        <v>2.3984236666442662E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="12">
+        <f>'NB Medium Temp'!D40</f>
+        <v>3.4771933032458345E-5</v>
+      </c>
+      <c r="C4" s="10">
+        <f>D4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="D4" s="12">
+        <f>'NB Medium Temp'!D41</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="E4" s="10">
+        <f>C4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="F4" s="10">
+        <f>D4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="G4" s="40">
+        <v>0</v>
+      </c>
+      <c r="H4" s="10">
+        <f t="shared" ref="H4" si="3">F4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="I4" s="10">
+        <f t="shared" ref="I4" si="4">F4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="J4" s="10">
+        <f t="shared" ref="J4" si="5">F4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="K4" s="10">
+        <f>D4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="L4" s="10">
+        <f t="shared" ref="L4" si="6">K4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="M4" s="10">
+        <f t="shared" si="0"/>
+        <v>3.1780367029653324E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12">
+        <f>'NB High Temp'!F10</f>
+        <v>1.7204637228083889E-4</v>
+      </c>
+      <c r="C5" s="12">
+        <f>'NB High Temp'!F45</f>
+        <v>4.5951806950193628E-6</v>
+      </c>
+      <c r="D5" s="12">
+        <f>'NB High Temp'!F56</f>
+        <v>2.0725243194734525E-5</v>
+      </c>
+      <c r="E5" s="10">
+        <f>C5</f>
+        <v>4.5951806950193628E-6</v>
+      </c>
+      <c r="F5" s="10">
+        <f>D5*(F2/D2)</f>
+        <v>1.2230751723262388E-5</v>
+      </c>
+      <c r="G5" s="40">
+        <v>0</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" ref="H5" si="7">F5</f>
+        <v>1.2230751723262388E-5</v>
+      </c>
+      <c r="I5" s="10">
+        <f t="shared" ref="I5" si="8">F5</f>
+        <v>1.2230751723262388E-5</v>
+      </c>
+      <c r="J5" s="10">
+        <f t="shared" ref="J5" si="9">F5</f>
+        <v>1.2230751723262388E-5</v>
+      </c>
+      <c r="K5" s="12">
+        <f>'NB High Temp'!F67</f>
+        <v>3.265784625690839E-5</v>
+      </c>
+      <c r="L5" s="12">
+        <f t="shared" ref="L5" si="10">K5</f>
+        <v>3.265784625690839E-5</v>
+      </c>
+      <c r="M5" s="12">
+        <f t="shared" si="0"/>
+        <v>3.265784625690839E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="12">
+        <f>Cooling!$B$49</f>
+        <v>4.4520366169683022E-5</v>
+      </c>
+      <c r="C6" s="10">
+        <f>$D$6</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="D6" s="12">
+        <f>Cooling!$B$27</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" ref="E6:F6" si="11">$D$6</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="11"/>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="G6" s="40">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" ref="H6:J6" si="12">$D$6</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" si="12"/>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="J6" s="10">
+        <f t="shared" si="12"/>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="K6" s="10">
+        <f>$D$6*(K2/D2)</f>
+        <v>2.7132239620912736E-5</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" ref="L6" si="13">K6</f>
+        <v>2.7132239620912736E-5</v>
+      </c>
+      <c r="M6" s="10">
+        <f t="shared" si="0"/>
+        <v>2.7132239620912736E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="12">
+        <f>'Machine Drive'!$W$22</f>
+        <v>2.9652197760109964E-5</v>
+      </c>
+      <c r="C7" s="10">
+        <f>$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="D7" s="10">
+        <f t="shared" ref="D7:E7" si="14">$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="14"/>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="F7" s="12">
+        <f>'Machine Drive'!D38</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="G7" s="40">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <f t="shared" ref="H7:K7" si="15">$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="I7" s="10">
+        <f t="shared" si="15"/>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="J7" s="10">
+        <f t="shared" si="15"/>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" si="15"/>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" ref="L7" si="16">K7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="M7" s="10">
+        <f t="shared" si="0"/>
+        <v>7.0734511678239686E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="12">
+        <f>Electrochemical!$G32</f>
+        <v>4.4539618429716232E-5</v>
+      </c>
+      <c r="C8" s="40">
+        <v>0</v>
+      </c>
+      <c r="D8" s="40">
+        <v>0</v>
+      </c>
+      <c r="E8" s="40">
+        <v>0</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0</v>
+      </c>
+      <c r="G8" s="40">
+        <v>0</v>
+      </c>
+      <c r="H8" s="40">
+        <v>0</v>
+      </c>
+      <c r="I8" s="40">
+        <v>0</v>
+      </c>
+      <c r="J8" s="40">
+        <v>0</v>
+      </c>
+      <c r="K8" s="40">
+        <v>0</v>
+      </c>
+      <c r="L8" s="40">
+        <f t="shared" ref="L8" si="17">K8</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="12">
+        <f>Other!E9</f>
+        <v>7.0401933942914745E-6</v>
+      </c>
+      <c r="C9" s="10">
+        <f>D9*(C2/D2)</f>
+        <v>2.0886792055175448E-5</v>
+      </c>
+      <c r="D9" s="12">
+        <f>Other!B24</f>
+        <v>2.2284525195577483E-5</v>
+      </c>
+      <c r="E9" s="10">
+        <f>C9</f>
+        <v>2.0886792055175448E-5</v>
+      </c>
+      <c r="F9" s="10">
+        <f>D9*(F2/D2)</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="G9" s="40">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10">
+        <f>F9</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="I9" s="10">
+        <f>F9</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="J9" s="10">
+        <f>F9</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="K9" s="10">
+        <f>D9*(K2/D2)</f>
+        <v>3.3426787793366228E-5</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" ref="L9" si="18">K9</f>
+        <v>3.3426787793366228E-5</v>
+      </c>
+      <c r="M9" s="10">
+        <f t="shared" si="0"/>
+        <v>3.3426787793366228E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="9"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="H3:J3 E3 D6" formula="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843ADA01-EFFE-45B2-B6A7-C20F6BBCF0E2}">
+  <sheetPr>
+    <tabColor theme="3" tint="0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="13.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12">
+        <f>'Other (mobile)'!A7</f>
+        <v>3.1381977460259781E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10">
+        <f>B6</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10">
+        <f>B6</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10">
+        <f>B6</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10">
+        <f>'Other (mobile)'!A6</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10">
+        <f>B6</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10">
+        <f>B6</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10">
+        <f>B6</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10">
+        <f>B6</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B12" s="10">
+        <f>B11</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>402</v>
+      </c>
+      <c r="B13" s="10">
+        <f>B12</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -6987,25 +8011,25 @@
       <c r="T23" s="21"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C24" s="55" t="s">
+      <c r="C24" s="61" t="s">
         <v>391</v>
       </c>
-      <c r="D24" s="56"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="52">
+      <c r="D24" s="62"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="58">
         <f>0.048/0.581</f>
         <v>8.2616179001721177E-2</v>
       </c>
-      <c r="G24" s="53"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="58">
+      <c r="G24" s="59"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="64">
         <f>((T13+T15)/2)</f>
         <v>23.414850000000001</v>
       </c>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59"/>
-      <c r="M24" s="60"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="66"/>
       <c r="N24" s="51">
         <f>((W13+W15)/2)</f>
         <v>2.2407199119595664E-4</v>
@@ -7015,25 +8039,25 @@
       <c r="T24" s="21"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C25" s="55" t="s">
+      <c r="C25" s="61" t="s">
         <v>392</v>
       </c>
-      <c r="D25" s="56"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="52">
+      <c r="D25" s="62"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="58">
         <f>0.104/0.581</f>
         <v>0.17900172117039587</v>
       </c>
-      <c r="G25" s="53"/>
-      <c r="H25" s="54"/>
-      <c r="I25" s="58">
+      <c r="G25" s="59"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="64">
         <f>T14</f>
         <v>97.18877280000001</v>
       </c>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="60"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="66"/>
       <c r="N25" s="51">
         <f>W14</f>
         <v>3.3521233224690123E-5</v>
@@ -7043,25 +8067,25 @@
       <c r="T25" s="21"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="61" t="s">
         <v>390</v>
       </c>
-      <c r="D26" s="56"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="52">
+      <c r="D26" s="62"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="58">
         <f>0.127/0.581</f>
         <v>0.21858864027538727</v>
       </c>
-      <c r="G26" s="53"/>
-      <c r="H26" s="54"/>
-      <c r="I26" s="58">
+      <c r="G26" s="59"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="64">
         <f>T16</f>
         <v>319.17554000000001</v>
       </c>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="60"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="66"/>
       <c r="N26" s="51">
         <f>W16</f>
         <v>1.1301491868138288E-5</v>
@@ -7071,25 +8095,25 @@
       <c r="T26" s="21"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C27" s="55" t="s">
+      <c r="C27" s="61" t="s">
         <v>389</v>
       </c>
-      <c r="D27" s="56"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="52">
+      <c r="D27" s="62"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="58">
         <f>0.144/0.581</f>
         <v>0.24784853700516352</v>
       </c>
-      <c r="G27" s="53"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="58">
+      <c r="G27" s="59"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="64">
         <f>((T10+T18)/2)</f>
         <v>1214.1039020000001</v>
       </c>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="60"/>
+      <c r="J27" s="65"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="66"/>
       <c r="N27" s="51">
         <f>((W10+W18)/2)</f>
         <v>5.481183696812177E-6</v>
@@ -7099,25 +8123,25 @@
       <c r="T27" s="21"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C28" s="55" t="s">
+      <c r="C28" s="61" t="s">
         <v>393</v>
       </c>
-      <c r="D28" s="56"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="52">
+      <c r="D28" s="62"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="58">
         <f>0.157/0.581</f>
         <v>0.27022375215146299</v>
       </c>
-      <c r="G28" s="53"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="58">
+      <c r="G28" s="59"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="64">
         <f>((T9+T11+T12+T17+T19)/5)</f>
         <v>49678.416604960003</v>
       </c>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="60"/>
+      <c r="J28" s="65"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="66"/>
       <c r="N28" s="51">
         <f>((W9+W11+W12+W17+W19)/5)</f>
         <v>4.8514850079979492E-6</v>
@@ -7721,502 +8745,441 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC78963D-3265-44FA-8138-35C2A57258D3}">
-  <sheetPr>
-    <tabColor theme="3" tint="0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:M44"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B88B710-1DAB-47E6-AE70-A12C5CA0B896}">
+  <dimension ref="A2:P84"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="11" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
+        <v>404</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="54">
+        <v>0.57060049240377109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="54">
+        <f>4000/15</f>
+        <v>266.66666666666669</v>
+      </c>
+      <c r="B4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="56">
+        <f>AVERAGE(O30,H40,H84)</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="56">
+        <f>AVERAGE(O31,H41,H83)</f>
+        <v>3.1381977460259781E-3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="24"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>409</v>
+      </c>
+      <c r="D29" t="s">
+        <v>411</v>
+      </c>
+      <c r="E29" t="s">
+        <v>412</v>
+      </c>
+      <c r="F29" t="s">
+        <v>413</v>
+      </c>
+      <c r="G29" t="s">
+        <v>414</v>
+      </c>
+      <c r="H29" t="s">
+        <v>418</v>
+      </c>
+      <c r="I29" t="s">
+        <v>436</v>
+      </c>
+      <c r="M29" t="s">
+        <v>440</v>
+      </c>
+      <c r="N29" t="s">
+        <v>441</v>
+      </c>
+      <c r="O29" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>406</v>
+      </c>
+      <c r="C30">
+        <v>17000</v>
+      </c>
+      <c r="D30">
+        <v>7.1</v>
+      </c>
+      <c r="F30">
+        <v>9.5</v>
+      </c>
+      <c r="G30" s="21">
+        <f>D30*About!$A$143</f>
+        <v>983279</v>
+      </c>
+      <c r="H30" s="21">
+        <f>G30/F30</f>
+        <v>103503.05263157895</v>
+      </c>
+      <c r="I30">
+        <v>250</v>
+      </c>
+      <c r="L30" t="s">
+        <v>403</v>
+      </c>
+      <c r="M30">
+        <f>AVERAGE(C30:C32)*About!A148</f>
+        <v>21966.588645333242</v>
+      </c>
+      <c r="N30">
+        <f>AVERAGE(H30:H32)*A4</f>
+        <v>27574616.079328757</v>
+      </c>
+      <c r="O30" s="55">
+        <f>M30/N30</f>
+        <v>7.9662355342094654E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>407</v>
+      </c>
+      <c r="C31">
+        <v>17000</v>
+      </c>
+      <c r="D31">
+        <v>7.1</v>
+      </c>
+      <c r="F31">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="12">
-        <f>Boilers!$A$18</f>
-        <v>5.6711966224873446E-5</v>
-      </c>
-      <c r="C2" s="12">
-        <f>Boilers!$G$43</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="D2" s="12">
-        <f>Boilers!A39</f>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="E2" s="10">
-        <f>C2</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="F2" s="12">
-        <f>Boilers!$G$44</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="G2" s="40">
-        <v>0</v>
-      </c>
-      <c r="H2" s="10">
-        <f>F2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="I2" s="10">
-        <f>F2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="J2" s="10">
-        <f>F2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="K2" s="12">
-        <f>Boilers!A60</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="L2" s="12">
-        <f>K2</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="M2" s="12">
-        <f t="shared" ref="M2:M9" si="0">L2</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="10">
-        <f>B2</f>
-        <v>5.6711966224873446E-5</v>
-      </c>
-      <c r="C3" s="10">
-        <f t="shared" ref="C3:K3" si="1">C2</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="D3" s="10">
-        <f t="shared" si="1"/>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="E3" s="10">
-        <f t="shared" si="1"/>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="F3" s="10">
-        <f t="shared" si="1"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="G3" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H3" s="10">
-        <f t="shared" si="1"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="I3" s="10">
-        <f t="shared" si="1"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="J3" s="10">
-        <f t="shared" si="1"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="K3" s="10">
-        <f t="shared" si="1"/>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="L3" s="10">
-        <f t="shared" ref="L3:M3" si="2">K3</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="M3" s="10">
+      <c r="G31" s="21">
+        <f>D31*About!$A$143</f>
+        <v>983279</v>
+      </c>
+      <c r="H31" s="21">
+        <f t="shared" ref="H31:H32" si="0">G31/F31</f>
+        <v>98327.9</v>
+      </c>
+      <c r="I31">
+        <v>250</v>
+      </c>
+      <c r="L31" t="s">
+        <v>439</v>
+      </c>
+      <c r="M31">
+        <f>C33*About!A148</f>
+        <v>43148.65626761887</v>
+      </c>
+      <c r="N31">
+        <f>N30*(1-A3)</f>
+        <v>11840526.566618824</v>
+      </c>
+      <c r="O31" s="55">
+        <f>M31/N31</f>
+        <v>3.6441501165383038E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>408</v>
+      </c>
+      <c r="C32">
+        <v>50000</v>
+      </c>
+      <c r="D32">
+        <v>18</v>
+      </c>
+      <c r="F32">
+        <v>23</v>
+      </c>
+      <c r="G32" s="21">
+        <f>D32*About!$A$143</f>
+        <v>2492820</v>
+      </c>
+      <c r="H32" s="21">
         <f t="shared" si="0"/>
-        <v>2.3984236666442662E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="12">
-        <f>'NB Medium Temp'!D40</f>
-        <v>3.4771933032458345E-5</v>
-      </c>
-      <c r="C4" s="10">
-        <f>D4</f>
-        <v>3.1780367029653324E-5</v>
-      </c>
-      <c r="D4" s="12">
-        <f>'NB Medium Temp'!D41</f>
-        <v>3.1780367029653324E-5</v>
-      </c>
-      <c r="E4" s="10">
-        <f>C4</f>
-        <v>3.1780367029653324E-5</v>
-      </c>
-      <c r="F4" s="10">
-        <f>D4</f>
-        <v>3.1780367029653324E-5</v>
-      </c>
-      <c r="G4" s="40">
-        <v>0</v>
-      </c>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4" si="3">F4</f>
-        <v>3.1780367029653324E-5</v>
-      </c>
-      <c r="I4" s="10">
-        <f t="shared" ref="I4" si="4">F4</f>
-        <v>3.1780367029653324E-5</v>
-      </c>
-      <c r="J4" s="10">
-        <f t="shared" ref="J4" si="5">F4</f>
-        <v>3.1780367029653324E-5</v>
-      </c>
-      <c r="K4" s="10">
-        <f>D4</f>
-        <v>3.1780367029653324E-5</v>
-      </c>
-      <c r="L4" s="10">
-        <f t="shared" ref="L4:M4" si="6">K4</f>
-        <v>3.1780367029653324E-5</v>
-      </c>
-      <c r="M4" s="10">
-        <f t="shared" si="0"/>
-        <v>3.1780367029653324E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12">
-        <f>'NB High Temp'!F10</f>
-        <v>1.7204637228083889E-4</v>
-      </c>
-      <c r="C5" s="12">
-        <f>'NB High Temp'!F45</f>
-        <v>4.5951806950193628E-6</v>
-      </c>
-      <c r="D5" s="12">
-        <f>'NB High Temp'!F56</f>
-        <v>2.0725243194734525E-5</v>
-      </c>
-      <c r="E5" s="10">
-        <f>C5</f>
-        <v>4.5951806950193628E-6</v>
-      </c>
-      <c r="F5" s="10">
-        <f>D5*(F2/D2)</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="G5" s="40">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" ref="H5" si="7">F5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="I5" s="10">
-        <f t="shared" ref="I5" si="8">F5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="J5" s="10">
-        <f t="shared" ref="J5" si="9">F5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="K5" s="12">
-        <f>'NB High Temp'!F67</f>
-        <v>3.265784625690839E-5</v>
-      </c>
-      <c r="L5" s="12">
-        <f t="shared" ref="L5:M5" si="10">K5</f>
-        <v>3.265784625690839E-5</v>
-      </c>
-      <c r="M5" s="12">
-        <f t="shared" si="0"/>
-        <v>3.265784625690839E-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="12">
-        <f>Cooling!$B$49</f>
-        <v>4.4520366169683022E-5</v>
-      </c>
-      <c r="C6" s="10">
-        <f>$D$6</f>
-        <v>1.8088159747275158E-5</v>
-      </c>
-      <c r="D6" s="12">
-        <f>Cooling!$B$27</f>
-        <v>1.8088159747275158E-5</v>
-      </c>
-      <c r="E6" s="10">
-        <f t="shared" ref="E6:F6" si="11">$D$6</f>
-        <v>1.8088159747275158E-5</v>
-      </c>
-      <c r="F6" s="10">
-        <f t="shared" si="11"/>
-        <v>1.8088159747275158E-5</v>
-      </c>
-      <c r="G6" s="40">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10">
-        <f t="shared" ref="H6:J6" si="12">$D$6</f>
-        <v>1.8088159747275158E-5</v>
-      </c>
-      <c r="I6" s="10">
-        <f t="shared" si="12"/>
-        <v>1.8088159747275158E-5</v>
-      </c>
-      <c r="J6" s="10">
-        <f t="shared" si="12"/>
-        <v>1.8088159747275158E-5</v>
-      </c>
-      <c r="K6" s="10">
-        <f>$D$6*(K2/D2)</f>
-        <v>2.7132239620912736E-5</v>
-      </c>
-      <c r="L6" s="10">
-        <f t="shared" ref="L6:M6" si="13">K6</f>
-        <v>2.7132239620912736E-5</v>
-      </c>
-      <c r="M6" s="10">
-        <f t="shared" si="0"/>
-        <v>2.7132239620912736E-5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+        <v>108383.47826086957</v>
+      </c>
+      <c r="I32">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>410</v>
+      </c>
+      <c r="C33">
+        <v>55000</v>
+      </c>
+      <c r="E33">
+        <v>24</v>
+      </c>
+      <c r="F33">
         <v>16</v>
       </c>
-      <c r="B7" s="12">
-        <f>'Machine Drive'!$W$22</f>
-        <v>2.9652197760109964E-5</v>
-      </c>
-      <c r="C7" s="10">
-        <f>$F$7</f>
-        <v>7.0734511678239686E-5</v>
-      </c>
-      <c r="D7" s="10">
-        <f t="shared" ref="D7:E7" si="14">$F$7</f>
-        <v>7.0734511678239686E-5</v>
-      </c>
-      <c r="E7" s="10">
-        <f t="shared" si="14"/>
-        <v>7.0734511678239686E-5</v>
-      </c>
-      <c r="F7" s="12">
-        <f>'Machine Drive'!D38</f>
-        <v>7.0734511678239686E-5</v>
-      </c>
-      <c r="G7" s="40">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10">
-        <f t="shared" ref="H7:M7" si="15">$F$7</f>
-        <v>7.0734511678239686E-5</v>
-      </c>
-      <c r="I7" s="10">
-        <f t="shared" si="15"/>
-        <v>7.0734511678239686E-5</v>
-      </c>
-      <c r="J7" s="10">
-        <f t="shared" si="15"/>
-        <v>7.0734511678239686E-5</v>
-      </c>
-      <c r="K7" s="10">
-        <f t="shared" si="15"/>
-        <v>7.0734511678239686E-5</v>
-      </c>
-      <c r="L7" s="10">
-        <f t="shared" ref="L7:M7" si="16">K7</f>
-        <v>7.0734511678239686E-5</v>
-      </c>
-      <c r="M7" s="10">
-        <f t="shared" si="0"/>
-        <v>7.0734511678239686E-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="12">
-        <f>Electrochemical!$G32</f>
-        <v>4.4539618429716232E-5</v>
-      </c>
-      <c r="C8" s="40">
-        <v>0</v>
-      </c>
-      <c r="D8" s="40">
-        <v>0</v>
-      </c>
-      <c r="E8" s="40">
-        <v>0</v>
-      </c>
-      <c r="F8" s="40">
-        <v>0</v>
-      </c>
-      <c r="G8" s="40">
-        <v>0</v>
-      </c>
-      <c r="H8" s="40">
-        <v>0</v>
-      </c>
-      <c r="I8" s="40">
-        <v>0</v>
-      </c>
-      <c r="J8" s="40">
-        <v>0</v>
-      </c>
-      <c r="K8" s="40">
-        <v>0</v>
-      </c>
-      <c r="L8" s="40">
-        <f t="shared" ref="L8:M8" si="17">K8</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="12">
-        <f>Other!E9</f>
-        <v>7.0401933942914745E-6</v>
-      </c>
-      <c r="C9" s="10">
-        <f>D9*(C2/D2)</f>
-        <v>2.0886792055175448E-5</v>
-      </c>
-      <c r="D9" s="12">
-        <f>Other!B24</f>
-        <v>2.2284525195577483E-5</v>
-      </c>
-      <c r="E9" s="10">
-        <f>C9</f>
-        <v>2.0886792055175448E-5</v>
-      </c>
-      <c r="F9" s="10">
-        <f>D9*(F2/D2)</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="G9" s="40">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10">
-        <f>F9</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="I9" s="10">
-        <f>F9</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="J9" s="10">
-        <f>F9</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="K9" s="10">
-        <f>D9*(K2/D2)</f>
-        <v>3.3426787793366228E-5</v>
-      </c>
-      <c r="L9" s="10">
-        <f t="shared" ref="L9:M9" si="18">K9</f>
-        <v>3.3426787793366228E-5</v>
-      </c>
-      <c r="M9" s="10">
-        <f t="shared" si="0"/>
-        <v>3.3426787793366228E-5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>399</v>
+      <c r="G33" s="21">
+        <f>E33*About!$A$145</f>
+        <v>81891.360000000001</v>
+      </c>
+      <c r="H33" s="21"/>
+      <c r="I33">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C34">
+        <f>C33/AVERAGE(C30:C32)</f>
+        <v>1.9642857142857142</v>
+      </c>
+      <c r="H34" s="21"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E35">
+        <f>E33/38.1</f>
+        <v>0.62992125984251968</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="24" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>420</v>
+      </c>
+      <c r="D39" t="s">
+        <v>247</v>
+      </c>
+      <c r="E39" t="s">
+        <v>435</v>
+      </c>
+      <c r="F39" t="s">
+        <v>443</v>
+      </c>
+      <c r="G39" t="s">
+        <v>445</v>
+      </c>
+      <c r="H39" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>421</v>
+      </c>
+      <c r="C40">
+        <v>2940</v>
+      </c>
+      <c r="D40">
+        <v>545</v>
+      </c>
+      <c r="E40">
+        <f>37500</f>
+        <v>37500</v>
+      </c>
+      <c r="F40" s="21">
+        <f>AVERAGE(60400,120900,214300)</f>
+        <v>131866.66666666666</v>
+      </c>
+      <c r="G40" s="21">
+        <f>F40*$A$4</f>
+        <v>35164444.444444448</v>
+      </c>
+      <c r="H40" s="55">
+        <f>E40*About!$A$149/G40</f>
+        <v>9.0358045924813471E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>422</v>
+      </c>
+      <c r="C41">
+        <v>113</v>
+      </c>
+      <c r="D41">
+        <v>995</v>
+      </c>
+      <c r="E41" s="21">
+        <f>AVERAGE(58000,74999)</f>
+        <v>66499.5</v>
+      </c>
+      <c r="F41" s="21">
+        <f>F40*(1-A3)</f>
+        <v>56623.481735022717</v>
+      </c>
+      <c r="G41" s="21">
+        <f>F41*$A$4</f>
+        <v>15099595.129339391</v>
+      </c>
+      <c r="H41" s="55">
+        <f>E41*About!$A$149/G41</f>
+        <v>3.7315769386037706E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F42" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="24" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C55" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>424</v>
+      </c>
+      <c r="C56" s="19">
+        <v>0.54</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>425</v>
+      </c>
+      <c r="C57" s="19">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C58" s="19"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="24" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C82" t="s">
+        <v>430</v>
+      </c>
+      <c r="D82" t="s">
+        <v>431</v>
+      </c>
+      <c r="E82" t="s">
+        <v>432</v>
+      </c>
+      <c r="F82" t="s">
+        <v>433</v>
+      </c>
+      <c r="G82" t="s">
+        <v>447</v>
+      </c>
+      <c r="H82" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>428</v>
+      </c>
+      <c r="C83">
+        <v>28398</v>
+      </c>
+      <c r="D83">
+        <v>250</v>
+      </c>
+      <c r="G83" s="21">
+        <f>G84*(1-A3)</f>
+        <v>11801531.10292552</v>
+      </c>
+      <c r="H83" s="55">
+        <f>C83*About!$A$149/G83</f>
+        <v>2.0388661829358595E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>429</v>
+      </c>
+      <c r="C84">
+        <v>25345</v>
+      </c>
+      <c r="D84">
+        <v>250</v>
+      </c>
+      <c r="E84">
+        <f>AVERAGE(144,228.1)</f>
+        <v>186.05</v>
+      </c>
+      <c r="G84" s="21">
+        <f>E84*About!A143*A4/D84</f>
+        <v>27483802.133333337</v>
+      </c>
+      <c r="H84" s="55">
+        <f>C84*About!$A$149/G84</f>
+        <v>7.8136653221209343E-4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="H3:J3 E3 D6" formula="1"/>
-  </ignoredErrors>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
+++ b/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\IECCpUAEU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code Repositories\eps-us\InputData\indst\IECCpUAEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D8BEB0-1EC6-4DE8-91A8-15757244A839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7C46AE-AD16-41EE-AF51-56BA6F443605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28410" yWindow="390" windowWidth="22785" windowHeight="14010" tabRatio="762" firstSheet="3" activeTab="10" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
+    <workbookView xWindow="27690" yWindow="750" windowWidth="23940" windowHeight="21210" tabRatio="762" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Boilers" sheetId="3" r:id="rId2"/>
+    <sheet name="Boilers &amp; Heat Pumps" sheetId="3" r:id="rId2"/>
     <sheet name="Cooling" sheetId="4" r:id="rId3"/>
     <sheet name="NB Medium Temp" sheetId="9" r:id="rId4"/>
     <sheet name="NB High Temp" sheetId="7" r:id="rId5"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="451">
   <si>
     <t>Sources:</t>
   </si>
@@ -129,24 +129,6 @@
     <t>Capital Cost (USD)</t>
   </si>
   <si>
-    <t>$/annual BTU</t>
-  </si>
-  <si>
-    <t>Case Study 1</t>
-  </si>
-  <si>
-    <t>Case Study 2</t>
-  </si>
-  <si>
-    <t>Case Study 3</t>
-  </si>
-  <si>
-    <t>Simple average</t>
-  </si>
-  <si>
-    <t>Therefore, we need to take into account the efficiency of heat use.</t>
-  </si>
-  <si>
     <t>Industrial heat pumps</t>
   </si>
   <si>
@@ -156,40 +138,7 @@
     <t>Industrial Heat Pumps</t>
   </si>
   <si>
-    <t>https://climate.emerson.com/documents/vilter-heat-pump-white-paper-en-us-5411194.pdf</t>
-  </si>
-  <si>
     <t>Industrial heat pumps cost per unit heat delivered</t>
-  </si>
-  <si>
-    <t>Industrial heat pump efficiency</t>
-  </si>
-  <si>
-    <t>Efficiency of industrial heat pump</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>Arpagaus et al.</t>
-  </si>
-  <si>
-    <t>High temperature heat pumps: Market overview, state of the art, research status, refrigerants, and application potentials</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/science/article/pii/S0360544218305759</t>
-  </si>
-  <si>
-    <t>Figure 8</t>
-  </si>
-  <si>
-    <t>Cost per unit of electricity consumed annually:</t>
-  </si>
-  <si>
-    <t>This is the cost per unit heat delivered via heat pump.  We want the cost per unit energy consumed.</t>
-  </si>
-  <si>
-    <t>Based on Arpagaus et al. curve, assuming a temperature lift of around 55 C (e.g., industries using waste heat as the heat source, boosting 45 C to 100 C or similar)</t>
   </si>
   <si>
     <t>Natural gas boilers</t>
@@ -1437,17 +1386,72 @@
   <si>
     <t>Electric tractor price $/BTU</t>
   </si>
+  <si>
+    <t>Industrial heat pumps capacity factor</t>
+  </si>
+  <si>
+    <t>Zühlsdorf, B., Andersen, M. P., Tammone, C. et.al.</t>
+  </si>
+  <si>
+    <t>Industrial High-Temperature Heat Pumps. Task 1 – Technologies: Yearly Report 2025</t>
+  </si>
+  <si>
+    <t>https://heatpumpingtechnologies.org/project68/task1/</t>
+  </si>
+  <si>
+    <t>Page 16, Figure 1-4</t>
+  </si>
+  <si>
+    <t>Page 5-7. Capacity factor is based on the average annual operating hours across the three examples, assuming each operates at full capacity.</t>
+  </si>
+  <si>
+    <t>https://web.archive.org/web/20210702173253/https://climate.emerson.com/documents/vilter-heat-pump-white-paper-en-us-5411194.pdf</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Per-kW CAPEX</t>
+  </si>
+  <si>
+    <t>Annual hours</t>
+  </si>
+  <si>
+    <t>hrs/yr</t>
+  </si>
+  <si>
+    <t>Capacity factor</t>
+  </si>
+  <si>
+    <t>Per-kWh/yr CAPEX</t>
+  </si>
+  <si>
+    <t>Per-BTU/yr CAPEX</t>
+  </si>
+  <si>
+    <t>$ / power draw</t>
+  </si>
+  <si>
+    <t>$ / electricity consumption each year</t>
+  </si>
+  <si>
+    <t>$ / electricity consumption (in BTU of electricity) each year</t>
+  </si>
+  <si>
+    <t>Does not need to be converted using heat pump COP because it is already based on electricity consumption</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1691,7 +1695,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1782,6 +1786,18 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1791,16 +1807,25 @@
     <xf numFmtId="9" fontId="8" fillId="11" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1924,9 +1949,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$K$1</c:f>
+              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>electricity if</c:v>
                 </c:pt>
@@ -1956,18 +1981,24 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$2:$K$2</c:f>
+              <c:f>IECCpUAEU!$B$2:$M$2</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>5.6711966224873446E-5</c:v>
+                  <c:v>3.0882108581950831E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.4986595988547842E-5</c:v>
@@ -1994,6 +2025,12 @@
                   <c:v>9.436004881678272E-6</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>2.3984236666442662E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.3984236666442662E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>2.3984236666442662E-5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2031,9 +2068,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$K$1</c:f>
+              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>electricity if</c:v>
                 </c:pt>
@@ -2063,18 +2100,24 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$3:$K$3</c:f>
+              <c:f>IECCpUAEU!$B$3:$M$3</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>5.6711966224873446E-5</c:v>
+                  <c:v>3.0882108581950831E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.4986595988547842E-5</c:v>
@@ -2101,6 +2144,12 @@
                   <c:v>9.436004881678272E-6</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>2.3984236666442662E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.3984236666442662E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>2.3984236666442662E-5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2138,9 +2187,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$K$1</c:f>
+              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>electricity if</c:v>
                 </c:pt>
@@ -2170,16 +2219,22 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$4:$K$4</c:f>
+              <c:f>IECCpUAEU!$B$4:$M$4</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>3.4771933032458345E-5</c:v>
                 </c:pt>
@@ -2208,6 +2263,12 @@
                   <c:v>3.1780367029653324E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>3.1780367029653324E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.1780367029653324E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>3.1780367029653324E-5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2245,9 +2306,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$K$1</c:f>
+              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>electricity if</c:v>
                 </c:pt>
@@ -2277,16 +2338,22 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$5:$K$5</c:f>
+              <c:f>IECCpUAEU!$B$5:$M$5</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.7204637228083889E-4</c:v>
                 </c:pt>
@@ -2315,6 +2382,12 @@
                   <c:v>1.2230751723262388E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>3.265784625690839E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.265784625690839E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>3.265784625690839E-5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2352,9 +2425,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$K$1</c:f>
+              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>electricity if</c:v>
                 </c:pt>
@@ -2384,16 +2457,22 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$6:$K$6</c:f>
+              <c:f>IECCpUAEU!$B$6:$M$6</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>4.4520366169683022E-5</c:v>
                 </c:pt>
@@ -2422,6 +2501,12 @@
                   <c:v>1.8088159747275158E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>2.7132239620912736E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.7132239620912736E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>2.7132239620912736E-5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2459,9 +2544,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$K$1</c:f>
+              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>electricity if</c:v>
                 </c:pt>
@@ -2491,16 +2576,22 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$7:$K$7</c:f>
+              <c:f>IECCpUAEU!$B$7:$M$7</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2.9652197760109964E-5</c:v>
                 </c:pt>
@@ -2529,6 +2620,12 @@
                   <c:v>7.0734511678239686E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>7.0734511678239686E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.0734511678239686E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>7.0734511678239686E-5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2568,9 +2665,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$K$1</c:f>
+              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>electricity if</c:v>
                 </c:pt>
@@ -2600,16 +2697,22 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$8:$K$8</c:f>
+              <c:f>IECCpUAEU!$B$8:$M$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0" formatCode="0.00E+00">
                   <c:v>4.4539618429716232E-5</c:v>
                 </c:pt>
@@ -2638,6 +2741,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2677,9 +2786,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$K$1</c:f>
+              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
               <c:strCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>electricity if</c:v>
                 </c:pt>
@@ -2709,16 +2818,22 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$9:$K$9</c:f>
+              <c:f>IECCpUAEU!$B$9:$M$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>7.0401933942914745E-6</c:v>
                 </c:pt>
@@ -2747,6 +2862,12 @@
                   <c:v>1.3150943145851209E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>3.3426787793366228E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.3426787793366228E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>3.3426787793366228E-5</c:v>
                 </c:pt>
               </c:numCache>
@@ -3505,13 +3626,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>582930</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>192405</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>167640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3566,13 +3687,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>548640</xdr:colOff>
-      <xdr:row>117</xdr:row>
+      <xdr:row>118</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>185146</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3632,13 +3753,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>675943</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>88899</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3676,13 +3797,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>139700</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>12504</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3720,13 +3841,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>610454</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>76742</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3764,13 +3885,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>320866</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>38159</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3811,16 +3932,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>14286</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>214312</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>176211</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:rowOff>161924</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4179,7 +4300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC3CA314-6128-4FC9-9CED-BF85AF9DB226}">
-  <dimension ref="A1:B149"/>
+  <dimension ref="A1:B150"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="76.42578125" customWidth="1"/>
@@ -4187,7 +4308,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4195,582 +4316,598 @@
         <v>0</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="13">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="67"/>
+      <c r="B4" s="69" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="67"/>
+      <c r="B5" s="70">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="67"/>
+      <c r="B6" s="69" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="67"/>
+      <c r="B7" s="71" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="67"/>
+      <c r="B8" s="69" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="67"/>
+      <c r="B9" s="69"/>
+    </row>
+    <row r="10" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="67"/>
+      <c r="B10" s="16" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="13">
         <v>2011</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="15" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="13">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>304</v>
-      </c>
-    </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="13">
+      <c r="B18" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="13">
         <v>2003</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>305</v>
-      </c>
-    </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
-        <v>306</v>
+      <c r="B20" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="16" t="s">
-        <v>61</v>
+      <c r="B21" s="15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>62</v>
+      <c r="B24" s="16" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="13">
+      <c r="B25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="13">
         <v>2016</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="16" t="s">
-        <v>70</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>71</v>
+      <c r="B30" s="16" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="14">
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="14">
         <v>2020</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="16" t="s">
-        <v>100</v>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="15" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>101</v>
+      <c r="B36" s="16" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="16" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" s="16" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="16" t="s">
-        <v>283</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
-        <v>269</v>
+      <c r="B48" s="16" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="38">
+      <c r="B49" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="38">
         <v>2016</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
-        <v>270</v>
-      </c>
-    </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="15" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="16" t="s">
-        <v>272</v>
+      <c r="B51" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="15" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>273</v>
+      <c r="B54" s="16" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="38">
+      <c r="B55" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="38">
         <v>2013</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
-        <v>274</v>
-      </c>
-    </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" s="15" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="16" t="s">
-        <v>218</v>
+      <c r="B57" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="15" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="1" t="s">
-        <v>229</v>
+      <c r="B60" s="16" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" t="s">
-        <v>219</v>
+      <c r="B61" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63" s="13">
+      <c r="B63" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="13">
         <v>2024</v>
       </c>
     </row>
-    <row r="64" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B64" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" s="35" t="s">
-        <v>222</v>
+    <row r="65" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B65" s="3" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="35"/>
+      <c r="B66" s="35" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" t="s">
-        <v>192</v>
-      </c>
+      <c r="B67" s="35"/>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" s="13">
+      <c r="B69" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="13">
         <v>2024</v>
       </c>
     </row>
-    <row r="70" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B70" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B71" s="3" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72" s="35" t="s">
-        <v>225</v>
+      <c r="B72" s="3" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B73" s="3"/>
+      <c r="B73" s="35" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B74" s="3" t="s">
-        <v>226</v>
-      </c>
+      <c r="B74" s="3"/>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" s="36">
+      <c r="B76" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="36">
         <v>44621</v>
       </c>
     </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B77" s="36" t="s">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="36" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B79" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="37"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B78" s="37" t="s">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="13">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="15" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79" s="37"/>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" s="13">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="15" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B84" s="15"/>
-    </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B85" t="s">
-        <v>266</v>
-      </c>
+      <c r="B85" s="15"/>
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B86" s="13">
+      <c r="B86" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="13">
         <v>2024</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B90" s="1" t="s">
-        <v>330</v>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B91" t="s">
-        <v>331</v>
+      <c r="B91" s="1" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B92" s="13">
+      <c r="B92" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="13">
         <v>2019</v>
       </c>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B93" t="s">
-        <v>332</v>
-      </c>
-    </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B94" s="15" t="s">
-        <v>327</v>
+      <c r="B94" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B98" s="31" t="s">
-        <v>230</v>
+      <c r="B95" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B99" s="36" t="s">
-        <v>231</v>
+      <c r="B99" s="31" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B100" s="36">
+      <c r="B100" s="36" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="36">
         <v>38231</v>
       </c>
     </row>
-    <row r="101" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B101" s="36" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B102" s="37" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B103" s="36"/>
+    <row r="102" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B102" s="36" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B103" s="37" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B104" s="16" t="s">
-        <v>335</v>
-      </c>
+      <c r="B104" s="36"/>
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B105" s="15" t="s">
-        <v>147</v>
+      <c r="B105" s="16" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B107" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B109" t="s">
-        <v>149</v>
+      <c r="B107" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B111" s="13">
+      <c r="B111" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B112" s="13">
         <v>2007</v>
       </c>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B112" s="15" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B114" t="s">
-        <v>387</v>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B113" s="15" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>156</v>
+        <v>370</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B117" s="15" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B134" s="16" t="s">
-        <v>184</v>
+      <c r="B117" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B118" s="15" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B135" s="15" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B137" t="s">
-        <v>187</v>
+      <c r="B135" s="16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="15" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B138" s="15" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>415</v>
+      <c r="B138" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B139" s="15" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143">
+      <c r="A143" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144">
         <v>138490</v>
       </c>
-      <c r="B143" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>417</v>
+      <c r="B144" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145">
+      <c r="A145" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146">
         <v>3412.14</v>
       </c>
-      <c r="B145" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A148">
-        <v>0.78452102304761584</v>
-      </c>
-      <c r="B148" t="s">
-        <v>437</v>
+      <c r="B146" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149">
+        <v>0.78452102304761584</v>
+      </c>
+      <c r="B149" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150">
         <v>0.84730412960844359</v>
       </c>
-      <c r="B149" t="s">
-        <v>446</v>
+      <c r="B150" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{C08BA00C-5E72-42AD-BB8F-655D467C5298}"/>
-    <hyperlink ref="B105" r:id="rId2" xr:uid="{810625CC-59B0-4E09-BD8A-7942EF52112A}"/>
-    <hyperlink ref="B106" r:id="rId3" xr:uid="{DE5DC99A-D169-4E5D-98F4-A0C74D220DA2}"/>
-    <hyperlink ref="B112" r:id="rId4" xr:uid="{EC39133E-2B1E-4926-9BAB-A0BC92F6703D}"/>
-    <hyperlink ref="B117" r:id="rId5" xr:uid="{5CBB2DBF-381E-4F40-8899-29D4B5FC9B35}"/>
-    <hyperlink ref="B135" r:id="rId6" display="Data from the DOE's Pathways to Commercial Liftoff: Clean Hydrogen (p.13, p.88)" xr:uid="{451B96CC-C781-4216-8C03-8132EE3013B2}"/>
-    <hyperlink ref="B138" r:id="rId7" xr:uid="{8276223D-26B3-43EA-A781-2BDC0C41D374}"/>
-    <hyperlink ref="B65" r:id="rId8" xr:uid="{C723E247-B6C1-46C7-B576-CF146861E8AC}"/>
-    <hyperlink ref="B72" r:id="rId9" xr:uid="{BA83290A-C082-4AAB-AFC4-39DE2DEA36E6}"/>
-    <hyperlink ref="B78" r:id="rId10" xr:uid="{437DE8DA-77A2-48D0-8792-6CEB29629218}"/>
-    <hyperlink ref="B102" r:id="rId11" xr:uid="{8C5AD67E-D9AA-4BD2-BE55-FC759DD68FCE}"/>
-    <hyperlink ref="B83" r:id="rId12" xr:uid="{D30485F8-6CEE-4196-A36A-BE4A2803E3DD}"/>
-    <hyperlink ref="B51" r:id="rId13" xr:uid="{07F897CB-7353-674E-92F0-010511F2EA56}"/>
-    <hyperlink ref="B57" r:id="rId14" xr:uid="{D0781D44-31AC-BC44-B7B2-E83275B62102}"/>
-    <hyperlink ref="B20" r:id="rId15" xr:uid="{27F2C98F-DA26-4901-A0EB-6AC6A38F1C0C}"/>
-    <hyperlink ref="B94" r:id="rId16" xr:uid="{561EFB21-D77A-400A-A718-A022D22539BB}"/>
+    <hyperlink ref="B106" r:id="rId1" xr:uid="{810625CC-59B0-4E09-BD8A-7942EF52112A}"/>
+    <hyperlink ref="B107" r:id="rId2" xr:uid="{DE5DC99A-D169-4E5D-98F4-A0C74D220DA2}"/>
+    <hyperlink ref="B113" r:id="rId3" xr:uid="{EC39133E-2B1E-4926-9BAB-A0BC92F6703D}"/>
+    <hyperlink ref="B118" r:id="rId4" xr:uid="{5CBB2DBF-381E-4F40-8899-29D4B5FC9B35}"/>
+    <hyperlink ref="B136" r:id="rId5" display="Data from the DOE's Pathways to Commercial Liftoff: Clean Hydrogen (p.13, p.88)" xr:uid="{451B96CC-C781-4216-8C03-8132EE3013B2}"/>
+    <hyperlink ref="B139" r:id="rId6" xr:uid="{8276223D-26B3-43EA-A781-2BDC0C41D374}"/>
+    <hyperlink ref="B66" r:id="rId7" xr:uid="{C723E247-B6C1-46C7-B576-CF146861E8AC}"/>
+    <hyperlink ref="B73" r:id="rId8" xr:uid="{BA83290A-C082-4AAB-AFC4-39DE2DEA36E6}"/>
+    <hyperlink ref="B79" r:id="rId9" xr:uid="{437DE8DA-77A2-48D0-8792-6CEB29629218}"/>
+    <hyperlink ref="B103" r:id="rId10" xr:uid="{8C5AD67E-D9AA-4BD2-BE55-FC759DD68FCE}"/>
+    <hyperlink ref="B84" r:id="rId11" xr:uid="{D30485F8-6CEE-4196-A36A-BE4A2803E3DD}"/>
+    <hyperlink ref="B52" r:id="rId12" xr:uid="{07F897CB-7353-674E-92F0-010511F2EA56}"/>
+    <hyperlink ref="B58" r:id="rId13" xr:uid="{D0781D44-31AC-BC44-B7B2-E83275B62102}"/>
+    <hyperlink ref="B21" r:id="rId14" xr:uid="{27F2C98F-DA26-4901-A0EB-6AC6A38F1C0C}"/>
+    <hyperlink ref="B95" r:id="rId15" xr:uid="{561EFB21-D77A-400A-A718-A022D22539BB}"/>
+    <hyperlink ref="B7" r:id="rId16" xr:uid="{5D5D64FB-C534-49E1-91CF-E9DAD8703987}"/>
+    <hyperlink ref="B14" r:id="rId17" xr:uid="{3ABDEADB-32F4-4E51-9C94-EFBD3570D876}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId17"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -4788,7 +4925,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -4821,10 +4958,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -4832,15 +4969,15 @@
         <v>11</v>
       </c>
       <c r="B2" s="12">
-        <f>Boilers!$A$18</f>
-        <v>5.6711966224873446E-5</v>
+        <f>'Boilers &amp; Heat Pumps'!B13</f>
+        <v>3.0882108581950831E-5</v>
       </c>
       <c r="C2" s="12">
-        <f>Boilers!$G$43</f>
+        <f>'Boilers &amp; Heat Pumps'!$G$39</f>
         <v>1.4986595988547842E-5</v>
       </c>
       <c r="D2" s="12">
-        <f>Boilers!A39</f>
+        <f>'Boilers &amp; Heat Pumps'!A35</f>
         <v>1.5989491110961776E-5</v>
       </c>
       <c r="E2" s="10">
@@ -4848,7 +4985,7 @@
         <v>1.4986595988547842E-5</v>
       </c>
       <c r="F2" s="12">
-        <f>Boilers!$G$44</f>
+        <f>'Boilers &amp; Heat Pumps'!$G$40</f>
         <v>9.436004881678272E-6</v>
       </c>
       <c r="G2" s="40">
@@ -4867,7 +5004,7 @@
         <v>9.436004881678272E-6</v>
       </c>
       <c r="K2" s="12">
-        <f>Boilers!A60</f>
+        <f>'Boilers &amp; Heat Pumps'!A56</f>
         <v>2.3984236666442662E-5</v>
       </c>
       <c r="L2" s="12">
@@ -4885,7 +5022,7 @@
       </c>
       <c r="B3" s="10">
         <f>B2</f>
-        <v>5.6711966224873446E-5</v>
+        <v>3.0882108581950831E-5</v>
       </c>
       <c r="C3" s="10">
         <f t="shared" ref="C3:K3" si="1">C2</f>
@@ -5241,32 +5378,32 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -5292,7 +5429,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5312,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="12">
-        <f>'Other (mobile)'!A7</f>
+        <f>'Other (mobile)'!A6</f>
         <v>3.1381977460259781E-3</v>
       </c>
     </row>
@@ -5348,7 +5485,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="10">
-        <f>'Other (mobile)'!A6</f>
+        <f>'Other (mobile)'!A5</f>
         <v>8.2719018162705823E-4</v>
       </c>
     </row>
@@ -5398,7 +5535,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="B12" s="10">
         <f>B11</f>
@@ -5407,7 +5544,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="B13" s="10">
         <f>B12</f>
@@ -5421,7 +5558,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F78C19FD-7E25-465C-BF9B-84ECCFD8C3AD}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -5434,314 +5571,364 @@
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="72" t="s">
+        <v>440</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="77"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>441</v>
       </c>
       <c r="B6">
-        <v>56603</v>
-      </c>
-      <c r="C6" s="8">
-        <v>750000</v>
-      </c>
-      <c r="D6" s="9">
-        <f>C6/(B6*10^6)</f>
-        <v>1.3250181085808173E-5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+      <c r="C6" s="75" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>442</v>
       </c>
       <c r="B7">
-        <v>25717</v>
-      </c>
-      <c r="C7" s="8">
-        <v>700000</v>
-      </c>
-      <c r="D7" s="9">
-        <f t="shared" ref="D7:D9" si="0">C7/(B7*10^6)</f>
-        <v>2.7219349068709415E-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8760</v>
+      </c>
+      <c r="C7" s="75" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" s="75"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8">
-        <v>60507</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1250000</v>
-      </c>
-      <c r="D8" s="9">
+        <v>444</v>
+      </c>
+      <c r="B8" s="19">
+        <v>0.65</v>
+      </c>
+      <c r="C8" s="75" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="75"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B9" s="76">
+        <f>B6/(B7*B8)</f>
+        <v>0.10537407797681771</v>
+      </c>
+      <c r="C9" s="75" t="s">
+        <v>296</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11">
+        <v>3412.14</v>
+      </c>
+      <c r="C11" s="75" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>446</v>
+      </c>
+      <c r="B13" s="12">
+        <f>B9/B11</f>
+        <v>3.0882108581950831E-5</v>
+      </c>
+      <c r="C13" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="D14" s="24" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" s="8">
+        <v>80375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>282</v>
+      </c>
+      <c r="B21" s="8">
+        <v>91475</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>283</v>
+      </c>
+      <c r="B22" s="8">
+        <f>AVERAGE(B20:B21)</f>
+        <v>85925</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>284</v>
+      </c>
+      <c r="B24">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>285</v>
+      </c>
+      <c r="B25">
+        <v>0.74570000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26">
+        <f>B24*B25</f>
+        <v>298.28000000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="22">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>286</v>
+      </c>
+      <c r="B30">
+        <f>B26*B28</f>
+        <v>1574918.4000000001</v>
+      </c>
+      <c r="C30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31">
+        <v>3412.14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>286</v>
+      </c>
+      <c r="B32">
+        <f>B30*B31</f>
+        <v>5373842069.3760004</v>
+      </c>
+      <c r="C32" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="12">
+        <f>B22/B32</f>
+        <v>1.5989491110961776E-5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B38" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39">
+        <v>2000</v>
+      </c>
+      <c r="C39">
+        <v>300</v>
+      </c>
+      <c r="D39">
+        <f>B39*C39</f>
+        <v>600000</v>
+      </c>
+      <c r="E39" s="19">
+        <v>0.9</v>
+      </c>
+      <c r="F39">
+        <f>$B$46/E39</f>
+        <v>40035776000</v>
+      </c>
+      <c r="G39" s="12">
+        <f>D39/F39</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40">
+        <v>2000</v>
+      </c>
+      <c r="C40">
+        <v>200</v>
+      </c>
+      <c r="D40">
+        <f t="shared" ref="D40:D41" si="0">B40*C40</f>
+        <v>400000</v>
+      </c>
+      <c r="E40" s="19">
+        <v>0.85</v>
+      </c>
+      <c r="F40">
+        <f t="shared" ref="F40:F41" si="1">$B$46/E40</f>
+        <v>42390821647.058823</v>
+      </c>
+      <c r="G40" s="12">
+        <f t="shared" ref="G40:G41" si="2">D40/F40</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41">
+        <v>2000</v>
+      </c>
+      <c r="C41">
+        <v>100</v>
+      </c>
+      <c r="D41">
         <f t="shared" si="0"/>
-        <v>2.0658766754259837E-5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9">
-        <f>AVERAGE(B6:B8)</f>
-        <v>47609</v>
-      </c>
-      <c r="C9">
-        <f>AVERAGE(C6:C8)</f>
-        <v>900000</v>
-      </c>
-      <c r="D9" s="10">
-        <f t="shared" si="0"/>
-        <v>1.8903988741624482E-5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>200000</v>
+      </c>
+      <c r="E41" s="19">
+        <v>0.95</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="1"/>
+        <v>37928629894.736847</v>
+      </c>
+      <c r="G41" s="9">
+        <f t="shared" si="2"/>
+        <v>5.2730615515260925E-6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="12">
-        <f>D9*A15</f>
-        <v>5.6711966224873446E-5</v>
-      </c>
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>298</v>
-      </c>
-      <c r="B24" s="8">
-        <v>80375</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>299</v>
-      </c>
-      <c r="B25" s="8">
-        <v>91475</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>300</v>
-      </c>
-      <c r="B26" s="8">
-        <f>AVERAGE(B24:B25)</f>
-        <v>85925</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>301</v>
-      </c>
-      <c r="B28">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>302</v>
-      </c>
-      <c r="B29">
-        <v>0.74570000000000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>117</v>
-      </c>
-      <c r="B30">
-        <f>B28*B29</f>
-        <v>298.28000000000003</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="22">
-        <v>5280</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>303</v>
-      </c>
-      <c r="B34">
-        <f>B30*B32</f>
-        <v>1574918.4000000001</v>
-      </c>
-      <c r="C34" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
-        <v>3412.14</v>
-      </c>
-      <c r="C35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>303</v>
-      </c>
-      <c r="B36">
-        <f>B34*B35</f>
-        <v>5373842069.3760004</v>
-      </c>
-      <c r="C36" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="12">
-        <f>B26/B36</f>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="B39" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-    </row>
-    <row r="42" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B42" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F42" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="G42" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43">
-        <v>2000</v>
-      </c>
-      <c r="C43">
-        <v>300</v>
-      </c>
-      <c r="D43">
-        <f>B43*C43</f>
-        <v>600000</v>
-      </c>
-      <c r="E43" s="19">
-        <v>0.9</v>
-      </c>
-      <c r="F43">
-        <f>$B$50/E43</f>
-        <v>40035776000</v>
-      </c>
-      <c r="G43" s="12">
-        <f>D43/F43</f>
-        <v>1.4986595988547842E-5</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -5749,133 +5936,73 @@
         <v>50</v>
       </c>
       <c r="B44">
-        <v>2000</v>
-      </c>
-      <c r="C44">
-        <v>200</v>
-      </c>
-      <c r="D44">
-        <f t="shared" ref="D44:D45" si="1">B44*C44</f>
-        <v>400000</v>
-      </c>
-      <c r="E44" s="19">
-        <v>0.85</v>
-      </c>
-      <c r="F44">
-        <f t="shared" ref="F44:F45" si="2">$B$50/E44</f>
-        <v>42390821647.058823</v>
-      </c>
-      <c r="G44" s="12">
-        <f t="shared" ref="G44:G45" si="3">D44/F44</f>
-        <v>9.436004881678272E-6</v>
+        <f>B39*B28</f>
+        <v>10560000</v>
+      </c>
+      <c r="C44" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B45">
-        <v>2000</v>
-      </c>
-      <c r="C45">
-        <v>100</v>
-      </c>
-      <c r="D45">
-        <f t="shared" si="1"/>
-        <v>200000</v>
-      </c>
-      <c r="E45" s="19">
-        <v>0.95</v>
-      </c>
-      <c r="F45">
-        <f t="shared" si="2"/>
-        <v>37928629894.736847</v>
-      </c>
-      <c r="G45" s="9">
-        <f t="shared" si="3"/>
-        <v>5.2730615515260925E-6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>57</v>
+        <v>3412.14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46">
+        <f>B44*B45</f>
+        <v>36032198400</v>
+      </c>
+      <c r="C46" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>67</v>
-      </c>
-      <c r="B48">
-        <f>B43*B32</f>
-        <v>10560000</v>
-      </c>
-      <c r="C48" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49">
-        <v>3412.14</v>
-      </c>
-      <c r="C49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>67</v>
-      </c>
-      <c r="B50">
-        <f>B48*B49</f>
-        <v>36032198400</v>
-      </c>
-      <c r="C50" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>65</v>
-      </c>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>75</v>
-      </c>
-      <c r="B57" s="8"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>76</v>
-      </c>
-      <c r="B58" s="20"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="12">
-        <f>A39*1.5</f>
+        <v>58</v>
+      </c>
+      <c r="B53" s="8"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="20"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <f>A35*1.5</f>
         <v>2.3984236666442662E-5</v>
       </c>
-      <c r="B60" t="s">
-        <v>45</v>
+      <c r="B56" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -5894,330 +6021,330 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B5" s="8">
         <v>307500</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B6">
         <v>4000</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B8" s="8">
         <v>75863</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B9" s="8">
         <v>6226</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B11" s="25">
         <v>0.45</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B12" s="25">
         <v>0.15</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B14" s="21">
         <f>B8/B11</f>
         <v>168584.44444444444</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B15" s="21">
         <f>B9/B12</f>
         <v>41506.666666666672</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B17">
         <v>100000</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B18">
         <v>3412.14</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B20" s="9">
         <f>B14*B17</f>
         <v>16858444444.444445</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B21" s="9">
         <f>B15*B18</f>
         <v>141626557.60000002</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B26" s="9">
         <f>SUM(B20:B21)</f>
         <v>17000071002.044445</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B27" s="12">
         <f>B5/B26</f>
         <v>1.8088159747275158E-5</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B32" s="8">
         <v>200</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B33" s="8">
         <v>500</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B34" s="8">
         <f>AVERAGE(B32:B33)</f>
         <v>350</v>
       </c>
       <c r="C34" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B36">
         <v>500</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B38" s="8">
         <f>B34*B36</f>
         <v>175000</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B41">
         <v>0.57599999999999996</v>
       </c>
       <c r="C41" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="B42">
         <f>B41*B36</f>
         <v>288</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B44">
         <f>B6</f>
         <v>4000</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D44" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B46">
         <f>B42*B44</f>
         <v>1152000</v>
       </c>
       <c r="C46" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B47" s="9">
         <f>B46*B18</f>
         <v>3930785280</v>
       </c>
       <c r="C47" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B49" s="12">
         <f>B38/B47</f>
         <v>4.4520366169683022E-5</v>
       </c>
       <c r="C49" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -6241,7 +6368,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6249,25 +6376,25 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="B3" s="42"/>
       <c r="C3" s="11" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="B5">
         <v>492000</v>
@@ -6276,7 +6403,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="B6">
         <v>135000</v>
@@ -6285,7 +6412,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B7">
         <v>474000</v>
@@ -6294,7 +6421,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="B8">
         <v>70000</v>
@@ -6303,7 +6430,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B9">
         <v>22000</v>
@@ -6312,7 +6439,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="B10">
         <v>18000</v>
@@ -6321,7 +6448,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B11">
         <v>216000</v>
@@ -6330,7 +6457,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="B12">
         <v>51000</v>
@@ -6339,7 +6466,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="B13">
         <v>125000</v>
@@ -6348,24 +6475,24 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="11" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="B17" s="20">
         <v>13400</v>
@@ -6373,7 +6500,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="B18" s="20">
         <v>5300</v>
@@ -6381,7 +6508,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="B19" s="20">
         <v>13600</v>
@@ -6389,32 +6516,32 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="11" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="B23">
         <v>4380</v>
@@ -6425,7 +6552,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B24">
         <v>4380</v>
@@ -6436,7 +6563,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="40"/>
@@ -6444,47 +6571,47 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="B33" s="1">
-        <f>Boilers!B32</f>
+        <f>'Boilers &amp; Heat Pumps'!B28</f>
         <v>5280</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B36" s="46">
         <v>3412.14</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -6492,7 +6619,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="45" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B38" s="44"/>
       <c r="C38" s="44"/>
@@ -6500,21 +6627,21 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="B40">
         <f>$B$33*D23*B36</f>
@@ -6531,7 +6658,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B41">
         <f>$B$33*C24</f>
@@ -6548,33 +6675,33 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="B51" s="42"/>
       <c r="C51" s="42"/>
       <c r="D51" s="11" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="B53">
         <v>722000</v>
@@ -6586,7 +6713,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B54">
         <v>882000</v>
@@ -6614,7 +6741,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6625,12 +6752,12 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I2" s="1" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="C3" s="25"/>
       <c r="F3" s="25">
@@ -6638,107 +6765,107 @@
         <v>264.16000000000003</v>
       </c>
       <c r="G3" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="F4">
         <v>450</v>
       </c>
       <c r="G4" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C5" s="32"/>
       <c r="F5" s="32">
         <v>800000</v>
       </c>
       <c r="G5" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F7">
         <f>F4*F5</f>
         <v>360000000</v>
       </c>
       <c r="G7" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F8">
         <f>F7*0.003412</f>
         <v>1228320</v>
       </c>
       <c r="G8" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="F9" s="25">
         <f>F3*F5</f>
         <v>211328000.00000003</v>
       </c>
       <c r="G9" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F10" s="12">
         <f>F9/(F8*10^6)</f>
         <v>1.7204637228083889E-4</v>
       </c>
       <c r="G10" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="E12">
         <f>8760*155</f>
         <v>1357800</v>
       </c>
       <c r="F12" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -6749,13 +6876,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="F16" s="20">
         <v>170</v>
       </c>
       <c r="G16" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -6764,7 +6891,7 @@
         <v>26.356589147286826</v>
       </c>
       <c r="G17" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -6773,7 +6900,7 @@
         <v>9.4883645023316546E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -6782,80 +6909,80 @@
         <v>2.7808805692648461E-5</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="F21">
         <v>36000000</v>
       </c>
       <c r="G21" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="F22" s="20">
         <f>F21*0.14</f>
         <v>5040000.0000000009</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="F23">
         <f>AVERAGE(5.1,7.8)</f>
         <v>6.4499999999999993</v>
       </c>
       <c r="G23" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="I23" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="F24">
         <v>8000</v>
       </c>
       <c r="G24" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="F25">
         <v>600</v>
       </c>
       <c r="G25" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -6864,7 +6991,7 @@
         <v>3869.9999999999995</v>
       </c>
       <c r="G26" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="I26" s="15"/>
     </row>
@@ -6874,95 +7001,95 @@
         <v>1289999.9999999998</v>
       </c>
       <c r="G27" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="I27" s="15"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F28">
         <f>F27*277.778</f>
         <v>358333619.99999994</v>
       </c>
       <c r="G28" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="I28" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F29">
         <f>F28*0.003412</f>
         <v>1222634.3114399998</v>
       </c>
       <c r="G29" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F30" s="12">
         <f>(F21*0.14)/(F29*10^6)</f>
         <v>4.1222464909102436E-6</v>
       </c>
       <c r="G30" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="I30" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="F34">
         <v>21.08</v>
       </c>
       <c r="G34" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="F35">
         <v>0.76</v>
       </c>
       <c r="G35" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="F36" s="34">
         <f>F34*F35</f>
         <v>16.020799999999998</v>
       </c>
       <c r="G36" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -6970,7 +7097,7 @@
         <v>1.3284</v>
       </c>
       <c r="G37" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -6979,7 +7106,7 @@
         <v>21.282030719999998</v>
       </c>
       <c r="G38" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -6987,7 +7114,7 @@
         <v>1.32</v>
       </c>
       <c r="G39" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -6996,7 +7123,7 @@
         <v>28.092280550399998</v>
       </c>
       <c r="G40" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -7005,7 +7132,7 @@
         <v>4.3553923333953488</v>
       </c>
       <c r="G41" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -7013,7 +7140,7 @@
         <v>277.77800000000002</v>
       </c>
       <c r="G42" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -7022,7 +7149,7 @@
         <v>1.5679399856703368E-2</v>
       </c>
       <c r="G43" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -7030,7 +7157,7 @@
         <v>3412.14</v>
       </c>
       <c r="G44" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -7039,12 +7166,12 @@
         <v>4.5951806950193628E-6</v>
       </c>
       <c r="G45" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -7055,99 +7182,99 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="F49" s="32">
         <v>6000000</v>
       </c>
       <c r="G49" s="33" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="F50">
         <v>300</v>
       </c>
       <c r="G50" t="s">
+        <v>197</v>
+      </c>
+      <c r="I50" s="15" t="s">
         <v>214</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="F51">
         <v>8760</v>
       </c>
       <c r="G51" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="F52">
         <v>1100</v>
       </c>
       <c r="G52" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F54">
         <f>(F3*365)*F52</f>
         <v>106060240.00000001</v>
       </c>
       <c r="G54" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F55" s="34">
         <f>F54*0.003412</f>
         <v>361877.53888000007</v>
       </c>
       <c r="G55" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F56" s="12">
         <f>(F49*1.25)/(F55*10^6)</f>
         <v>2.0725243194734525E-5</v>
       </c>
       <c r="G56" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
@@ -7158,90 +7285,90 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="F60">
         <f>574-184</f>
         <v>390</v>
       </c>
       <c r="G60" s="33" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="F61">
         <v>3500</v>
       </c>
       <c r="G61" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="F62" s="32">
         <v>1500000</v>
       </c>
       <c r="G62" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="I62" s="15" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F64">
         <f>F61*F62</f>
         <v>5250000000</v>
       </c>
       <c r="G64" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F65">
         <f>F64*0.003412</f>
         <v>17913000</v>
       </c>
       <c r="G65" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="F66" s="25">
         <f>F60*F62</f>
         <v>585000000</v>
       </c>
       <c r="G66" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F67" s="12">
         <f>F66/(F65*10^6)</f>
         <v>3.265784625690839E-5</v>
       </c>
       <c r="G67" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -7281,67 +7408,67 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="26" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="C8" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="J8" s="30" t="s">
         <v>136</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>153</v>
       </c>
       <c r="K8" s="27"/>
       <c r="L8" s="29" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="M8" s="27"/>
       <c r="N8" s="28" t="s">
@@ -7349,28 +7476,28 @@
       </c>
       <c r="O8" s="27"/>
       <c r="P8" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="Q8" s="27"/>
       <c r="R8" s="29" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="S8" s="27"/>
       <c r="T8" s="29" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="U8" s="27"/>
       <c r="V8" s="27"/>
       <c r="W8" s="29" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>0.3</v>
@@ -7420,10 +7547,10 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -7473,10 +7600,10 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>350</v>
@@ -7526,10 +7653,10 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>500</v>
@@ -7579,10 +7706,10 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>0.35</v>
@@ -7632,10 +7759,10 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>1.8</v>
@@ -7685,10 +7812,10 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D15">
         <v>0.35</v>
@@ -7738,10 +7865,10 @@
     </row>
     <row r="16" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -7791,10 +7918,10 @@
     </row>
     <row r="17" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D17">
         <v>50</v>
@@ -7844,10 +7971,10 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -7897,10 +8024,10 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D19">
         <v>180</v>
@@ -7953,7 +8080,7 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N21" s="21"/>
       <c r="P21" s="21"/>
@@ -7969,7 +8096,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="N22" s="21"/>
       <c r="P22" s="21"/>
@@ -7987,24 +8114,24 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C23" s="49" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="49" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="G23" s="49"/>
       <c r="H23" s="49"/>
       <c r="I23" s="49" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="J23" s="49"/>
       <c r="K23" s="49"/>
       <c r="L23" s="49"/>
       <c r="M23" s="49"/>
       <c r="N23" s="50" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
@@ -8012,24 +8139,24 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C24" s="61" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="D24" s="62"/>
       <c r="E24" s="63"/>
-      <c r="F24" s="58">
+      <c r="F24" s="64">
         <f>0.048/0.581</f>
         <v>8.2616179001721177E-2</v>
       </c>
-      <c r="G24" s="59"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="64">
+      <c r="G24" s="65"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="58">
         <f>((T13+T15)/2)</f>
         <v>23.414850000000001</v>
       </c>
-      <c r="J24" s="65"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="66"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="59"/>
+      <c r="M24" s="60"/>
       <c r="N24" s="51">
         <f>((W13+W15)/2)</f>
         <v>2.2407199119595664E-4</v>
@@ -8040,24 +8167,24 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C25" s="61" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="D25" s="62"/>
       <c r="E25" s="63"/>
-      <c r="F25" s="58">
+      <c r="F25" s="64">
         <f>0.104/0.581</f>
         <v>0.17900172117039587</v>
       </c>
-      <c r="G25" s="59"/>
-      <c r="H25" s="60"/>
-      <c r="I25" s="64">
+      <c r="G25" s="65"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="58">
         <f>T14</f>
         <v>97.18877280000001</v>
       </c>
-      <c r="J25" s="65"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="66"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="60"/>
       <c r="N25" s="51">
         <f>W14</f>
         <v>3.3521233224690123E-5</v>
@@ -8068,24 +8195,24 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C26" s="61" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="D26" s="62"/>
       <c r="E26" s="63"/>
-      <c r="F26" s="58">
+      <c r="F26" s="64">
         <f>0.127/0.581</f>
         <v>0.21858864027538727</v>
       </c>
-      <c r="G26" s="59"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="64">
+      <c r="G26" s="65"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="58">
         <f>T16</f>
         <v>319.17554000000001</v>
       </c>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="66"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="59"/>
+      <c r="M26" s="60"/>
       <c r="N26" s="51">
         <f>W16</f>
         <v>1.1301491868138288E-5</v>
@@ -8096,24 +8223,24 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C27" s="61" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D27" s="62"/>
       <c r="E27" s="63"/>
-      <c r="F27" s="58">
+      <c r="F27" s="64">
         <f>0.144/0.581</f>
         <v>0.24784853700516352</v>
       </c>
-      <c r="G27" s="59"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="64">
+      <c r="G27" s="65"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="58">
         <f>((T10+T18)/2)</f>
         <v>1214.1039020000001</v>
       </c>
-      <c r="J27" s="65"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="66"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="59"/>
+      <c r="M27" s="60"/>
       <c r="N27" s="51">
         <f>((W10+W18)/2)</f>
         <v>5.481183696812177E-6</v>
@@ -8124,24 +8251,24 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C28" s="61" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="D28" s="62"/>
       <c r="E28" s="63"/>
-      <c r="F28" s="58">
+      <c r="F28" s="64">
         <f>0.157/0.581</f>
         <v>0.27022375215146299</v>
       </c>
-      <c r="G28" s="59"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="64">
+      <c r="G28" s="65"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="58">
         <f>((T9+T11+T12+T17+T19)/5)</f>
         <v>49678.416604960003</v>
       </c>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="66"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="60"/>
       <c r="N28" s="51">
         <f>((W9+W11+W12+W17+W19)/5)</f>
         <v>4.8514850079979492E-6</v>
@@ -8160,72 +8287,72 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="G32" s="1" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="U32" s="9"/>
       <c r="W32" s="9"/>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="D33" s="21">
         <v>502</v>
       </c>
       <c r="E33" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="T33" s="9"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="D34" s="21">
         <v>250</v>
       </c>
       <c r="E34" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="T34" s="9"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="D35" s="21">
         <f>D34/1.341</f>
         <v>186.42803877703207</v>
       </c>
       <c r="E35" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="D36" s="21">
         <v>2080</v>
       </c>
       <c r="E36" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="I36" s="8"/>
     </row>
@@ -8238,38 +8365,38 @@
         <v>1323.0723340790455</v>
       </c>
       <c r="E37" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D38" s="12">
         <f>(D33*D35)/(D37*10^6)</f>
         <v>7.0734511678239686E-5</v>
       </c>
       <c r="E38" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
     <mergeCell ref="I24:M24"/>
     <mergeCell ref="I25:M25"/>
     <mergeCell ref="I26:M26"/>
     <mergeCell ref="I27:M27"/>
     <mergeCell ref="I28:M28"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G33" r:id="rId1" xr:uid="{89D540DE-65F8-419E-8E02-FD08F0D4350B}"/>
@@ -8292,7 +8419,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -8303,12 +8430,12 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -8316,94 +8443,94 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="G5" s="1"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="D6">
         <f>AVERAGE(760,1000)</f>
         <v>880</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="D7">
         <f>AVERAGE(373.1,597)</f>
         <v>485.05</v>
       </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D11">
         <f>AVERAGE(975,1200)</f>
         <v>1087.5</v>
       </c>
       <c r="E11" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="D12">
         <f>AVERAGE(1492.5,2238.8)</f>
         <v>1865.65</v>
       </c>
       <c r="E12" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="D15">
         <v>1.5</v>
       </c>
       <c r="E15" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="D16">
         <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="G18">
         <f>(D6)*(1.5*1000000)</f>
@@ -8412,7 +8539,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G19">
         <f>(1.5*1000000)*(0.7*8760)</f>
@@ -8421,7 +8548,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="G20">
         <f>G19*3412</f>
@@ -8430,7 +8557,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="G21">
         <f>G18/G20</f>
@@ -8439,7 +8566,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="G22">
         <f>(D7*(1.5*1000000))/G20</f>
@@ -8448,7 +8575,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="G24">
         <f>(D11)*(1.5*1000000)</f>
@@ -8457,7 +8584,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="G25">
         <f>(1.5*1000000)*(0.7*8760)</f>
@@ -8466,7 +8593,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="G26">
         <f>G25*3412</f>
@@ -8475,7 +8602,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="G27">
         <f>G24/G26</f>
@@ -8484,7 +8611,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="G28">
         <f>(D12*(1.5*1000000))/G26</f>
@@ -8493,12 +8620,12 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="G32" s="12">
         <f>(G21*0.75)+(G27*0.25)</f>
@@ -8507,7 +8634,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="G33" s="9">
         <f>G32*0.6</f>
@@ -8519,7 +8646,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="G35" s="9">
         <f>(G22*0.75)+(G28*0.25)</f>
@@ -8544,7 +8671,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -8556,184 +8683,184 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="E3" s="39">
         <f>2758*1.03</f>
         <v>2840.7400000000002</v>
       </c>
       <c r="F3" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="H3" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="E4">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <f>18*365</f>
         <v>6570</v>
       </c>
       <c r="F5" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="H5" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="E7">
         <f>E4*E5</f>
         <v>118260</v>
       </c>
       <c r="F7" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="E8">
         <f>E7*0.003412</f>
         <v>403.50312000000002</v>
       </c>
       <c r="F8" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E9" s="12">
         <f>E3/(E8*10^6)</f>
         <v>7.0401933942914745E-6</v>
       </c>
       <c r="F9" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="B16" s="8">
         <v>862500</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B17" s="8">
         <v>1500000</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="B18" s="8">
         <f>AVERAGE(B16,B17)</f>
         <v>1181250</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B20" s="32">
         <v>8760</v>
       </c>
       <c r="C20" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="B21" s="32">
         <v>6051100</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="B23">
         <f>B20*B21</f>
         <v>53007636000</v>
       </c>
       <c r="C23" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B24" s="12">
         <f>B18/B23</f>
         <v>2.2284525195577483E-5</v>
       </c>
       <c r="C24" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -8746,7 +8873,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B88B710-1DAB-47E6-AE70-A12C5CA0B896}">
-  <dimension ref="A2:P84"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
@@ -8757,107 +8884,147 @@
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="53" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+    </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="53" t="s">
-        <v>404</v>
-      </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
+      <c r="A2" s="54">
+        <v>0.57060049240377109</v>
+      </c>
+      <c r="B2" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="54">
-        <v>0.57060049240377109</v>
-      </c>
-      <c r="B3" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="54">
         <f>4000/15</f>
         <v>266.66666666666669</v>
       </c>
-      <c r="B4" t="s">
-        <v>442</v>
-      </c>
+      <c r="B3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
+      <c r="A5" s="56">
+        <f>AVERAGE(O29,H39,H83)</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="56">
-        <f>AVERAGE(O30,H40,H84)</f>
-        <v>8.2719018162705823E-4</v>
+        <f>AVERAGE(O30,H40,H82)</f>
+        <v>3.1381977460259781E-3</v>
       </c>
       <c r="B6" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="56">
-        <f>AVERAGE(O31,H41,H83)</f>
-        <v>3.1381977460259781E-3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="24"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>405</v>
+      <c r="A7" s="24"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>392</v>
+      </c>
+      <c r="D28" t="s">
+        <v>394</v>
+      </c>
+      <c r="E28" t="s">
+        <v>395</v>
+      </c>
+      <c r="F28" t="s">
+        <v>396</v>
+      </c>
+      <c r="G28" t="s">
+        <v>397</v>
+      </c>
+      <c r="H28" t="s">
+        <v>401</v>
+      </c>
+      <c r="I28" t="s">
+        <v>419</v>
+      </c>
+      <c r="M28" t="s">
+        <v>423</v>
+      </c>
+      <c r="N28" t="s">
+        <v>424</v>
+      </c>
+      <c r="O28" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>409</v>
-      </c>
-      <c r="D29" t="s">
-        <v>411</v>
-      </c>
-      <c r="E29" t="s">
-        <v>412</v>
-      </c>
-      <c r="F29" t="s">
-        <v>413</v>
-      </c>
-      <c r="G29" t="s">
-        <v>414</v>
-      </c>
-      <c r="H29" t="s">
-        <v>418</v>
-      </c>
-      <c r="I29" t="s">
-        <v>436</v>
-      </c>
-      <c r="M29" t="s">
-        <v>440</v>
-      </c>
-      <c r="N29" t="s">
-        <v>441</v>
-      </c>
-      <c r="O29" t="s">
-        <v>145</v>
+      <c r="B29" t="s">
+        <v>389</v>
+      </c>
+      <c r="C29">
+        <v>17000</v>
+      </c>
+      <c r="D29">
+        <v>7.1</v>
+      </c>
+      <c r="F29">
+        <v>9.5</v>
+      </c>
+      <c r="G29" s="21">
+        <f>D29*About!$A$144</f>
+        <v>983279</v>
+      </c>
+      <c r="H29" s="21">
+        <f>G29/F29</f>
+        <v>103503.05263157895</v>
+      </c>
+      <c r="I29">
+        <v>250</v>
+      </c>
+      <c r="L29" t="s">
+        <v>386</v>
+      </c>
+      <c r="M29">
+        <f>AVERAGE(C29:C31)*About!A149</f>
+        <v>21966.588645333242</v>
+      </c>
+      <c r="N29">
+        <f>AVERAGE(H29:H31)*A3</f>
+        <v>27574616.079328757</v>
+      </c>
+      <c r="O29" s="55">
+        <f>M29/N29</f>
+        <v>7.9662355342094654E-4</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="C30">
         <v>17000</v>
@@ -8866,315 +9033,275 @@
         <v>7.1</v>
       </c>
       <c r="F30">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="G30" s="21">
-        <f>D30*About!$A$143</f>
+        <f>D30*About!$A$144</f>
         <v>983279</v>
       </c>
       <c r="H30" s="21">
-        <f>G30/F30</f>
-        <v>103503.05263157895</v>
+        <f t="shared" ref="H30:H31" si="0">G30/F30</f>
+        <v>98327.9</v>
       </c>
       <c r="I30">
         <v>250</v>
       </c>
       <c r="L30" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="M30">
-        <f>AVERAGE(C30:C32)*About!A148</f>
-        <v>21966.588645333242</v>
+        <f>C32*About!A149</f>
+        <v>43148.65626761887</v>
       </c>
       <c r="N30">
-        <f>AVERAGE(H30:H32)*A4</f>
-        <v>27574616.079328757</v>
+        <f>N29*(1-A2)</f>
+        <v>11840526.566618824</v>
       </c>
       <c r="O30" s="55">
         <f>M30/N30</f>
-        <v>7.9662355342094654E-4</v>
+        <v>3.6441501165383038E-3</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="C31">
-        <v>17000</v>
+        <v>50000</v>
       </c>
       <c r="D31">
-        <v>7.1</v>
+        <v>18</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G31" s="21">
-        <f>D31*About!$A$143</f>
-        <v>983279</v>
+        <f>D31*About!$A$144</f>
+        <v>2492820</v>
       </c>
       <c r="H31" s="21">
-        <f t="shared" ref="H31:H32" si="0">G31/F31</f>
-        <v>98327.9</v>
+        <f t="shared" si="0"/>
+        <v>108383.47826086957</v>
       </c>
       <c r="I31">
         <v>250</v>
       </c>
-      <c r="L31" t="s">
-        <v>439</v>
-      </c>
-      <c r="M31">
-        <f>C33*About!A148</f>
-        <v>43148.65626761887</v>
-      </c>
-      <c r="N31">
-        <f>N30*(1-A3)</f>
-        <v>11840526.566618824</v>
-      </c>
-      <c r="O31" s="55">
-        <f>M31/N31</f>
-        <v>3.6441501165383038E-3</v>
-      </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="C32">
-        <v>50000</v>
-      </c>
-      <c r="D32">
-        <v>18</v>
+        <v>55000</v>
+      </c>
+      <c r="E32">
+        <v>24</v>
       </c>
       <c r="F32">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G32" s="21">
-        <f>D32*About!$A$143</f>
-        <v>2492820</v>
-      </c>
-      <c r="H32" s="21">
-        <f t="shared" si="0"/>
-        <v>108383.47826086957</v>
-      </c>
+        <f>E32*About!$A$146</f>
+        <v>81891.360000000001</v>
+      </c>
+      <c r="H32" s="21"/>
       <c r="I32">
         <v>250</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B33" t="s">
-        <v>410</v>
-      </c>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C33">
-        <v>55000</v>
-      </c>
-      <c r="E33">
-        <v>24</v>
-      </c>
-      <c r="F33">
-        <v>16</v>
-      </c>
-      <c r="G33" s="21">
-        <f>E33*About!$A$145</f>
-        <v>81891.360000000001</v>
+        <f>C32/AVERAGE(C29:C31)</f>
+        <v>1.9642857142857142</v>
       </c>
       <c r="H33" s="21"/>
-      <c r="I33">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C34">
-        <f>C33/AVERAGE(C30:C32)</f>
-        <v>1.9642857142857142</v>
-      </c>
-      <c r="H34" s="21"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E35">
-        <f>E33/38.1</f>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E34">
+        <f>E32/38.1</f>
         <v>0.62992125984251968</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C39" t="s">
-        <v>420</v>
-      </c>
-      <c r="D39" t="s">
-        <v>247</v>
-      </c>
-      <c r="E39" t="s">
-        <v>435</v>
-      </c>
-      <c r="F39" t="s">
-        <v>443</v>
-      </c>
-      <c r="G39" t="s">
-        <v>445</v>
-      </c>
-      <c r="H39" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>421</v>
-      </c>
-      <c r="C40">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="24" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>403</v>
+      </c>
+      <c r="D38" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" t="s">
+        <v>418</v>
+      </c>
+      <c r="F38" t="s">
+        <v>426</v>
+      </c>
+      <c r="G38" t="s">
+        <v>428</v>
+      </c>
+      <c r="H38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>404</v>
+      </c>
+      <c r="C39">
         <v>2940</v>
       </c>
-      <c r="D40">
+      <c r="D39">
         <v>545</v>
       </c>
-      <c r="E40">
+      <c r="E39">
         <f>37500</f>
         <v>37500</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F39" s="21">
         <f>AVERAGE(60400,120900,214300)</f>
         <v>131866.66666666666</v>
       </c>
-      <c r="G40" s="21">
-        <f>F40*$A$4</f>
+      <c r="G39" s="21">
+        <f>F39*$A$3</f>
         <v>35164444.444444448</v>
       </c>
-      <c r="H40" s="55">
-        <f>E40*About!$A$149/G40</f>
+      <c r="H39" s="55">
+        <f>E39*About!$A$150/G39</f>
         <v>9.0358045924813471E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>422</v>
-      </c>
-      <c r="C41">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>405</v>
+      </c>
+      <c r="C40">
         <v>113</v>
       </c>
-      <c r="D41">
+      <c r="D40">
         <v>995</v>
       </c>
-      <c r="E41" s="21">
+      <c r="E40" s="21">
         <f>AVERAGE(58000,74999)</f>
         <v>66499.5</v>
       </c>
-      <c r="F41" s="21">
-        <f>F40*(1-A3)</f>
+      <c r="F40" s="21">
+        <f>F39*(1-A2)</f>
         <v>56623.481735022717</v>
       </c>
-      <c r="G41" s="21">
-        <f>F41*$A$4</f>
+      <c r="G40" s="21">
+        <f>F40*$A$3</f>
         <v>15099595.129339391</v>
       </c>
-      <c r="H41" s="55">
-        <f>E41*About!$A$149/G41</f>
+      <c r="H40" s="55">
+        <f>E40*About!$A$150/G40</f>
         <v>3.7315769386037706E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F42" t="s">
-        <v>444</v>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="24" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
-        <v>423</v>
+      <c r="C54" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C55" t="s">
-        <v>426</v>
+      <c r="B55" t="s">
+        <v>407</v>
+      </c>
+      <c r="C55" s="19">
+        <v>0.54</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="C56" s="19">
-        <v>0.54</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>434</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B57" t="s">
-        <v>425</v>
-      </c>
-      <c r="C57" s="19">
-        <v>0.52</v>
-      </c>
+      <c r="C57" s="19"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C58" s="19"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="24" t="s">
-        <v>427</v>
+      <c r="A58" s="24" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C81" t="s">
+        <v>413</v>
+      </c>
+      <c r="D81" t="s">
+        <v>414</v>
+      </c>
+      <c r="E81" t="s">
+        <v>415</v>
+      </c>
+      <c r="F81" t="s">
+        <v>416</v>
+      </c>
+      <c r="G81" t="s">
+        <v>430</v>
+      </c>
+      <c r="H81" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C82" t="s">
-        <v>430</v>
-      </c>
-      <c r="D82" t="s">
-        <v>431</v>
-      </c>
-      <c r="E82" t="s">
-        <v>432</v>
-      </c>
-      <c r="F82" t="s">
-        <v>433</v>
-      </c>
-      <c r="G82" t="s">
-        <v>447</v>
-      </c>
-      <c r="H82" t="s">
-        <v>145</v>
+      <c r="B82" t="s">
+        <v>411</v>
+      </c>
+      <c r="C82">
+        <v>28398</v>
+      </c>
+      <c r="D82">
+        <v>250</v>
+      </c>
+      <c r="G82" s="21">
+        <f>G83*(1-A2)</f>
+        <v>11801531.10292552</v>
+      </c>
+      <c r="H82" s="55">
+        <f>C82*About!$A$150/G82</f>
+        <v>2.0388661829358595E-3</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="C83">
-        <v>28398</v>
+        <v>25345</v>
       </c>
       <c r="D83">
         <v>250</v>
       </c>
-      <c r="G83" s="21">
-        <f>G84*(1-A3)</f>
-        <v>11801531.10292552</v>
-      </c>
-      <c r="H83" s="55">
-        <f>C83*About!$A$149/G83</f>
-        <v>2.0388661829358595E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B84" t="s">
-        <v>429</v>
-      </c>
-      <c r="C84">
-        <v>25345</v>
-      </c>
-      <c r="D84">
-        <v>250</v>
-      </c>
-      <c r="E84">
+      <c r="E83">
         <f>AVERAGE(144,228.1)</f>
         <v>186.05</v>
       </c>
-      <c r="G84" s="21">
-        <f>E84*About!A143*A4/D84</f>
+      <c r="G83" s="21">
+        <f>E83*About!A144*A3/D83</f>
         <v>27483802.133333337</v>
       </c>
-      <c r="H84" s="55">
-        <f>C84*About!$A$149/G84</f>
+      <c r="H83" s="55">
+        <f>C83*About!$A$150/G83</f>
         <v>7.8136653221209343E-4</v>
       </c>
     </row>

--- a/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
+++ b/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code Repositories\eps-us\InputData\indst\IECCpUAEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7C46AE-AD16-41EE-AF51-56BA6F443605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048DA2A3-2C9E-4B97-876D-4CA04A490527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27690" yWindow="750" windowWidth="23940" windowHeight="21210" tabRatio="762" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
+    <workbookView xWindow="14145" yWindow="1035" windowWidth="33990" windowHeight="22305" tabRatio="762" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -123,9 +123,6 @@
     <t>other processes</t>
   </si>
   <si>
-    <t>Annual heat delivered (MMbtu)</t>
-  </si>
-  <si>
     <t>Capital Cost (USD)</t>
   </si>
   <si>
@@ -147,9 +144,6 @@
     <t>BTU</t>
   </si>
   <si>
-    <t>Capital cost per BTU</t>
-  </si>
-  <si>
     <t>$/(BTU/yr)</t>
   </si>
   <si>
@@ -246,9 +240,6 @@
     <t>50% more than a natural gas boiler.</t>
   </si>
   <si>
-    <t>Cost per annual energy ($/(BTU/yr))</t>
-  </si>
-  <si>
     <t>For electricity in the "boilers" end use, we use industrial heat pumps rather than electric boilers because industrial heat pumps</t>
   </si>
   <si>
@@ -534,12 +525,6 @@
     <t>Average total operating capacity (first 3 years)</t>
   </si>
   <si>
-    <t xml:space="preserve">Yield in kWh/year: </t>
-  </si>
-  <si>
-    <t>Yield in BTU/year</t>
-  </si>
-  <si>
     <t>DOE projected capex cost reduction by 2030:</t>
   </si>
   <si>
@@ -606,12 +591,6 @@
     <t>kWh/year</t>
   </si>
   <si>
-    <t>Annual heat delivered/year (mmBTU):</t>
-  </si>
-  <si>
-    <t>Annual energy expenditure/year (kWh):</t>
-  </si>
-  <si>
     <t>mmBTU/year</t>
   </si>
   <si>
@@ -844,9 +823,6 @@
   </si>
   <si>
     <t>Electric example (Infrared Heater for Processed Foods)</t>
-  </si>
-  <si>
-    <t>Energy expenditure:</t>
   </si>
   <si>
     <t>USD</t>
@@ -1192,9 +1168,6 @@
     </r>
   </si>
   <si>
-    <t>Annual energy delivered (MMbtu)</t>
-  </si>
-  <si>
     <t xml:space="preserve">% Distr. by Energy Use of Motor HP Category </t>
   </si>
   <si>
@@ -1231,9 +1204,6 @@
     <t>% Distr. by Energy Use Per HP Bin</t>
   </si>
   <si>
-    <t>Average Annual Energy Delivered by HP Bin (MMbtu)</t>
-  </si>
-  <si>
     <t>electrified industrial heating equipment. So we do not consider them to be an outlier - i.e., the higher cost is justified.</t>
   </si>
   <si>
@@ -1439,6 +1409,36 @@
   </si>
   <si>
     <t>Does not need to be converted using heat pump COP because it is already based on electricity consumption</t>
+  </si>
+  <si>
+    <t>Cost per annual energy input ($/(BTU/yr))</t>
+  </si>
+  <si>
+    <t>Capital cost per BTU energy consumption</t>
+  </si>
+  <si>
+    <t>Annual energy consumption/year (kWh):</t>
+  </si>
+  <si>
+    <t>Annual energy consumption/year (mmBTU):</t>
+  </si>
+  <si>
+    <t>Annual energy consumed (MMbtu)</t>
+  </si>
+  <si>
+    <t>Annual energy use (MMbtu)</t>
+  </si>
+  <si>
+    <t>Average Annual Energy Use by HP Bin (MMbtu)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy use in kWh/year: </t>
+  </si>
+  <si>
+    <t>Energy use in BTU/year</t>
+  </si>
+  <si>
+    <t>Capacity:</t>
   </si>
 </sst>
 </file>
@@ -1695,7 +1695,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1786,33 +1786,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="8" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="11" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="11" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1825,7 +1798,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="11" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="11" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3758,7 +3752,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>675943</xdr:colOff>
+      <xdr:colOff>523543</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>88899</xdr:rowOff>
     </xdr:to>
@@ -3846,7 +3840,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>610454</xdr:colOff>
+      <xdr:colOff>458054</xdr:colOff>
       <xdr:row>79</xdr:row>
       <xdr:rowOff>76742</xdr:rowOff>
     </xdr:to>
@@ -3890,7 +3884,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>320866</xdr:colOff>
+      <xdr:colOff>168466</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>38159</xdr:rowOff>
     </xdr:to>
@@ -4308,7 +4302,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4316,52 +4310,51 @@
         <v>0</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
-      <c r="B4" s="69" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67"/>
-      <c r="B5" s="70">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="13">
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67"/>
-      <c r="B6" s="69" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="71" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="67"/>
-      <c r="B8" s="69" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="67"/>
-      <c r="B9" s="69"/>
-    </row>
-    <row r="10" spans="1:2" s="68" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="67"/>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="58" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
       <c r="B10" s="16" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4371,27 +4364,27 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
@@ -4401,27 +4394,27 @@
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
@@ -4431,27 +4424,27 @@
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -4461,67 +4454,67 @@
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="16" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="16" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" s="16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
@@ -4531,22 +4524,22 @@
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B54" s="16" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.25">
@@ -4556,32 +4549,32 @@
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="16" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.25">
@@ -4591,12 +4584,12 @@
     </row>
     <row r="65" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" s="35" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.25">
@@ -4604,12 +4597,12 @@
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
@@ -4619,17 +4612,17 @@
     </row>
     <row r="71" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B71" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B73" s="35" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
@@ -4637,12 +4630,12 @@
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.25">
@@ -4652,12 +4645,12 @@
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B78" s="36" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B79" s="37" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.25">
@@ -4665,12 +4658,12 @@
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.25">
@@ -4680,7 +4673,7 @@
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.25">
@@ -4688,7 +4681,7 @@
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.25">
@@ -4698,22 +4691,22 @@
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.25">
@@ -4723,27 +4716,27 @@
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="31" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="36" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.25">
@@ -4753,12 +4746,12 @@
     </row>
     <row r="102" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B102" s="36" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103" spans="2:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B103" s="37" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.25">
@@ -4766,32 +4759,32 @@
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B105" s="16" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.25">
@@ -4801,52 +4794,52 @@
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B135" s="16" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -4854,12 +4847,12 @@
         <v>138490</v>
       </c>
       <c r="B144" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -4867,7 +4860,7 @@
         <v>3412.14</v>
       </c>
       <c r="B146" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -4875,7 +4868,7 @@
         <v>0.78452102304761584</v>
       </c>
       <c r="B149" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -4883,7 +4876,7 @@
         <v>0.84730412960844359</v>
       </c>
       <c r="B150" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -4925,7 +4918,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -4958,10 +4951,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -5378,32 +5371,32 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -5429,7 +5422,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5535,7 +5528,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B12" s="10">
         <f>B11</f>
@@ -5544,7 +5537,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B13" s="10">
         <f>B12</f>
@@ -5567,13 +5560,13 @@
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5581,80 +5574,80 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="72" t="s">
-        <v>440</v>
-      </c>
-      <c r="B5" s="73" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="74" t="s">
+      <c r="A5" s="59" t="s">
+        <v>430</v>
+      </c>
+      <c r="B5" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="77"/>
+      <c r="C5" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="64"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B6">
         <v>600</v>
       </c>
-      <c r="C6" s="75" t="s">
-        <v>147</v>
+      <c r="C6" s="62" t="s">
+        <v>144</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="B7">
         <v>8760</v>
       </c>
-      <c r="C7" s="75" t="s">
-        <v>443</v>
-      </c>
-      <c r="D7" s="75"/>
+      <c r="C7" s="62" t="s">
+        <v>433</v>
+      </c>
+      <c r="D7" s="62"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="B8" s="19">
         <v>0.65</v>
       </c>
-      <c r="C8" s="75" t="s">
-        <v>154</v>
-      </c>
-      <c r="D8" s="75"/>
+      <c r="C8" s="62" t="s">
+        <v>151</v>
+      </c>
+      <c r="D8" s="62"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>445</v>
-      </c>
-      <c r="B9" s="76">
+        <v>435</v>
+      </c>
+      <c r="B9" s="63">
         <f>B6/(B7*B8)</f>
         <v>0.10537407797681771</v>
       </c>
-      <c r="C9" s="75" t="s">
-        <v>296</v>
+      <c r="C9" s="62" t="s">
+        <v>288</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5662,13 +5655,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>3412.14</v>
       </c>
-      <c r="C11" s="75" t="s">
-        <v>41</v>
+      <c r="C11" s="62" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5676,28 +5669,28 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="B13" s="12">
         <f>B9/B11</f>
         <v>3.0882108581950831E-5</v>
       </c>
-      <c r="C13" s="75" t="s">
-        <v>28</v>
+      <c r="C13" s="62" t="s">
+        <v>26</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="24" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -5706,12 +5699,12 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B20" s="8">
         <v>80375</v>
@@ -5719,7 +5712,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B21" s="8">
         <v>91475</v>
@@ -5727,7 +5720,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B22" s="8">
         <f>AVERAGE(B20:B21)</f>
@@ -5736,7 +5729,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B24">
         <v>400</v>
@@ -5744,7 +5737,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B25">
         <v>0.74570000000000003</v>
@@ -5752,7 +5745,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B26">
         <f>B24*B25</f>
@@ -5761,7 +5754,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B28" s="22">
         <v>5280</v>
@@ -5769,42 +5762,42 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B30">
         <f>B26*B28</f>
         <v>1574918.4000000001</v>
       </c>
       <c r="C30" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <v>3412.14</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B32">
         <f>B30*B31</f>
         <v>5373842069.3760004</v>
       </c>
       <c r="C32" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>442</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5813,12 +5806,12 @@
         <v>1.5989491110961776E-5</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
@@ -5827,27 +5820,27 @@
     </row>
     <row r="38" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F38" s="23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>60</v>
+        <v>441</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B39">
         <v>2000</v>
@@ -5873,7 +5866,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B40">
         <v>2000</v>
@@ -5899,7 +5892,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B41">
         <v>2000</v>
@@ -5925,60 +5918,60 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B44">
         <f>B39*B28</f>
         <v>10560000</v>
       </c>
       <c r="C44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B45">
         <v>3412.14</v>
       </c>
       <c r="C45" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <f>B44*B45</f>
         <v>36032198400</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -5986,13 +5979,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B53" s="8"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B54" s="20"/>
     </row>
@@ -6002,7 +5995,7 @@
         <v>2.3984236666442662E-5</v>
       </c>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -6021,330 +6014,330 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B5" s="8">
         <v>307500</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B6">
         <v>4000</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B8" s="8">
         <v>75863</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B9" s="8">
         <v>6226</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B11" s="25">
         <v>0.45</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B12" s="25">
         <v>0.15</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B14" s="21">
         <f>B8/B11</f>
         <v>168584.44444444444</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B15" s="21">
         <f>B9/B12</f>
         <v>41506.666666666672</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>100000</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18">
         <v>3412.14</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B20" s="9">
         <f>B14*B17</f>
         <v>16858444444.444445</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B21" s="9">
         <f>B15*B18</f>
         <v>141626557.60000002</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B26" s="9">
         <f>SUM(B20:B21)</f>
         <v>17000071002.044445</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B27" s="12">
         <f>B5/B26</f>
         <v>1.8088159747275158E-5</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B32" s="8">
         <v>200</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B33" s="8">
         <v>500</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B34" s="8">
         <f>AVERAGE(B32:B33)</f>
         <v>350</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B36">
         <v>500</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D36" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B38" s="8">
         <f>B34*B36</f>
         <v>175000</v>
       </c>
       <c r="C38" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B41">
         <v>0.57599999999999996</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B42">
         <f>B41*B36</f>
         <v>288</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B44">
         <f>B6</f>
         <v>4000</v>
       </c>
       <c r="C44" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D44" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B46">
         <f>B42*B44</f>
         <v>1152000</v>
       </c>
       <c r="C46" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B47" s="9">
         <f>B46*B18</f>
         <v>3930785280</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B49" s="12">
         <f>B38/B47</f>
         <v>4.4520366169683022E-5</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -6368,7 +6361,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6376,25 +6369,25 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B3" s="42"/>
       <c r="C3" s="11" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B5">
         <v>492000</v>
@@ -6403,7 +6396,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B6">
         <v>135000</v>
@@ -6412,7 +6405,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B7">
         <v>474000</v>
@@ -6421,7 +6414,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="B8">
         <v>70000</v>
@@ -6430,7 +6423,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B9">
         <v>22000</v>
@@ -6439,7 +6432,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="B10">
         <v>18000</v>
@@ -6448,7 +6441,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B11">
         <v>216000</v>
@@ -6457,7 +6450,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B12">
         <v>51000</v>
@@ -6466,7 +6459,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B13">
         <v>125000</v>
@@ -6475,24 +6468,24 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="11" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B17" s="20">
         <v>13400</v>
@@ -6500,7 +6493,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B18" s="20">
         <v>5300</v>
@@ -6508,7 +6501,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B19" s="20">
         <v>13600</v>
@@ -6516,32 +6509,32 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="11" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B23">
         <v>4380</v>
@@ -6552,7 +6545,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B24">
         <v>4380</v>
@@ -6563,7 +6556,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="40"/>
@@ -6571,32 +6564,32 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B33" s="1">
         <f>'Boilers &amp; Heat Pumps'!B28</f>
@@ -6605,13 +6598,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" s="46">
         <v>3412.14</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -6619,7 +6612,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="45" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B38" s="44"/>
       <c r="C38" s="44"/>
@@ -6627,21 +6620,21 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B40">
         <f>$B$33*D23*B36</f>
@@ -6658,7 +6651,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B41">
         <f>$B$33*C24</f>
@@ -6675,33 +6668,33 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B51" s="42"/>
       <c r="C51" s="42"/>
       <c r="D51" s="11" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="B53">
         <v>722000</v>
@@ -6713,7 +6706,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B54">
         <v>882000</v>
@@ -6741,7 +6734,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6752,12 +6745,12 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I2" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C3" s="25"/>
       <c r="F3" s="25">
@@ -6765,107 +6758,107 @@
         <v>264.16000000000003</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F4">
         <v>450</v>
       </c>
       <c r="G4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C5" s="32"/>
       <c r="F5" s="32">
         <v>800000</v>
       </c>
       <c r="G5" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>443</v>
       </c>
       <c r="F7">
         <f>F4*F5</f>
         <v>360000000</v>
       </c>
       <c r="G7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>180</v>
+        <v>444</v>
       </c>
       <c r="F8">
         <f>F7*0.003412</f>
         <v>1228320</v>
       </c>
       <c r="G8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F9" s="25">
         <f>F3*F5</f>
         <v>211328000.00000003</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F10" s="12">
         <f>F9/(F8*10^6)</f>
         <v>1.7204637228083889E-4</v>
       </c>
       <c r="G10" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E12">
         <f>8760*155</f>
         <v>1357800</v>
       </c>
       <c r="F12" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -6876,13 +6869,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="F16" s="20">
         <v>170</v>
       </c>
       <c r="G16" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -6891,7 +6884,7 @@
         <v>26.356589147286826</v>
       </c>
       <c r="G17" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -6900,7 +6893,7 @@
         <v>9.4883645023316546E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -6909,80 +6902,80 @@
         <v>2.7808805692648461E-5</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F21">
         <v>36000000</v>
       </c>
       <c r="G21" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F22" s="20">
         <f>F21*0.14</f>
         <v>5040000.0000000009</v>
       </c>
       <c r="G22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="F23">
         <f>AVERAGE(5.1,7.8)</f>
         <v>6.4499999999999993</v>
       </c>
       <c r="G23" t="s">
+        <v>218</v>
+      </c>
+      <c r="I23" t="s">
         <v>225</v>
-      </c>
-      <c r="I23" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F24">
         <v>8000</v>
       </c>
       <c r="G24" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F25">
         <v>600</v>
       </c>
       <c r="G25" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -6991,7 +6984,7 @@
         <v>3869.9999999999995</v>
       </c>
       <c r="G26" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="I26" s="15"/>
     </row>
@@ -7001,95 +6994,95 @@
         <v>1289999.9999999998</v>
       </c>
       <c r="G27" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="I27" s="15"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>181</v>
+        <v>443</v>
       </c>
       <c r="F28">
         <f>F27*277.778</f>
         <v>358333619.99999994</v>
       </c>
       <c r="G28" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I28" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>180</v>
+        <v>444</v>
       </c>
       <c r="F29">
         <f>F28*0.003412</f>
         <v>1222634.3114399998</v>
       </c>
       <c r="G29" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F30" s="12">
         <f>(F21*0.14)/(F29*10^6)</f>
         <v>4.1222464909102436E-6</v>
       </c>
       <c r="G30" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="I30" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F34">
         <v>21.08</v>
       </c>
       <c r="G34" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="F35">
         <v>0.76</v>
       </c>
       <c r="G35" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="F36" s="34">
         <f>F34*F35</f>
         <v>16.020799999999998</v>
       </c>
       <c r="G36" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -7097,7 +7090,7 @@
         <v>1.3284</v>
       </c>
       <c r="G37" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -7106,7 +7099,7 @@
         <v>21.282030719999998</v>
       </c>
       <c r="G38" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -7114,7 +7107,7 @@
         <v>1.32</v>
       </c>
       <c r="G39" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -7123,7 +7116,7 @@
         <v>28.092280550399998</v>
       </c>
       <c r="G40" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -7132,7 +7125,7 @@
         <v>4.3553923333953488</v>
       </c>
       <c r="G41" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -7140,7 +7133,7 @@
         <v>277.77800000000002</v>
       </c>
       <c r="G42" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -7149,7 +7142,7 @@
         <v>1.5679399856703368E-2</v>
       </c>
       <c r="G43" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -7157,7 +7150,7 @@
         <v>3412.14</v>
       </c>
       <c r="G44" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -7166,12 +7159,12 @@
         <v>4.5951806950193628E-6</v>
       </c>
       <c r="G45" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -7182,99 +7175,99 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F49" s="32">
         <v>6000000</v>
       </c>
       <c r="G49" s="33" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F50">
         <v>300</v>
       </c>
       <c r="G50" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F51">
         <v>8760</v>
       </c>
       <c r="G51" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="F52">
         <v>1100</v>
       </c>
       <c r="G52" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>181</v>
+        <v>443</v>
       </c>
       <c r="F54">
         <f>(F3*365)*F52</f>
         <v>106060240.00000001</v>
       </c>
       <c r="G54" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>444</v>
       </c>
       <c r="F55" s="34">
         <f>F54*0.003412</f>
         <v>361877.53888000007</v>
       </c>
       <c r="G55" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F56" s="12">
         <f>(F49*1.25)/(F55*10^6)</f>
         <v>2.0725243194734525E-5</v>
       </c>
       <c r="G56" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
@@ -7285,90 +7278,90 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F60">
         <f>574-184</f>
         <v>390</v>
       </c>
       <c r="G60" s="33" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F61">
         <v>3500</v>
       </c>
       <c r="G61" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F62" s="32">
         <v>1500000</v>
       </c>
       <c r="G62" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="I62" s="15" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>181</v>
+        <v>443</v>
       </c>
       <c r="F64">
         <f>F61*F62</f>
         <v>5250000000</v>
       </c>
       <c r="G64" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>180</v>
+        <v>444</v>
       </c>
       <c r="F65">
         <f>F64*0.003412</f>
         <v>17913000</v>
       </c>
       <c r="G65" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F66" s="25">
         <f>F60*F62</f>
         <v>585000000</v>
       </c>
       <c r="G66" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F67" s="12">
         <f>F66/(F65*10^6)</f>
         <v>3.265784625690839E-5</v>
       </c>
       <c r="G67" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -7408,96 +7401,96 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="F8" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="G8" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="H8" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="I8" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="G8" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>125</v>
-      </c>
       <c r="J8" s="30" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K8" s="27"/>
       <c r="L8" s="29" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="M8" s="27"/>
       <c r="N8" s="28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O8" s="27"/>
       <c r="P8" s="29" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="Q8" s="27"/>
       <c r="R8" s="29" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="S8" s="27"/>
       <c r="T8" s="29" t="s">
-        <v>368</v>
+        <v>446</v>
       </c>
       <c r="U8" s="27"/>
       <c r="V8" s="27"/>
       <c r="W8" s="29" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D9">
         <v>0.3</v>
@@ -7547,10 +7540,10 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -7600,10 +7593,10 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D11">
         <v>350</v>
@@ -7653,10 +7646,10 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D12">
         <v>500</v>
@@ -7706,10 +7699,10 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D13">
         <v>0.35</v>
@@ -7759,10 +7752,10 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D14">
         <v>1.8</v>
@@ -7812,10 +7805,10 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D15">
         <v>0.35</v>
@@ -7865,10 +7858,10 @@
     </row>
     <row r="16" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -7918,10 +7911,10 @@
     </row>
     <row r="17" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D17">
         <v>50</v>
@@ -7971,10 +7964,10 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -8024,10 +8017,10 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D19">
         <v>180</v>
@@ -8080,7 +8073,7 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N21" s="21"/>
       <c r="P21" s="21"/>
@@ -8096,7 +8089,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="N22" s="21"/>
       <c r="P22" s="21"/>
@@ -8114,49 +8107,49 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C23" s="49" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="49" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="G23" s="49"/>
       <c r="H23" s="49"/>
       <c r="I23" s="49" t="s">
-        <v>381</v>
+        <v>447</v>
       </c>
       <c r="J23" s="49"/>
       <c r="K23" s="49"/>
       <c r="L23" s="49"/>
       <c r="M23" s="49"/>
       <c r="N23" s="50" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
       <c r="T23" s="21"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C24" s="61" t="s">
-        <v>374</v>
-      </c>
-      <c r="D24" s="62"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="64">
+      <c r="C24" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="D24" s="69"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="65">
         <f>0.048/0.581</f>
         <v>8.2616179001721177E-2</v>
       </c>
-      <c r="G24" s="65"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="58">
+      <c r="G24" s="66"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="71">
         <f>((T13+T15)/2)</f>
         <v>23.414850000000001</v>
       </c>
-      <c r="J24" s="59"/>
-      <c r="K24" s="59"/>
-      <c r="L24" s="59"/>
-      <c r="M24" s="60"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="73"/>
       <c r="N24" s="51">
         <f>((W13+W15)/2)</f>
         <v>2.2407199119595664E-4</v>
@@ -8166,25 +8159,25 @@
       <c r="T24" s="21"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C25" s="61" t="s">
-        <v>375</v>
-      </c>
-      <c r="D25" s="62"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="64">
+      <c r="C25" s="68" t="s">
+        <v>366</v>
+      </c>
+      <c r="D25" s="69"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="65">
         <f>0.104/0.581</f>
         <v>0.17900172117039587</v>
       </c>
-      <c r="G25" s="65"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="58">
+      <c r="G25" s="66"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="71">
         <f>T14</f>
         <v>97.18877280000001</v>
       </c>
-      <c r="J25" s="59"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="59"/>
-      <c r="M25" s="60"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="73"/>
       <c r="N25" s="51">
         <f>W14</f>
         <v>3.3521233224690123E-5</v>
@@ -8194,25 +8187,25 @@
       <c r="T25" s="21"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C26" s="61" t="s">
-        <v>373</v>
-      </c>
-      <c r="D26" s="62"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="64">
+      <c r="C26" s="68" t="s">
+        <v>364</v>
+      </c>
+      <c r="D26" s="69"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="65">
         <f>0.127/0.581</f>
         <v>0.21858864027538727</v>
       </c>
-      <c r="G26" s="65"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="58">
+      <c r="G26" s="66"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="71">
         <f>T16</f>
         <v>319.17554000000001</v>
       </c>
-      <c r="J26" s="59"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="59"/>
-      <c r="M26" s="60"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="73"/>
       <c r="N26" s="51">
         <f>W16</f>
         <v>1.1301491868138288E-5</v>
@@ -8222,25 +8215,25 @@
       <c r="T26" s="21"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C27" s="61" t="s">
-        <v>372</v>
-      </c>
-      <c r="D27" s="62"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="64">
+      <c r="C27" s="68" t="s">
+        <v>363</v>
+      </c>
+      <c r="D27" s="69"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="65">
         <f>0.144/0.581</f>
         <v>0.24784853700516352</v>
       </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="58">
+      <c r="G27" s="66"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="71">
         <f>((T10+T18)/2)</f>
         <v>1214.1039020000001</v>
       </c>
-      <c r="J27" s="59"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="59"/>
-      <c r="M27" s="60"/>
+      <c r="J27" s="72"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="72"/>
+      <c r="M27" s="73"/>
       <c r="N27" s="51">
         <f>((W10+W18)/2)</f>
         <v>5.481183696812177E-6</v>
@@ -8250,25 +8243,25 @@
       <c r="T27" s="21"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C28" s="61" t="s">
-        <v>376</v>
-      </c>
-      <c r="D28" s="62"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64">
+      <c r="C28" s="68" t="s">
+        <v>367</v>
+      </c>
+      <c r="D28" s="69"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="65">
         <f>0.157/0.581</f>
         <v>0.27022375215146299</v>
       </c>
-      <c r="G28" s="65"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="58">
+      <c r="G28" s="66"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="71">
         <f>((T9+T11+T12+T17+T19)/5)</f>
         <v>49678.416604960003</v>
       </c>
-      <c r="J28" s="59"/>
-      <c r="K28" s="59"/>
-      <c r="L28" s="59"/>
-      <c r="M28" s="60"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="73"/>
       <c r="N28" s="51">
         <f>((W9+W11+W12+W17+W19)/5)</f>
         <v>4.8514850079979492E-6</v>
@@ -8287,116 +8280,116 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="G32" s="1" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="U32" s="9"/>
       <c r="W32" s="9"/>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D33" s="21">
         <v>502</v>
       </c>
       <c r="E33" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="T33" s="9"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D34" s="21">
         <v>250</v>
       </c>
       <c r="E34" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="T34" s="9"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D35" s="21">
         <f>D34/1.341</f>
         <v>186.42803877703207</v>
       </c>
       <c r="E35" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D36" s="21">
         <v>2080</v>
       </c>
       <c r="E36" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>19</v>
+        <v>445</v>
       </c>
       <c r="D37" s="21">
         <f>D35*0.003412*D36</f>
         <v>1323.0723340790455</v>
       </c>
       <c r="E37" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D38" s="12">
         <f>(D33*D35)/(D37*10^6)</f>
         <v>7.0734511678239686E-5</v>
       </c>
       <c r="E38" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="I24:M24"/>
+    <mergeCell ref="I25:M25"/>
+    <mergeCell ref="I26:M26"/>
+    <mergeCell ref="I27:M27"/>
+    <mergeCell ref="I28:M28"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="F26:H26"/>
     <mergeCell ref="F27:H27"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="I24:M24"/>
-    <mergeCell ref="I25:M25"/>
-    <mergeCell ref="I26:M26"/>
-    <mergeCell ref="I27:M27"/>
-    <mergeCell ref="I28:M28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G33" r:id="rId1" xr:uid="{89D540DE-65F8-419E-8E02-FD08F0D4350B}"/>
@@ -8419,7 +8412,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -8430,12 +8423,12 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -8443,94 +8436,94 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G5" s="1"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D6">
         <f>AVERAGE(760,1000)</f>
         <v>880</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D7">
         <f>AVERAGE(373.1,597)</f>
         <v>485.05</v>
       </c>
       <c r="E7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D11">
         <f>AVERAGE(975,1200)</f>
         <v>1087.5</v>
       </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D12">
         <f>AVERAGE(1492.5,2238.8)</f>
         <v>1865.65</v>
       </c>
       <c r="E12" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D15">
         <v>1.5</v>
       </c>
       <c r="E15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D16">
         <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G18">
         <f>(D6)*(1.5*1000000)</f>
@@ -8539,7 +8532,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>156</v>
+        <v>448</v>
       </c>
       <c r="G19">
         <f>(1.5*1000000)*(0.7*8760)</f>
@@ -8548,7 +8541,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>157</v>
+        <v>449</v>
       </c>
       <c r="G20">
         <f>G19*3412</f>
@@ -8557,7 +8550,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G21">
         <f>G18/G20</f>
@@ -8566,7 +8559,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G22">
         <f>(D7*(1.5*1000000))/G20</f>
@@ -8575,7 +8568,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G24">
         <f>(D11)*(1.5*1000000)</f>
@@ -8584,7 +8577,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>156</v>
+        <v>448</v>
       </c>
       <c r="G25">
         <f>(1.5*1000000)*(0.7*8760)</f>
@@ -8593,7 +8586,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>157</v>
+        <v>449</v>
       </c>
       <c r="G26">
         <f>G25*3412</f>
@@ -8602,7 +8595,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G27">
         <f>G24/G26</f>
@@ -8611,7 +8604,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G28">
         <f>(D12*(1.5*1000000))/G26</f>
@@ -8620,12 +8613,12 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G32" s="12">
         <f>(G21*0.75)+(G27*0.25)</f>
@@ -8634,7 +8627,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G33" s="9">
         <f>G32*0.6</f>
@@ -8646,7 +8639,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G35" s="9">
         <f>(G22*0.75)+(G28*0.25)</f>
@@ -8671,7 +8664,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -8683,184 +8676,184 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E3" s="39">
         <f>2758*1.03</f>
         <v>2840.7400000000002</v>
       </c>
       <c r="F3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>260</v>
+        <v>450</v>
       </c>
       <c r="E4">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <f>18*365</f>
         <v>6570</v>
       </c>
       <c r="F5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H5" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>181</v>
+        <v>443</v>
       </c>
       <c r="E7">
         <f>E4*E5</f>
         <v>118260</v>
       </c>
       <c r="F7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>180</v>
+        <v>444</v>
       </c>
       <c r="E8">
         <f>E7*0.003412</f>
         <v>403.50312000000002</v>
       </c>
       <c r="F8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E9" s="12">
         <f>E3/(E8*10^6)</f>
         <v>7.0401933942914745E-6</v>
       </c>
       <c r="F9" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B16" s="8">
         <v>862500</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B17" s="8">
         <v>1500000</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B18" s="8">
         <f>AVERAGE(B16,B17)</f>
         <v>1181250</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B20" s="32">
         <v>8760</v>
       </c>
       <c r="C20" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B21" s="32">
         <v>6051100</v>
       </c>
       <c r="C21" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B23">
         <f>B20*B21</f>
         <v>53007636000</v>
       </c>
       <c r="C23" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B24" s="12">
         <f>B18/B23</f>
         <v>2.2284525195577483E-5</v>
       </c>
       <c r="C24" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -8876,6 +8869,7 @@
   <dimension ref="A1:P83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
@@ -8886,7 +8880,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
@@ -8909,7 +8903,7 @@
         <v>0.57060049240377109</v>
       </c>
       <c r="B2" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -8918,7 +8912,7 @@
         <v>266.66666666666669</v>
       </c>
       <c r="B3" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -8930,7 +8924,7 @@
         <v>8.2719018162705823E-4</v>
       </c>
       <c r="B5" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -8939,7 +8933,7 @@
         <v>3.1381977460259781E-3</v>
       </c>
       <c r="B6" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -8947,44 +8941,44 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D28" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="E28" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="F28" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="G28" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="H28" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="I28" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="M28" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="N28" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="O28" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C29">
         <v>17000</v>
@@ -9007,7 +9001,7 @@
         <v>250</v>
       </c>
       <c r="L29" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="M29">
         <f>AVERAGE(C29:C31)*About!A149</f>
@@ -9024,7 +9018,7 @@
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C30">
         <v>17000</v>
@@ -9047,7 +9041,7 @@
         <v>250</v>
       </c>
       <c r="L30" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="M30">
         <f>C32*About!A149</f>
@@ -9064,7 +9058,7 @@
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C31">
         <v>50000</v>
@@ -9089,7 +9083,7 @@
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C32">
         <v>55000</v>
@@ -9124,32 +9118,32 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="D38" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
+        <v>408</v>
+      </c>
+      <c r="F38" t="s">
+        <v>416</v>
+      </c>
+      <c r="G38" t="s">
         <v>418</v>
       </c>
-      <c r="F38" t="s">
-        <v>426</v>
-      </c>
-      <c r="G38" t="s">
-        <v>428</v>
-      </c>
       <c r="H38" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C39">
         <v>2940</v>
@@ -9176,7 +9170,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C40">
         <v>113</v>
@@ -9203,33 +9197,33 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F41" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="24" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C55" s="19">
         <v>0.54</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C56" s="19">
         <v>0.52</v>
@@ -9240,32 +9234,32 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C81" t="s">
-        <v>413</v>
-      </c>
-      <c r="D81" t="s">
-        <v>414</v>
-      </c>
-      <c r="E81" t="s">
-        <v>415</v>
-      </c>
-      <c r="F81" t="s">
-        <v>416</v>
-      </c>
-      <c r="G81" t="s">
-        <v>430</v>
-      </c>
-      <c r="H81" t="s">
-        <v>128</v>
+      <c r="C81" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>411</v>
+      <c r="B82" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="C82">
         <v>28398</v>
@@ -9283,8 +9277,8 @@
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>412</v>
+      <c r="B83" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="C83">
         <v>25345</v>
@@ -9307,7 +9301,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
+++ b/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code Repositories\eps-us\InputData\indst\IECCpUAEU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\IECCpUAEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048DA2A3-2C9E-4B97-876D-4CA04A490527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{B95E0DDC-D38A-4AEC-9FED-2EF80C57FCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14145" yWindow="1035" windowWidth="33990" windowHeight="22305" tabRatio="762" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
+    <workbookView xWindow="-28965" yWindow="-165" windowWidth="29130" windowHeight="17610" tabRatio="762" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <sheet name="NB High Temp" sheetId="7" r:id="rId5"/>
     <sheet name="Machine Drive" sheetId="5" r:id="rId6"/>
     <sheet name="Electrochemical" sheetId="6" r:id="rId7"/>
-    <sheet name="Other" sheetId="10" r:id="rId8"/>
-    <sheet name="Other (mobile)" sheetId="11" r:id="rId9"/>
-    <sheet name="IECCpUAEU" sheetId="2" r:id="rId10"/>
-    <sheet name="IECCpUAEU-mobile" sheetId="12" r:id="rId11"/>
+    <sheet name="Lighting" sheetId="13" r:id="rId8"/>
+    <sheet name="Other" sheetId="10" r:id="rId9"/>
+    <sheet name="Other (mobile)" sheetId="11" r:id="rId10"/>
+    <sheet name="Summary" sheetId="14" r:id="rId11"/>
+    <sheet name="IECCpUAEU" sheetId="2" r:id="rId12"/>
+    <sheet name="IECCpUAEU-mobile" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="516">
   <si>
     <t>Sources:</t>
   </si>
@@ -115,9 +118,6 @@
   </si>
   <si>
     <t>machine drive</t>
-  </si>
-  <si>
-    <t>electrochemical</t>
   </si>
   <si>
     <t>other processes</t>
@@ -1440,18 +1440,218 @@
   <si>
     <t>Capacity:</t>
   </si>
+  <si>
+    <t>facility HVAC</t>
+  </si>
+  <si>
+    <t>facility lighting</t>
+  </si>
+  <si>
+    <t>other nonprocess</t>
+  </si>
+  <si>
+    <t>https://www.bulkofficesupply.com/Categories/Janitorial-and-Facility-Supplies/Lighting/Light-Bulbs.aspx?srsltid=AfmBOorWkgJMp4H4zdZKPjbhWJ39KPaQWfcg1JIX1YpF1EunQjEtuY1Z</t>
+  </si>
+  <si>
+    <t>Satco A15 Appliance Light Bulb</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>lm</t>
+  </si>
+  <si>
+    <t>hr life</t>
+  </si>
+  <si>
+    <t>Satco 6.5W PAR 20/FL 3000K LED Bulb</t>
+  </si>
+  <si>
+    <t>Satco 7.5W BR30 3000K LED Bulb</t>
+  </si>
+  <si>
+    <t>Satco 12W PAR 30/LN/FL 3000K LED Bulb</t>
+  </si>
+  <si>
+    <t>Satco 15W PAR38 3000K LED Bulb</t>
+  </si>
+  <si>
+    <t>Satco 10W A19 LED 5000K Light Bulbs</t>
+  </si>
+  <si>
+    <t>W equiv. incandesc.</t>
+  </si>
+  <si>
+    <t>Satco 40W T8 4000K LED Tube Light</t>
+  </si>
+  <si>
+    <t>bulb</t>
+  </si>
+  <si>
+    <t>parabolic</t>
+  </si>
+  <si>
+    <t>reflector</t>
+  </si>
+  <si>
+    <t>tube</t>
+  </si>
+  <si>
+    <t>Satco 11 Watt LED T8 Bulb</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Satco 13W GX23 Pin-Based 2700K Compact Fluorescent Bulb</t>
+  </si>
+  <si>
+    <t>incand</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>fluorescent</t>
+  </si>
+  <si>
+    <t>twin tube</t>
+  </si>
+  <si>
+    <t>Satco 54W T5 3500K Fluorescent Tube</t>
+  </si>
+  <si>
+    <t>Satco Flourescent Light Bulbs 32W 6/box</t>
+  </si>
+  <si>
+    <t>CFL</t>
+  </si>
+  <si>
+    <t>Satco 23W T2 2700K Spiral CFL Bulb</t>
+  </si>
+  <si>
+    <t>https://www.mordorintelligence.com/industry-reports/industrial-lighting-market</t>
+  </si>
+  <si>
+    <t>Industrial lighting market</t>
+  </si>
+  <si>
+    <t>Fluorescent</t>
+  </si>
+  <si>
+    <t>HID fixtures</t>
+  </si>
+  <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>lightstoreusa.com</t>
+  </si>
+  <si>
+    <t>HID</t>
+  </si>
+  <si>
+    <t>Plusrite 1035</t>
+  </si>
+  <si>
+    <t>M47 BT37 Mogul</t>
+  </si>
+  <si>
+    <t>Plusrite 1056</t>
+  </si>
+  <si>
+    <t>floodlight</t>
+  </si>
+  <si>
+    <t>Plusrite 1061</t>
+  </si>
+  <si>
+    <t>PLUSRITE Par 38</t>
+  </si>
+  <si>
+    <t>hour life</t>
+  </si>
+  <si>
+    <t>years</t>
+  </si>
+  <si>
+    <t>assumed lighting lifetime (IESD)</t>
+  </si>
+  <si>
+    <t>hours/yr use</t>
+  </si>
+  <si>
+    <t>lifetime</t>
+  </si>
+  <si>
+    <t>BTU/yr</t>
+  </si>
+  <si>
+    <t>Lighting is generally electric. Other fuels can be used to power a generator to power lighting.</t>
+  </si>
+  <si>
+    <t>So we apply an efficiency loss for using a generator to power lighting.</t>
+  </si>
+  <si>
+    <t>generator efficiency</t>
+  </si>
+  <si>
+    <t>And must account for the cost of a generator:</t>
+  </si>
+  <si>
+    <t>Generac</t>
+  </si>
+  <si>
+    <t>Westinghouse Wgen 5300c</t>
+  </si>
+  <si>
+    <t>Westinghouse Wgen7500c</t>
+  </si>
+  <si>
+    <t>Westinghouse WGen9500c</t>
+  </si>
+  <si>
+    <t>WEN DF5600X</t>
+  </si>
+  <si>
+    <t>DuroMax XP13000HX</t>
+  </si>
+  <si>
+    <t>Firman Tri Fuel</t>
+  </si>
+  <si>
+    <t>avg watts</t>
+  </si>
+  <si>
+    <t>avg $</t>
+  </si>
+  <si>
+    <t>generator upfront cost per lightbulb powered</t>
+  </si>
+  <si>
+    <t>lightbulb contribution to cost</t>
+  </si>
+  <si>
+    <t>generator contribution to cost</t>
+  </si>
+  <si>
+    <t>total cost per BTU</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="175" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.000E+00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1531,7 +1731,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1600,6 +1800,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1695,7 +1901,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1822,6 +2028,16 @@
     <xf numFmtId="1" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1922,7 +2138,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>IECCpUAEU!$A$2</c:f>
+              <c:f>Summary!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1943,7 +2159,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
+              <c:f>Summary!$B$1:$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -1987,9 +2203,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$2:$M$2</c:f>
+              <c:f>Summary!$B$2:$M$2</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
+                <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>3.0882108581950831E-5</c:v>
@@ -2006,7 +2222,7 @@
                 <c:pt idx="4">
                   <c:v>9.436004881678272E-6</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="General">
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -2032,7 +2248,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AC6F-455C-AF10-DE9805C4FD60}"/>
+              <c16:uniqueId val="{00000000-89B1-4510-AEB3-F1F6A92C50C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2041,7 +2257,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>IECCpUAEU!$A$3</c:f>
+              <c:f>Summary!$A$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2062,7 +2278,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
+              <c:f>Summary!$B$1:$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2106,9 +2322,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$3:$M$3</c:f>
+              <c:f>Summary!$B$3:$M$3</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
+                <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>3.0882108581950831E-5</c:v>
@@ -2125,7 +2341,7 @@
                 <c:pt idx="4">
                   <c:v>9.436004881678272E-6</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="General">
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -2151,7 +2367,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AC6F-455C-AF10-DE9805C4FD60}"/>
+              <c16:uniqueId val="{00000001-89B1-4510-AEB3-F1F6A92C50C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2160,7 +2376,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>IECCpUAEU!$A$4</c:f>
+              <c:f>Summary!$A$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2181,7 +2397,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
+              <c:f>Summary!$B$1:$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2225,9 +2441,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$4:$M$4</c:f>
+              <c:f>Summary!$B$4:$M$4</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
+                <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>3.4771933032458345E-5</c:v>
@@ -2244,7 +2460,7 @@
                 <c:pt idx="4">
                   <c:v>3.1780367029653324E-5</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="General">
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -2270,7 +2486,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AC6F-455C-AF10-DE9805C4FD60}"/>
+              <c16:uniqueId val="{00000002-89B1-4510-AEB3-F1F6A92C50C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2279,7 +2495,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>IECCpUAEU!$A$5</c:f>
+              <c:f>Summary!$A$5</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2300,7 +2516,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
+              <c:f>Summary!$B$1:$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2344,9 +2560,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$5:$M$5</c:f>
+              <c:f>Summary!$B$5:$M$5</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
+                <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1.7204637228083889E-4</c:v>
@@ -2363,7 +2579,7 @@
                 <c:pt idx="4">
                   <c:v>1.2230751723262388E-5</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="General">
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -2389,7 +2605,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-AC6F-455C-AF10-DE9805C4FD60}"/>
+              <c16:uniqueId val="{00000003-89B1-4510-AEB3-F1F6A92C50C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2398,7 +2614,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>IECCpUAEU!$A$6</c:f>
+              <c:f>Summary!$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2419,7 +2635,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
+              <c:f>Summary!$B$1:$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2463,9 +2679,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$6:$M$6</c:f>
+              <c:f>Summary!$B$6:$M$6</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
+                <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>4.4520366169683022E-5</c:v>
@@ -2482,7 +2698,7 @@
                 <c:pt idx="4">
                   <c:v>1.8088159747275158E-5</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="General">
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -2508,7 +2724,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-AC6F-455C-AF10-DE9805C4FD60}"/>
+              <c16:uniqueId val="{00000004-89B1-4510-AEB3-F1F6A92C50C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2517,7 +2733,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>IECCpUAEU!$A$7</c:f>
+              <c:f>Summary!$A$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2538,7 +2754,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
+              <c:f>Summary!$B$1:$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2582,9 +2798,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$7:$M$7</c:f>
+              <c:f>Summary!$B$7:$M$7</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
+                <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>2.9652197760109964E-5</c:v>
@@ -2601,7 +2817,7 @@
                 <c:pt idx="4">
                   <c:v>7.0734511678239686E-5</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="General">
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -2627,7 +2843,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-AC6F-455C-AF10-DE9805C4FD60}"/>
+              <c16:uniqueId val="{00000005-89B1-4510-AEB3-F1F6A92C50C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2636,11 +2852,11 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>IECCpUAEU!$A$8</c:f>
+              <c:f>Summary!$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>electrochemical</c:v>
+                  <c:v>other processes</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2659,7 +2875,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
+              <c:f>Summary!$B$1:$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2703,52 +2919,52 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$8:$M$8</c:f>
+              <c:f>Summary!$B$8:$M$8</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
-                <c:pt idx="0" formatCode="0.00E+00">
-                  <c:v>4.4539618429716232E-5</c:v>
+                <c:pt idx="0">
+                  <c:v>7.0401933942914745E-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>2.0886792055175448E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.2284525195577483E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2.0886792055175448E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1.3150943145851209E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1.3150943145851209E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1.3150943145851209E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1.3150943145851209E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>3.3426787793366228E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>3.3426787793366228E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>3.3426787793366228E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-AC6F-455C-AF10-DE9805C4FD60}"/>
+              <c16:uniqueId val="{00000006-89B1-4510-AEB3-F1F6A92C50C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2757,11 +2973,11 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>IECCpUAEU!$A$9</c:f>
+              <c:f>Summary!$A$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>other processes</c:v>
+                  <c:v>facility HVAC</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2780,7 +2996,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>IECCpUAEU!$B$1:$M$1</c:f>
+              <c:f>Summary!$B$1:$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
@@ -2824,52 +3040,294 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>IECCpUAEU!$B$9:$M$9</c:f>
+              <c:f>Summary!$B$9:$M$9</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
+                <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>7.0401933942914745E-6</c:v>
+                  <c:v>3.0882108581950831E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0886792055175448E-5</c:v>
+                  <c:v>1.4986595988547842E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.2284525195577483E-5</c:v>
+                  <c:v>1.5989491110961776E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.0886792055175448E-5</c:v>
+                  <c:v>1.4986595988547842E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3150943145851209E-5</c:v>
-                </c:pt>
-                <c:pt idx="5" formatCode="General">
+                  <c:v>9.436004881678272E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.3150943145851209E-5</c:v>
+                  <c:v>9.436004881678272E-6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3150943145851209E-5</c:v>
+                  <c:v>9.436004881678272E-6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.3150943145851209E-5</c:v>
+                  <c:v>9.436004881678272E-6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.3426787793366228E-5</c:v>
+                  <c:v>2.3984236666442662E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.3426787793366228E-5</c:v>
+                  <c:v>2.3984236666442662E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.3426787793366228E-5</c:v>
+                  <c:v>2.3984236666442662E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-AC6F-455C-AF10-DE9805C4FD60}"/>
+              <c16:uniqueId val="{00000007-89B1-4510-AEB3-F1F6A92C50C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>facility lighting</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$B$1:$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>electricity if</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hard coal if</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>natural gas if</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>biomass if</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>petroleum diesel if</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>heat if</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>crude oil if</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>heavy or residual fuel oil if</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>LPG propane or butane if</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$B$10:$M$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1.0540697873601793E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.0753846553479132E-6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-89B1-4510-AEB3-F1F6A92C50C5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Summary!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>other nonprocess</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4">
+                <a:lumMod val="60000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Summary!$B$1:$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>electricity if</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hard coal if</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>natural gas if</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>biomass if</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>petroleum diesel if</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>heat if</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>crude oil if</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>heavy or residual fuel oil if</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>LPG propane or butane if</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>green hydrogen if</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>low carbon hydrogen if</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Summary!$B$11:$M$11</c:f>
+              <c:numCache>
+                <c:formatCode>0.000E+00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>4.3468676250759544E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.2235575980706048E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.4517407203745931E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2235575980706048E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.0374236958296052E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.0374236958296052E-5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.0374236958296052E-5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.0374236958296052E-5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.0751094114861809E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.0751094114861809E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.0751094114861809E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-89B1-4510-AEB3-F1F6A92C50C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2955,7 +3413,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.000E+00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3928,13 +4386,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>214312</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>176211</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>38</xdr:row>
+      <xdr:row>39</xdr:row>
       <xdr:rowOff>161924</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3942,11 +4400,13 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27BFA2FA-DB13-925C-2E8E-221F7BFBE255}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{311C43C5-EAFA-4B41-8B79-743C2EAA3BF5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4302,7 +4762,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4310,13 +4770,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4328,19 +4788,19 @@
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="58" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4349,12 +4809,12 @@
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4364,27 +4824,27 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
@@ -4394,27 +4854,27 @@
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
@@ -4424,27 +4884,27 @@
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
@@ -4454,67 +4914,67 @@
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B42" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B48" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
@@ -4524,22 +4984,22 @@
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B54" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.25">
@@ -4549,32 +5009,32 @@
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.25">
@@ -4584,12 +5044,12 @@
     </row>
     <row r="65" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B65" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" s="35" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.25">
@@ -4597,12 +5057,12 @@
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
@@ -4612,17 +5072,17 @@
     </row>
     <row r="71" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B71" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B73" s="35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
@@ -4630,12 +5090,12 @@
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B75" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.25">
@@ -4645,12 +5105,12 @@
     </row>
     <row r="78" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B78" s="36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B79" s="37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="80" spans="2:2" x14ac:dyDescent="0.25">
@@ -4658,12 +5118,12 @@
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" spans="2:2" x14ac:dyDescent="0.25">
@@ -4673,7 +5133,7 @@
     </row>
     <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.25">
@@ -4681,7 +5141,7 @@
     </row>
     <row r="86" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.25">
@@ -4691,22 +5151,22 @@
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.25">
@@ -4716,27 +5176,27 @@
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B99" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.25">
@@ -4746,12 +5206,12 @@
     </row>
     <row r="102" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B102" s="36" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="103" spans="2:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B103" s="37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" spans="2:2" x14ac:dyDescent="0.25">
@@ -4759,32 +5219,32 @@
     </row>
     <row r="105" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B105" s="16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="108" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.25">
@@ -4794,52 +5254,52 @@
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B135" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -4847,12 +5307,12 @@
         <v>138490</v>
       </c>
       <c r="B144" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -4860,7 +5320,7 @@
         <v>3412.14</v>
       </c>
       <c r="B146" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -4868,7 +5328,7 @@
         <v>0.78452102304761584</v>
       </c>
       <c r="B149" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -4876,7 +5336,7 @@
         <v>0.84730412960844359</v>
       </c>
       <c r="B150" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -4905,20 +5365,1078 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B88B710-1DAB-47E6-AE70-A12C5CA0B896}">
+  <dimension ref="A1:P83"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="53" t="s">
+        <v>376</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="54">
+        <v>0.57060049240377109</v>
+      </c>
+      <c r="B2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="54">
+        <f>4000/15</f>
+        <v>266.66666666666669</v>
+      </c>
+      <c r="B3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="56">
+        <f>AVERAGE(O29,H39,H83)</f>
+        <v>8.2719018162705823E-4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="56">
+        <f>AVERAGE(O30,H40,H82)</f>
+        <v>3.1381977460259781E-3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D28" t="s">
+        <v>383</v>
+      </c>
+      <c r="E28" t="s">
+        <v>384</v>
+      </c>
+      <c r="F28" t="s">
+        <v>385</v>
+      </c>
+      <c r="G28" t="s">
+        <v>386</v>
+      </c>
+      <c r="H28" t="s">
+        <v>390</v>
+      </c>
+      <c r="I28" t="s">
+        <v>408</v>
+      </c>
+      <c r="M28" t="s">
+        <v>412</v>
+      </c>
+      <c r="N28" t="s">
+        <v>413</v>
+      </c>
+      <c r="O28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>378</v>
+      </c>
+      <c r="C29">
+        <v>17000</v>
+      </c>
+      <c r="D29">
+        <v>7.1</v>
+      </c>
+      <c r="F29">
+        <v>9.5</v>
+      </c>
+      <c r="G29" s="21">
+        <f>D29*About!$A$144</f>
+        <v>983279</v>
+      </c>
+      <c r="H29" s="21">
+        <f>G29/F29</f>
+        <v>103503.05263157895</v>
+      </c>
+      <c r="I29">
+        <v>250</v>
+      </c>
+      <c r="L29" t="s">
+        <v>375</v>
+      </c>
+      <c r="M29">
+        <f>AVERAGE(C29:C31)*About!A149</f>
+        <v>21966.588645333242</v>
+      </c>
+      <c r="N29">
+        <f>AVERAGE(H29:H31)*A3</f>
+        <v>27574616.079328757</v>
+      </c>
+      <c r="O29" s="55">
+        <f>M29/N29</f>
+        <v>7.9662355342094654E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>379</v>
+      </c>
+      <c r="C30">
+        <v>17000</v>
+      </c>
+      <c r="D30">
+        <v>7.1</v>
+      </c>
+      <c r="F30">
+        <v>10</v>
+      </c>
+      <c r="G30" s="21">
+        <f>D30*About!$A$144</f>
+        <v>983279</v>
+      </c>
+      <c r="H30" s="21">
+        <f>G30/F30</f>
+        <v>98327.9</v>
+      </c>
+      <c r="I30">
+        <v>250</v>
+      </c>
+      <c r="L30" t="s">
+        <v>411</v>
+      </c>
+      <c r="M30">
+        <f>C32*About!A149</f>
+        <v>43148.65626761887</v>
+      </c>
+      <c r="N30">
+        <f>N29*(1-A2)</f>
+        <v>11840526.566618824</v>
+      </c>
+      <c r="O30" s="55">
+        <f>M30/N30</f>
+        <v>3.6441501165383038E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>380</v>
+      </c>
+      <c r="C31">
+        <v>50000</v>
+      </c>
+      <c r="D31">
+        <v>18</v>
+      </c>
+      <c r="F31">
+        <v>23</v>
+      </c>
+      <c r="G31" s="21">
+        <f>D31*About!$A$144</f>
+        <v>2492820</v>
+      </c>
+      <c r="H31" s="21">
+        <f>G31/F31</f>
+        <v>108383.47826086957</v>
+      </c>
+      <c r="I31">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>382</v>
+      </c>
+      <c r="C32">
+        <v>55000</v>
+      </c>
+      <c r="E32">
+        <v>24</v>
+      </c>
+      <c r="F32">
+        <v>16</v>
+      </c>
+      <c r="G32" s="21">
+        <f>E32*About!$A$146</f>
+        <v>81891.360000000001</v>
+      </c>
+      <c r="H32" s="21"/>
+      <c r="I32">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C33">
+        <f>C32/AVERAGE(C29:C31)</f>
+        <v>1.9642857142857142</v>
+      </c>
+      <c r="H33" s="21"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E34">
+        <f>E32/38.1</f>
+        <v>0.62992125984251968</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="24" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C38" t="s">
+        <v>392</v>
+      </c>
+      <c r="D38" t="s">
+        <v>222</v>
+      </c>
+      <c r="E38" t="s">
+        <v>407</v>
+      </c>
+      <c r="F38" t="s">
+        <v>415</v>
+      </c>
+      <c r="G38" t="s">
+        <v>417</v>
+      </c>
+      <c r="H38" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>393</v>
+      </c>
+      <c r="C39">
+        <v>2940</v>
+      </c>
+      <c r="D39">
+        <v>545</v>
+      </c>
+      <c r="E39">
+        <f>37500</f>
+        <v>37500</v>
+      </c>
+      <c r="F39" s="21">
+        <f>AVERAGE(60400,120900,214300)</f>
+        <v>131866.66666666666</v>
+      </c>
+      <c r="G39" s="21">
+        <f>F39*$A$3</f>
+        <v>35164444.444444448</v>
+      </c>
+      <c r="H39" s="55">
+        <f>E39*About!$A$150/G39</f>
+        <v>9.0358045924813471E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>394</v>
+      </c>
+      <c r="C40">
+        <v>113</v>
+      </c>
+      <c r="D40">
+        <v>995</v>
+      </c>
+      <c r="E40" s="21">
+        <f>AVERAGE(58000,74999)</f>
+        <v>66499.5</v>
+      </c>
+      <c r="F40" s="21">
+        <f>F39*(1-A2)</f>
+        <v>56623.481735022717</v>
+      </c>
+      <c r="G40" s="21">
+        <f>F40*$A$3</f>
+        <v>15099595.129339391</v>
+      </c>
+      <c r="H40" s="55">
+        <f>E40*About!$A$150/G40</f>
+        <v>3.7315769386037706E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F41" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="24" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C54" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>396</v>
+      </c>
+      <c r="C55" s="19">
+        <v>0.54</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>397</v>
+      </c>
+      <c r="C56" s="19">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C57" s="19"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="24" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C81" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B82" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C82">
+        <v>28398</v>
+      </c>
+      <c r="D82">
+        <v>250</v>
+      </c>
+      <c r="G82" s="21">
+        <f>G83*(1-A2)</f>
+        <v>11801531.10292552</v>
+      </c>
+      <c r="H82" s="55">
+        <f>C82*About!$A$150/G82</f>
+        <v>2.0388661829358595E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B83" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C83">
+        <v>25345</v>
+      </c>
+      <c r="D83">
+        <v>250</v>
+      </c>
+      <c r="E83">
+        <f>AVERAGE(144,228.1)</f>
+        <v>186.05</v>
+      </c>
+      <c r="G83" s="21">
+        <f>E83*About!A144*A3/D83</f>
+        <v>27483802.133333337</v>
+      </c>
+      <c r="H83" s="55">
+        <f>C83*About!$A$150/G83</f>
+        <v>7.8136653221209343E-4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03FEDD54-04F6-423F-9D03-CF219E654680}">
+  <sheetPr>
+    <tabColor theme="2" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="78">
+        <f>'Boilers &amp; Heat Pumps'!B13</f>
+        <v>3.0882108581950831E-5</v>
+      </c>
+      <c r="C2" s="78">
+        <f>'Boilers &amp; Heat Pumps'!$G$39</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="D2" s="78">
+        <f>'Boilers &amp; Heat Pumps'!A35</f>
+        <v>1.5989491110961776E-5</v>
+      </c>
+      <c r="E2" s="79">
+        <f>C2</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="F2" s="78">
+        <f>'Boilers &amp; Heat Pumps'!$G$40</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="G2" s="80">
+        <v>0</v>
+      </c>
+      <c r="H2" s="79">
+        <f>F2</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="I2" s="79">
+        <f>F2</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="J2" s="79">
+        <f>F2</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="K2" s="78">
+        <f>'Boilers &amp; Heat Pumps'!A56</f>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="L2" s="78">
+        <f t="shared" ref="L2:M8" si="0">K2</f>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="M2" s="78">
+        <f t="shared" si="0"/>
+        <v>2.3984236666442662E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="79">
+        <f>B2</f>
+        <v>3.0882108581950831E-5</v>
+      </c>
+      <c r="C3" s="79">
+        <f t="shared" ref="C3:K3" si="1">C2</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="D3" s="79">
+        <f t="shared" si="1"/>
+        <v>1.5989491110961776E-5</v>
+      </c>
+      <c r="E3" s="79">
+        <f t="shared" si="1"/>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="F3" s="79">
+        <f t="shared" si="1"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="G3" s="80">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H3" s="79">
+        <f t="shared" si="1"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="I3" s="79">
+        <f t="shared" si="1"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="J3" s="79">
+        <f t="shared" si="1"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="K3" s="79">
+        <f t="shared" si="1"/>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="L3" s="79">
+        <f t="shared" si="0"/>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="M3" s="79">
+        <f t="shared" si="0"/>
+        <v>2.3984236666442662E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="78">
+        <f>'NB Medium Temp'!D40</f>
+        <v>3.4771933032458345E-5</v>
+      </c>
+      <c r="C4" s="79">
+        <f>D4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="D4" s="78">
+        <f>'NB Medium Temp'!D41</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="E4" s="79">
+        <f>C4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="F4" s="79">
+        <f>D4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="G4" s="80">
+        <v>0</v>
+      </c>
+      <c r="H4" s="79">
+        <f>F4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="I4" s="79">
+        <f>F4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="J4" s="79">
+        <f>F4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="K4" s="79">
+        <f>D4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="L4" s="79">
+        <f t="shared" si="0"/>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="M4" s="79">
+        <f t="shared" si="0"/>
+        <v>3.1780367029653324E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="78">
+        <f>'NB High Temp'!F10</f>
+        <v>1.7204637228083889E-4</v>
+      </c>
+      <c r="C5" s="78">
+        <f>'NB High Temp'!F45</f>
+        <v>4.5951806950193628E-6</v>
+      </c>
+      <c r="D5" s="78">
+        <f>'NB High Temp'!F56</f>
+        <v>2.0725243194734525E-5</v>
+      </c>
+      <c r="E5" s="79">
+        <f>C5</f>
+        <v>4.5951806950193628E-6</v>
+      </c>
+      <c r="F5" s="79">
+        <f>D5*(F2/D2)</f>
+        <v>1.2230751723262388E-5</v>
+      </c>
+      <c r="G5" s="80">
+        <v>0</v>
+      </c>
+      <c r="H5" s="79">
+        <f>F5</f>
+        <v>1.2230751723262388E-5</v>
+      </c>
+      <c r="I5" s="79">
+        <f>F5</f>
+        <v>1.2230751723262388E-5</v>
+      </c>
+      <c r="J5" s="79">
+        <f>F5</f>
+        <v>1.2230751723262388E-5</v>
+      </c>
+      <c r="K5" s="78">
+        <f>'NB High Temp'!F67</f>
+        <v>3.265784625690839E-5</v>
+      </c>
+      <c r="L5" s="78">
+        <f t="shared" si="0"/>
+        <v>3.265784625690839E-5</v>
+      </c>
+      <c r="M5" s="78">
+        <f t="shared" si="0"/>
+        <v>3.265784625690839E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="78">
+        <f>Cooling!$B$49</f>
+        <v>4.4520366169683022E-5</v>
+      </c>
+      <c r="C6" s="79">
+        <f>$D$6</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="D6" s="78">
+        <f>Cooling!$B$27</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="E6" s="79">
+        <f>$D$6</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="F6" s="79">
+        <f>$D$6</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="G6" s="80">
+        <v>0</v>
+      </c>
+      <c r="H6" s="79">
+        <f>$D$6</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="I6" s="79">
+        <f>$D$6</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="J6" s="79">
+        <f>$D$6</f>
+        <v>1.8088159747275158E-5</v>
+      </c>
+      <c r="K6" s="79">
+        <f>$D$6*(K2/D2)</f>
+        <v>2.7132239620912736E-5</v>
+      </c>
+      <c r="L6" s="79">
+        <f t="shared" si="0"/>
+        <v>2.7132239620912736E-5</v>
+      </c>
+      <c r="M6" s="79">
+        <f t="shared" si="0"/>
+        <v>2.7132239620912736E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="78">
+        <f>'Machine Drive'!$W$22</f>
+        <v>2.9652197760109964E-5</v>
+      </c>
+      <c r="C7" s="79">
+        <f>$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="D7" s="79">
+        <f>$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="E7" s="79">
+        <f>$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="F7" s="78">
+        <f>'Machine Drive'!D38</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="G7" s="80">
+        <v>0</v>
+      </c>
+      <c r="H7" s="79">
+        <f>$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="I7" s="79">
+        <f>$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="J7" s="79">
+        <f>$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="K7" s="79">
+        <f>$F$7</f>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="L7" s="79">
+        <f t="shared" si="0"/>
+        <v>7.0734511678239686E-5</v>
+      </c>
+      <c r="M7" s="79">
+        <f t="shared" si="0"/>
+        <v>7.0734511678239686E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="78">
+        <f>Other!E9</f>
+        <v>7.0401933942914745E-6</v>
+      </c>
+      <c r="C8" s="79">
+        <f>D8*(C2/D2)</f>
+        <v>2.0886792055175448E-5</v>
+      </c>
+      <c r="D8" s="78">
+        <f>Other!B24</f>
+        <v>2.2284525195577483E-5</v>
+      </c>
+      <c r="E8" s="79">
+        <f>C8</f>
+        <v>2.0886792055175448E-5</v>
+      </c>
+      <c r="F8" s="79">
+        <f>D8*(F2/D2)</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="G8" s="80">
+        <v>0</v>
+      </c>
+      <c r="H8" s="79">
+        <f>F8</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="I8" s="79">
+        <f>F8</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="J8" s="79">
+        <f>F8</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="K8" s="79">
+        <f>D8*(K2/D2)</f>
+        <v>3.3426787793366228E-5</v>
+      </c>
+      <c r="L8" s="79">
+        <f t="shared" si="0"/>
+        <v>3.3426787793366228E-5</v>
+      </c>
+      <c r="M8" s="79">
+        <f>L8</f>
+        <v>3.3426787793366228E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" s="79">
+        <f>B2</f>
+        <v>3.0882108581950831E-5</v>
+      </c>
+      <c r="C9" s="79">
+        <f t="shared" ref="C9:M9" si="2">C2</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="D9" s="79">
+        <f t="shared" si="2"/>
+        <v>1.5989491110961776E-5</v>
+      </c>
+      <c r="E9" s="79">
+        <f t="shared" si="2"/>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="F9" s="79">
+        <f t="shared" si="2"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="G9" s="80">
+        <v>0</v>
+      </c>
+      <c r="H9" s="79">
+        <f t="shared" si="2"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="I9" s="79">
+        <f t="shared" si="2"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="J9" s="79">
+        <f t="shared" si="2"/>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="K9" s="79">
+        <f t="shared" si="2"/>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="L9" s="79">
+        <f t="shared" si="2"/>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="M9" s="79">
+        <f t="shared" si="2"/>
+        <v>2.3984236666442662E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" s="78">
+        <f>Lighting!O23</f>
+        <v>1.0540697873601793E-5</v>
+      </c>
+      <c r="C10" s="79">
+        <f t="shared" ref="C10:E10" si="3">$F$10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="D10" s="79">
+        <f t="shared" si="3"/>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="E10" s="79">
+        <f>$F$10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="F10" s="78">
+        <f>Lighting!I39</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="G10" s="80">
+        <v>0</v>
+      </c>
+      <c r="H10" s="79">
+        <f t="shared" ref="H10:M10" si="4">$F$10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="I10" s="79">
+        <f t="shared" si="4"/>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="J10" s="79">
+        <f t="shared" si="4"/>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="K10" s="79">
+        <f t="shared" si="4"/>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="L10" s="79">
+        <f t="shared" si="4"/>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="M10" s="79">
+        <f t="shared" si="4"/>
+        <v>9.0753846553479132E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B11" s="79">
+        <f>AVERAGE(B2:B10)</f>
+        <v>4.3468676250759544E-5</v>
+      </c>
+      <c r="C11" s="79">
+        <f t="shared" ref="C11:M11" si="5">AVERAGE(C2:C10)</f>
+        <v>2.2235575980706048E-5</v>
+      </c>
+      <c r="D11" s="79">
+        <f t="shared" si="5"/>
+        <v>2.4517407203745931E-5</v>
+      </c>
+      <c r="E11" s="79">
+        <f t="shared" si="5"/>
+        <v>2.2235575980706048E-5</v>
+      </c>
+      <c r="F11" s="79">
+        <f t="shared" si="5"/>
+        <v>2.0374236958296052E-5</v>
+      </c>
+      <c r="G11" s="77">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="79">
+        <f t="shared" si="5"/>
+        <v>2.0374236958296052E-5</v>
+      </c>
+      <c r="I11" s="79">
+        <f t="shared" si="5"/>
+        <v>2.0374236958296052E-5</v>
+      </c>
+      <c r="J11" s="79">
+        <f t="shared" si="5"/>
+        <v>2.0374236958296052E-5</v>
+      </c>
+      <c r="K11" s="79">
+        <f t="shared" si="5"/>
+        <v>3.0751094114861809E-5</v>
+      </c>
+      <c r="L11" s="79">
+        <f t="shared" si="5"/>
+        <v>3.0751094114861809E-5</v>
+      </c>
+      <c r="M11" s="79">
+        <f t="shared" si="5"/>
+        <v>3.0751094114861809E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="9"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>371</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC78963D-3265-44FA-8138-35C2A57258D3}">
   <sheetPr>
     <tabColor theme="3" tint="0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:AR11"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="13" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -4951,464 +6469,579 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+      <c r="Q1"/>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
+      <c r="X1"/>
+      <c r="Y1"/>
+      <c r="Z1"/>
+      <c r="AA1"/>
+      <c r="AB1"/>
+      <c r="AC1"/>
+      <c r="AD1"/>
+      <c r="AE1"/>
+      <c r="AF1"/>
+      <c r="AG1"/>
+      <c r="AH1"/>
+      <c r="AI1"/>
+      <c r="AJ1"/>
+      <c r="AK1"/>
+      <c r="AL1"/>
+      <c r="AM1"/>
+      <c r="AN1"/>
+      <c r="AO1"/>
+      <c r="AP1"/>
+      <c r="AQ1"/>
+      <c r="AR1"/>
+    </row>
+    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="12">
-        <f>'Boilers &amp; Heat Pumps'!B13</f>
+      <c r="B2" s="81">
+        <f>Summary!B2</f>
         <v>3.0882108581950831E-5</v>
       </c>
-      <c r="C2" s="12">
-        <f>'Boilers &amp; Heat Pumps'!$G$39</f>
+      <c r="C2" s="81">
+        <f>Summary!C2</f>
         <v>1.4986595988547842E-5</v>
       </c>
-      <c r="D2" s="12">
-        <f>'Boilers &amp; Heat Pumps'!A35</f>
+      <c r="D2" s="81">
+        <f>Summary!D2</f>
         <v>1.5989491110961776E-5</v>
       </c>
-      <c r="E2" s="10">
-        <f>C2</f>
+      <c r="E2" s="81">
+        <f>Summary!E2</f>
         <v>1.4986595988547842E-5</v>
       </c>
-      <c r="F2" s="12">
-        <f>'Boilers &amp; Heat Pumps'!$G$40</f>
+      <c r="F2" s="81">
+        <f>Summary!F2</f>
         <v>9.436004881678272E-6</v>
       </c>
-      <c r="G2" s="40">
+      <c r="G2" s="81">
+        <f>Summary!G2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="10">
-        <f>F2</f>
+      <c r="H2" s="81">
+        <f>Summary!H2</f>
         <v>9.436004881678272E-6</v>
       </c>
-      <c r="I2" s="10">
-        <f>F2</f>
+      <c r="I2" s="81">
+        <f>Summary!I2</f>
         <v>9.436004881678272E-6</v>
       </c>
-      <c r="J2" s="10">
-        <f>F2</f>
+      <c r="J2" s="81">
+        <f>Summary!J2</f>
         <v>9.436004881678272E-6</v>
       </c>
-      <c r="K2" s="12">
-        <f>'Boilers &amp; Heat Pumps'!A56</f>
+      <c r="K2" s="81">
+        <f>Summary!K2</f>
         <v>2.3984236666442662E-5</v>
       </c>
-      <c r="L2" s="12">
-        <f>K2</f>
+      <c r="L2" s="81">
+        <f>Summary!L2</f>
         <v>2.3984236666442662E-5</v>
       </c>
-      <c r="M2" s="12">
-        <f t="shared" ref="M2:M9" si="0">L2</f>
+      <c r="M2" s="81">
+        <f>Summary!M2</f>
         <v>2.3984236666442662E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="10">
-        <f>B2</f>
+      <c r="B3" s="81">
+        <f>Summary!B3</f>
         <v>3.0882108581950831E-5</v>
       </c>
-      <c r="C3" s="10">
-        <f t="shared" ref="C3:K3" si="1">C2</f>
+      <c r="C3" s="81">
+        <f>Summary!C3</f>
         <v>1.4986595988547842E-5</v>
       </c>
-      <c r="D3" s="10">
-        <f t="shared" si="1"/>
+      <c r="D3" s="81">
+        <f>Summary!D3</f>
         <v>1.5989491110961776E-5</v>
       </c>
-      <c r="E3" s="10">
-        <f t="shared" si="1"/>
+      <c r="E3" s="81">
+        <f>Summary!E3</f>
         <v>1.4986595988547842E-5</v>
       </c>
-      <c r="F3" s="10">
-        <f t="shared" si="1"/>
+      <c r="F3" s="81">
+        <f>Summary!F3</f>
         <v>9.436004881678272E-6</v>
       </c>
-      <c r="G3" s="40">
-        <f t="shared" si="1"/>
+      <c r="G3" s="81">
+        <f>Summary!G3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="10">
-        <f t="shared" si="1"/>
+      <c r="H3" s="81">
+        <f>Summary!H3</f>
         <v>9.436004881678272E-6</v>
       </c>
-      <c r="I3" s="10">
-        <f t="shared" si="1"/>
+      <c r="I3" s="81">
+        <f>Summary!I3</f>
         <v>9.436004881678272E-6</v>
       </c>
-      <c r="J3" s="10">
-        <f t="shared" si="1"/>
+      <c r="J3" s="81">
+        <f>Summary!J3</f>
         <v>9.436004881678272E-6</v>
       </c>
-      <c r="K3" s="10">
-        <f t="shared" si="1"/>
+      <c r="K3" s="81">
+        <f>Summary!K3</f>
         <v>2.3984236666442662E-5</v>
       </c>
-      <c r="L3" s="10">
-        <f t="shared" ref="L3" si="2">K3</f>
+      <c r="L3" s="81">
+        <f>Summary!L3</f>
         <v>2.3984236666442662E-5</v>
       </c>
-      <c r="M3" s="10">
-        <f t="shared" si="0"/>
+      <c r="M3" s="81">
+        <f>Summary!M3</f>
         <v>2.3984236666442662E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="12">
-        <f>'NB Medium Temp'!D40</f>
+      <c r="B4" s="81">
+        <f>Summary!B4</f>
         <v>3.4771933032458345E-5</v>
       </c>
-      <c r="C4" s="10">
-        <f>D4</f>
+      <c r="C4" s="81">
+        <f>Summary!C4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="D4" s="12">
-        <f>'NB Medium Temp'!D41</f>
+      <c r="D4" s="81">
+        <f>Summary!D4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="E4" s="10">
-        <f>C4</f>
+      <c r="E4" s="81">
+        <f>Summary!E4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="F4" s="10">
-        <f>D4</f>
+      <c r="F4" s="81">
+        <f>Summary!F4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="G4" s="40">
+      <c r="G4" s="81">
+        <f>Summary!G4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="10">
-        <f t="shared" ref="H4" si="3">F4</f>
+      <c r="H4" s="81">
+        <f>Summary!H4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="I4" s="10">
-        <f t="shared" ref="I4" si="4">F4</f>
+      <c r="I4" s="81">
+        <f>Summary!I4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="J4" s="10">
-        <f t="shared" ref="J4" si="5">F4</f>
+      <c r="J4" s="81">
+        <f>Summary!J4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="K4" s="10">
-        <f>D4</f>
+      <c r="K4" s="81">
+        <f>Summary!K4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="L4" s="10">
-        <f t="shared" ref="L4" si="6">K4</f>
+      <c r="L4" s="81">
+        <f>Summary!L4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="M4" s="10">
-        <f t="shared" si="0"/>
+      <c r="M4" s="81">
+        <f>Summary!M4</f>
         <v>3.1780367029653324E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="12">
-        <f>'NB High Temp'!F10</f>
+      <c r="B5" s="81">
+        <f>Summary!B5</f>
         <v>1.7204637228083889E-4</v>
       </c>
-      <c r="C5" s="12">
-        <f>'NB High Temp'!F45</f>
+      <c r="C5" s="81">
+        <f>Summary!C5</f>
         <v>4.5951806950193628E-6</v>
       </c>
-      <c r="D5" s="12">
-        <f>'NB High Temp'!F56</f>
+      <c r="D5" s="81">
+        <f>Summary!D5</f>
         <v>2.0725243194734525E-5</v>
       </c>
-      <c r="E5" s="10">
-        <f>C5</f>
+      <c r="E5" s="81">
+        <f>Summary!E5</f>
         <v>4.5951806950193628E-6</v>
       </c>
-      <c r="F5" s="10">
-        <f>D5*(F2/D2)</f>
+      <c r="F5" s="81">
+        <f>Summary!F5</f>
         <v>1.2230751723262388E-5</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="81">
+        <f>Summary!G5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="10">
-        <f t="shared" ref="H5" si="7">F5</f>
+      <c r="H5" s="81">
+        <f>Summary!H5</f>
         <v>1.2230751723262388E-5</v>
       </c>
-      <c r="I5" s="10">
-        <f t="shared" ref="I5" si="8">F5</f>
+      <c r="I5" s="81">
+        <f>Summary!I5</f>
         <v>1.2230751723262388E-5</v>
       </c>
-      <c r="J5" s="10">
-        <f t="shared" ref="J5" si="9">F5</f>
+      <c r="J5" s="81">
+        <f>Summary!J5</f>
         <v>1.2230751723262388E-5</v>
       </c>
-      <c r="K5" s="12">
-        <f>'NB High Temp'!F67</f>
+      <c r="K5" s="81">
+        <f>Summary!K5</f>
         <v>3.265784625690839E-5</v>
       </c>
-      <c r="L5" s="12">
-        <f t="shared" ref="L5" si="10">K5</f>
+      <c r="L5" s="81">
+        <f>Summary!L5</f>
         <v>3.265784625690839E-5</v>
       </c>
-      <c r="M5" s="12">
-        <f t="shared" si="0"/>
+      <c r="M5" s="81">
+        <f>Summary!M5</f>
         <v>3.265784625690839E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="12">
-        <f>Cooling!$B$49</f>
+      <c r="B6" s="81">
+        <f>Summary!B6</f>
         <v>4.4520366169683022E-5</v>
       </c>
-      <c r="C6" s="10">
-        <f>$D$6</f>
+      <c r="C6" s="81">
+        <f>Summary!C6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="D6" s="12">
-        <f>Cooling!$B$27</f>
+      <c r="D6" s="81">
+        <f>Summary!D6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="E6" s="10">
-        <f t="shared" ref="E6:F6" si="11">$D$6</f>
+      <c r="E6" s="81">
+        <f>Summary!E6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="F6" s="10">
-        <f t="shared" si="11"/>
+      <c r="F6" s="81">
+        <f>Summary!F6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="81">
+        <f>Summary!G6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="10">
-        <f t="shared" ref="H6:J6" si="12">$D$6</f>
+      <c r="H6" s="81">
+        <f>Summary!H6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="I6" s="10">
-        <f t="shared" si="12"/>
+      <c r="I6" s="81">
+        <f>Summary!I6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="J6" s="10">
-        <f t="shared" si="12"/>
+      <c r="J6" s="81">
+        <f>Summary!J6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="K6" s="10">
-        <f>$D$6*(K2/D2)</f>
+      <c r="K6" s="81">
+        <f>Summary!K6</f>
         <v>2.7132239620912736E-5</v>
       </c>
-      <c r="L6" s="10">
-        <f t="shared" ref="L6" si="13">K6</f>
+      <c r="L6" s="81">
+        <f>Summary!L6</f>
         <v>2.7132239620912736E-5</v>
       </c>
-      <c r="M6" s="10">
-        <f t="shared" si="0"/>
+      <c r="M6" s="81">
+        <f>Summary!M6</f>
         <v>2.7132239620912736E-5</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="12">
-        <f>'Machine Drive'!$W$22</f>
+      <c r="B7" s="81">
+        <f>Summary!B7</f>
         <v>2.9652197760109964E-5</v>
       </c>
-      <c r="C7" s="10">
-        <f>$F$7</f>
+      <c r="C7" s="81">
+        <f>Summary!C7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="D7" s="10">
-        <f t="shared" ref="D7:E7" si="14">$F$7</f>
+      <c r="D7" s="81">
+        <f>Summary!D7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="E7" s="10">
-        <f t="shared" si="14"/>
+      <c r="E7" s="81">
+        <f>Summary!E7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="F7" s="12">
-        <f>'Machine Drive'!D38</f>
+      <c r="F7" s="81">
+        <f>Summary!F7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="81">
+        <f>Summary!G7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="10">
-        <f t="shared" ref="H7:K7" si="15">$F$7</f>
+      <c r="H7" s="81">
+        <f>Summary!H7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="I7" s="10">
-        <f t="shared" si="15"/>
+      <c r="I7" s="81">
+        <f>Summary!I7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="J7" s="10">
-        <f t="shared" si="15"/>
+      <c r="J7" s="81">
+        <f>Summary!J7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="K7" s="10">
-        <f t="shared" si="15"/>
+      <c r="K7" s="81">
+        <f>Summary!K7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="L7" s="10">
-        <f t="shared" ref="L7" si="16">K7</f>
+      <c r="L7" s="81">
+        <f>Summary!L7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="M7" s="10">
-        <f t="shared" si="0"/>
+      <c r="M7" s="81">
+        <f>Summary!M7</f>
         <v>7.0734511678239686E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="12">
-        <f>Electrochemical!$G32</f>
-        <v>4.4539618429716232E-5</v>
-      </c>
-      <c r="C8" s="40">
+      <c r="B8" s="81">
+        <f>Summary!B8</f>
+        <v>7.0401933942914745E-6</v>
+      </c>
+      <c r="C8" s="81">
+        <f>Summary!C8</f>
+        <v>2.0886792055175448E-5</v>
+      </c>
+      <c r="D8" s="81">
+        <f>Summary!D8</f>
+        <v>2.2284525195577483E-5</v>
+      </c>
+      <c r="E8" s="81">
+        <f>Summary!E8</f>
+        <v>2.0886792055175448E-5</v>
+      </c>
+      <c r="F8" s="81">
+        <f>Summary!F8</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="G8" s="81">
+        <f>Summary!G8</f>
         <v>0</v>
       </c>
-      <c r="D8" s="40">
+      <c r="H8" s="81">
+        <f>Summary!H8</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="I8" s="81">
+        <f>Summary!I8</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="J8" s="81">
+        <f>Summary!J8</f>
+        <v>1.3150943145851209E-5</v>
+      </c>
+      <c r="K8" s="81">
+        <f>Summary!K8</f>
+        <v>3.3426787793366228E-5</v>
+      </c>
+      <c r="L8" s="81">
+        <f>Summary!L8</f>
+        <v>3.3426787793366228E-5</v>
+      </c>
+      <c r="M8" s="81">
+        <f>Summary!M8</f>
+        <v>3.3426787793366228E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" s="81">
+        <f>Summary!B9</f>
+        <v>3.0882108581950831E-5</v>
+      </c>
+      <c r="C9" s="81">
+        <f>Summary!C9</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="D9" s="81">
+        <f>Summary!D9</f>
+        <v>1.5989491110961776E-5</v>
+      </c>
+      <c r="E9" s="81">
+        <f>Summary!E9</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="F9" s="81">
+        <f>Summary!F9</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="G9" s="81">
+        <f>Summary!G9</f>
         <v>0</v>
       </c>
-      <c r="E8" s="40">
+      <c r="H9" s="81">
+        <f>Summary!H9</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="I9" s="81">
+        <f>Summary!I9</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="J9" s="81">
+        <f>Summary!J9</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="K9" s="81">
+        <f>Summary!K9</f>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="L9" s="81">
+        <f>Summary!L9</f>
+        <v>2.3984236666442662E-5</v>
+      </c>
+      <c r="M9" s="81">
+        <f>Summary!M9</f>
+        <v>2.3984236666442662E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" s="81">
+        <f>Summary!B10</f>
+        <v>1.0540697873601793E-5</v>
+      </c>
+      <c r="C10" s="81">
+        <f>Summary!C10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="D10" s="81">
+        <f>Summary!D10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="E10" s="81">
+        <f>Summary!E10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="F10" s="81">
+        <f>Summary!F10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="G10" s="81">
+        <f>Summary!G10</f>
         <v>0</v>
       </c>
-      <c r="F8" s="40">
+      <c r="H10" s="81">
+        <f>Summary!H10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="I10" s="81">
+        <f>Summary!I10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="J10" s="81">
+        <f>Summary!J10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="K10" s="81">
+        <f>Summary!K10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="L10" s="81">
+        <f>Summary!L10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="M10" s="81">
+        <f>Summary!M10</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B11" s="81">
+        <f>Summary!B11</f>
+        <v>4.3468676250759544E-5</v>
+      </c>
+      <c r="C11" s="81">
+        <f>Summary!C11</f>
+        <v>2.2235575980706048E-5</v>
+      </c>
+      <c r="D11" s="81">
+        <f>Summary!D11</f>
+        <v>2.4517407203745931E-5</v>
+      </c>
+      <c r="E11" s="81">
+        <f>Summary!E11</f>
+        <v>2.2235575980706048E-5</v>
+      </c>
+      <c r="F11" s="81">
+        <f>Summary!F11</f>
+        <v>2.0374236958296052E-5</v>
+      </c>
+      <c r="G11" s="81">
+        <f>Summary!G11</f>
         <v>0</v>
       </c>
-      <c r="G8" s="40">
-        <v>0</v>
-      </c>
-      <c r="H8" s="40">
-        <v>0</v>
-      </c>
-      <c r="I8" s="40">
-        <v>0</v>
-      </c>
-      <c r="J8" s="40">
-        <v>0</v>
-      </c>
-      <c r="K8" s="40">
-        <v>0</v>
-      </c>
-      <c r="L8" s="40">
-        <f t="shared" ref="L8" si="17">K8</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="12">
-        <f>Other!E9</f>
-        <v>7.0401933942914745E-6</v>
-      </c>
-      <c r="C9" s="10">
-        <f>D9*(C2/D2)</f>
-        <v>2.0886792055175448E-5</v>
-      </c>
-      <c r="D9" s="12">
-        <f>Other!B24</f>
-        <v>2.2284525195577483E-5</v>
-      </c>
-      <c r="E9" s="10">
-        <f>C9</f>
-        <v>2.0886792055175448E-5</v>
-      </c>
-      <c r="F9" s="10">
-        <f>D9*(F2/D2)</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="G9" s="40">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10">
-        <f>F9</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="I9" s="10">
-        <f>F9</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="J9" s="10">
-        <f>F9</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="K9" s="10">
-        <f>D9*(K2/D2)</f>
-        <v>3.3426787793366228E-5</v>
-      </c>
-      <c r="L9" s="10">
-        <f t="shared" ref="L9" si="18">K9</f>
-        <v>3.3426787793366228E-5</v>
-      </c>
-      <c r="M9" s="10">
-        <f t="shared" si="0"/>
-        <v>3.3426787793366228E-5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="9"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>372</v>
+      <c r="H11" s="81">
+        <f>Summary!H11</f>
+        <v>2.0374236958296052E-5</v>
+      </c>
+      <c r="I11" s="81">
+        <f>Summary!I11</f>
+        <v>2.0374236958296052E-5</v>
+      </c>
+      <c r="J11" s="81">
+        <f>Summary!J11</f>
+        <v>2.0374236958296052E-5</v>
+      </c>
+      <c r="K11" s="81">
+        <f>Summary!K11</f>
+        <v>3.0751094114861809E-5</v>
+      </c>
+      <c r="L11" s="81">
+        <f>Summary!L11</f>
+        <v>3.0751094114861809E-5</v>
+      </c>
+      <c r="M11" s="81">
+        <f>Summary!M11</f>
+        <v>3.0751094114861809E-5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="H3:J3 E3 D6" formula="1"/>
-  </ignoredErrors>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843ADA01-EFFE-45B2-B6A7-C20F6BBCF0E2}">
   <sheetPr>
     <tabColor theme="3" tint="0.249977111117893"/>
@@ -5422,7 +7055,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5528,7 +7161,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B12" s="10">
         <f>B11</f>
@@ -5537,7 +7170,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B13" s="10">
         <f>B12</f>
@@ -5566,7 +7199,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -5574,12 +7207,12 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5587,67 +7220,67 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="64"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B6">
         <v>600</v>
       </c>
       <c r="C6" s="62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B7">
         <v>8760</v>
       </c>
       <c r="C7" s="62" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D7" s="62"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B8" s="19">
         <v>0.65</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D8" s="62"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B9" s="63">
         <f>B6/(B7*B8)</f>
         <v>0.10537407797681771</v>
       </c>
       <c r="C9" s="62" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5655,13 +7288,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11">
         <v>3412.14</v>
       </c>
       <c r="C11" s="62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5669,28 +7302,28 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B13" s="12">
         <f>B9/B11</f>
         <v>3.0882108581950831E-5</v>
       </c>
       <c r="C13" s="62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="D14" s="24" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -5699,12 +7332,12 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B20" s="8">
         <v>80375</v>
@@ -5712,7 +7345,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B21" s="8">
         <v>91475</v>
@@ -5720,7 +7353,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B22" s="8">
         <f>AVERAGE(B20:B21)</f>
@@ -5729,7 +7362,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B24">
         <v>400</v>
@@ -5737,7 +7370,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B25">
         <v>0.74570000000000003</v>
@@ -5745,7 +7378,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26">
         <f>B24*B25</f>
@@ -5754,7 +7387,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="22">
         <v>5280</v>
@@ -5762,42 +7395,42 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B30">
         <f>B26*B28</f>
         <v>1574918.4000000001</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31">
         <v>3412.14</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B32">
         <f>B30*B31</f>
         <v>5373842069.3760004</v>
       </c>
       <c r="C32" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5806,12 +7439,12 @@
         <v>1.5989491110961776E-5</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
@@ -5820,27 +7453,27 @@
     </row>
     <row r="38" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B38" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E38" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F38" s="23" t="s">
-        <v>50</v>
-      </c>
       <c r="G38" s="23" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>2000</v>
@@ -5866,7 +7499,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40">
         <v>2000</v>
@@ -5875,24 +7508,24 @@
         <v>200</v>
       </c>
       <c r="D40">
-        <f t="shared" ref="D40:D41" si="0">B40*C40</f>
+        <f>B40*C40</f>
         <v>400000</v>
       </c>
       <c r="E40" s="19">
         <v>0.85</v>
       </c>
       <c r="F40">
-        <f t="shared" ref="F40:F41" si="1">$B$46/E40</f>
+        <f>$B$46/E40</f>
         <v>42390821647.058823</v>
       </c>
       <c r="G40" s="12">
-        <f t="shared" ref="G40:G41" si="2">D40/F40</f>
+        <f>D40/F40</f>
         <v>9.436004881678272E-6</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B41">
         <v>2000</v>
@@ -5901,77 +7534,77 @@
         <v>100</v>
       </c>
       <c r="D41">
-        <f t="shared" si="0"/>
+        <f>B41*C41</f>
         <v>200000</v>
       </c>
       <c r="E41" s="19">
         <v>0.95</v>
       </c>
       <c r="F41">
-        <f t="shared" si="1"/>
+        <f>$B$46/E41</f>
         <v>37928629894.736847</v>
       </c>
       <c r="G41" s="9">
-        <f t="shared" si="2"/>
+        <f>D41/F41</f>
         <v>5.2730615515260925E-6</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44">
         <f>B39*B28</f>
         <v>10560000</v>
       </c>
       <c r="C44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B45">
         <v>3412.14</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46">
         <f>B44*B45</f>
         <v>36032198400</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
@@ -5979,13 +7612,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" s="8"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" s="20"/>
     </row>
@@ -5995,7 +7628,7 @@
         <v>2.3984236666442662E-5</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -6014,330 +7647,330 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" s="8">
         <v>307500</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B6">
         <v>4000</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" s="8">
         <v>75863</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" s="8">
         <v>6226</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="25">
         <v>0.45</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" s="25">
         <v>0.15</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" s="21">
         <f>B8/B11</f>
         <v>168584.44444444444</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="21">
         <f>B9/B12</f>
         <v>41506.666666666672</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17">
         <v>100000</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18">
         <v>3412.14</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" s="9">
         <f>B14*B17</f>
         <v>16858444444.444445</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B21" s="9">
         <f>B15*B18</f>
         <v>141626557.60000002</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="9">
         <f>SUM(B20:B21)</f>
         <v>17000071002.044445</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B27" s="12">
         <f>B5/B26</f>
         <v>1.8088159747275158E-5</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" s="8">
         <v>200</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B33" s="8">
         <v>500</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B34" s="8">
         <f>AVERAGE(B32:B33)</f>
         <v>350</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B36">
         <v>500</v>
       </c>
       <c r="C36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B38" s="8">
         <f>B34*B36</f>
         <v>175000</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B41">
         <v>0.57599999999999996</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B42">
         <f>B41*B36</f>
         <v>288</v>
       </c>
       <c r="C42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B44">
         <f>B6</f>
         <v>4000</v>
       </c>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B46">
         <f>B42*B44</f>
         <v>1152000</v>
       </c>
       <c r="C46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B47" s="9">
         <f>B46*B18</f>
         <v>3930785280</v>
       </c>
       <c r="C47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B49" s="12">
         <f>B38/B47</f>
         <v>4.4520366169683022E-5</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -6361,7 +7994,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6369,25 +8002,25 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B3" s="42"/>
       <c r="C3" s="11" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B5">
         <v>492000</v>
@@ -6396,7 +8029,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B6">
         <v>135000</v>
@@ -6405,7 +8038,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B7">
         <v>474000</v>
@@ -6414,7 +8047,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B8">
         <v>70000</v>
@@ -6423,7 +8056,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B9">
         <v>22000</v>
@@ -6432,7 +8065,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B10">
         <v>18000</v>
@@ -6441,7 +8074,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B11">
         <v>216000</v>
@@ -6450,7 +8083,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B12">
         <v>51000</v>
@@ -6459,7 +8092,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B13">
         <v>125000</v>
@@ -6468,24 +8101,24 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B17" s="20">
         <v>13400</v>
@@ -6493,7 +8126,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B18" s="20">
         <v>5300</v>
@@ -6501,7 +8134,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B19" s="20">
         <v>13600</v>
@@ -6509,32 +8142,32 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B23">
         <v>4380</v>
@@ -6545,7 +8178,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B24">
         <v>4380</v>
@@ -6556,7 +8189,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="40"/>
@@ -6564,32 +8197,32 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B33" s="1">
         <f>'Boilers &amp; Heat Pumps'!B28</f>
@@ -6598,13 +8231,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="46">
         <v>3412.14</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -6612,7 +8245,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="45" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B38" s="44"/>
       <c r="C38" s="44"/>
@@ -6620,21 +8253,21 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="D39" s="7" t="s">
         <v>344</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B40">
         <f>$B$33*D23*B36</f>
@@ -6651,7 +8284,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B41">
         <f>$B$33*C24</f>
@@ -6668,33 +8301,33 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B51" s="42"/>
       <c r="C51" s="42"/>
       <c r="D51" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="C52" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B53">
         <v>722000</v>
@@ -6706,7 +8339,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B54">
         <v>882000</v>
@@ -6734,7 +8367,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -6745,12 +8378,12 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I2" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" s="25"/>
       <c r="F3" s="25">
@@ -6758,107 +8391,107 @@
         <v>264.16000000000003</v>
       </c>
       <c r="G3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F4">
         <v>450</v>
       </c>
       <c r="G4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C5" s="32"/>
       <c r="F5" s="32">
         <v>800000</v>
       </c>
       <c r="G5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F7">
         <f>F4*F5</f>
         <v>360000000</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F8">
         <f>F7*0.003412</f>
         <v>1228320</v>
       </c>
       <c r="G8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F9" s="25">
         <f>F3*F5</f>
         <v>211328000.00000003</v>
       </c>
       <c r="G9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F10" s="12">
         <f>F9/(F8*10^6)</f>
         <v>1.7204637228083889E-4</v>
       </c>
       <c r="G10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E12">
         <f>8760*155</f>
         <v>1357800</v>
       </c>
       <c r="F12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -6869,13 +8502,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F16" s="20">
         <v>170</v>
       </c>
       <c r="G16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -6884,7 +8517,7 @@
         <v>26.356589147286826</v>
       </c>
       <c r="G17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -6893,7 +8526,7 @@
         <v>9.4883645023316546E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -6902,80 +8535,80 @@
         <v>2.7808805692648461E-5</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F21">
         <v>36000000</v>
       </c>
       <c r="G21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F22" s="20">
         <f>F21*0.14</f>
         <v>5040000.0000000009</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F23">
         <f>AVERAGE(5.1,7.8)</f>
         <v>6.4499999999999993</v>
       </c>
       <c r="G23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I23" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F24">
         <v>8000</v>
       </c>
       <c r="G24" t="s">
+        <v>222</v>
+      </c>
+      <c r="I24" s="15" t="s">
         <v>223</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F25">
         <v>600</v>
       </c>
       <c r="G25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -6984,7 +8617,7 @@
         <v>3869.9999999999995</v>
       </c>
       <c r="G26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I26" s="15"/>
     </row>
@@ -6994,95 +8627,95 @@
         <v>1289999.9999999998</v>
       </c>
       <c r="G27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I27" s="15"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F28">
         <f>F27*277.778</f>
         <v>358333619.99999994</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F29">
         <f>F28*0.003412</f>
         <v>1222634.3114399998</v>
       </c>
       <c r="G29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F30" s="12">
         <f>(F21*0.14)/(F29*10^6)</f>
         <v>4.1222464909102436E-6</v>
       </c>
       <c r="G30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F34">
         <v>21.08</v>
       </c>
       <c r="G34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F35">
         <v>0.76</v>
       </c>
       <c r="G35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F36" s="34">
         <f>F34*F35</f>
         <v>16.020799999999998</v>
       </c>
       <c r="G36" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -7090,7 +8723,7 @@
         <v>1.3284</v>
       </c>
       <c r="G37" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -7099,7 +8732,7 @@
         <v>21.282030719999998</v>
       </c>
       <c r="G38" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -7107,7 +8740,7 @@
         <v>1.32</v>
       </c>
       <c r="G39" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -7116,7 +8749,7 @@
         <v>28.092280550399998</v>
       </c>
       <c r="G40" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -7125,7 +8758,7 @@
         <v>4.3553923333953488</v>
       </c>
       <c r="G41" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -7133,7 +8766,7 @@
         <v>277.77800000000002</v>
       </c>
       <c r="G42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -7142,7 +8775,7 @@
         <v>1.5679399856703368E-2</v>
       </c>
       <c r="G43" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -7150,7 +8783,7 @@
         <v>3412.14</v>
       </c>
       <c r="G44" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -7159,12 +8792,12 @@
         <v>4.5951806950193628E-6</v>
       </c>
       <c r="G45" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -7175,99 +8808,99 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F49" s="32">
         <v>6000000</v>
       </c>
       <c r="G49" s="33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F50">
         <v>300</v>
       </c>
       <c r="G50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F51">
         <v>8760</v>
       </c>
       <c r="G51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F52">
         <v>1100</v>
       </c>
       <c r="G52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F54">
         <f>(F3*365)*F52</f>
         <v>106060240.00000001</v>
       </c>
       <c r="G54" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F55" s="34">
         <f>F54*0.003412</f>
         <v>361877.53888000007</v>
       </c>
       <c r="G55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F56" s="12">
         <f>(F49*1.25)/(F55*10^6)</f>
         <v>2.0725243194734525E-5</v>
       </c>
       <c r="G56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
@@ -7278,90 +8911,90 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F60">
         <f>574-184</f>
         <v>390</v>
       </c>
       <c r="G60" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F61">
         <v>3500</v>
       </c>
       <c r="G61" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F62" s="32">
         <v>1500000</v>
       </c>
       <c r="G62" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I62" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F64">
         <f>F61*F62</f>
         <v>5250000000</v>
       </c>
       <c r="G64" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F65">
         <f>F64*0.003412</f>
         <v>17913000</v>
       </c>
       <c r="G65" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F66" s="25">
         <f>F60*F62</f>
         <v>585000000</v>
       </c>
       <c r="G66" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F67" s="12">
         <f>F66/(F65*10^6)</f>
         <v>3.265784625690839E-5</v>
       </c>
       <c r="G67" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -7401,96 +9034,96 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="D8" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="E8" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="F8" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="G8" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="H8" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="I8" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="I8" s="26" t="s">
-        <v>122</v>
-      </c>
       <c r="J8" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K8" s="27"/>
       <c r="L8" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M8" s="27"/>
       <c r="N8" s="28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O8" s="27"/>
       <c r="P8" s="29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q8" s="27"/>
       <c r="R8" s="29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="S8" s="27"/>
       <c r="T8" s="29" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="U8" s="27"/>
       <c r="V8" s="27"/>
       <c r="W8" s="29" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D9">
         <v>0.3</v>
@@ -7540,10 +9173,10 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -7593,10 +9226,10 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11">
         <v>350</v>
@@ -7646,10 +9279,10 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D12">
         <v>500</v>
@@ -7699,10 +9332,10 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13">
         <v>0.35</v>
@@ -7752,10 +9385,10 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14">
         <v>1.8</v>
@@ -7805,10 +9438,10 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
         <v>109</v>
-      </c>
-      <c r="C15" t="s">
-        <v>110</v>
       </c>
       <c r="D15">
         <v>0.35</v>
@@ -7858,10 +9491,10 @@
     </row>
     <row r="16" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" t="s">
         <v>111</v>
-      </c>
-      <c r="C16" t="s">
-        <v>112</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -7882,7 +9515,7 @@
         <v>1000</v>
       </c>
       <c r="J16" s="21">
-        <f t="shared" ref="J16:J19" si="5">AVERAGE(D16,E16)</f>
+        <f>AVERAGE(D16,E16)</f>
         <v>26.5</v>
       </c>
       <c r="L16" s="21">
@@ -7911,10 +9544,10 @@
     </row>
     <row r="17" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17">
         <v>50</v>
@@ -7935,7 +9568,7 @@
         <v>1000</v>
       </c>
       <c r="J17" s="21">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(D17,E17)</f>
         <v>775</v>
       </c>
       <c r="L17" s="21">
@@ -7964,10 +9597,10 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -7988,7 +9621,7 @@
         <v>1000</v>
       </c>
       <c r="J18" s="21">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(D18,E18)</f>
         <v>91.5</v>
       </c>
       <c r="L18" s="21">
@@ -8017,10 +9650,10 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D19">
         <v>180</v>
@@ -8041,7 +9674,7 @@
         <v>1000</v>
       </c>
       <c r="J19" s="21">
-        <f t="shared" si="5"/>
+        <f>AVERAGE(D19,E19)</f>
         <v>840</v>
       </c>
       <c r="L19" s="21">
@@ -8073,7 +9706,7 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N21" s="21"/>
       <c r="P21" s="21"/>
@@ -8089,7 +9722,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="N22" s="21"/>
       <c r="P22" s="21"/>
@@ -8107,24 +9740,24 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C23" s="49" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="49" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G23" s="49"/>
       <c r="H23" s="49"/>
       <c r="I23" s="49" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J23" s="49"/>
       <c r="K23" s="49"/>
       <c r="L23" s="49"/>
       <c r="M23" s="49"/>
       <c r="N23" s="50" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
@@ -8132,7 +9765,7 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C24" s="68" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D24" s="69"/>
       <c r="E24" s="70"/>
@@ -8160,7 +9793,7 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C25" s="68" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D25" s="69"/>
       <c r="E25" s="70"/>
@@ -8188,7 +9821,7 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C26" s="68" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D26" s="69"/>
       <c r="E26" s="70"/>
@@ -8216,7 +9849,7 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C27" s="68" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D27" s="69"/>
       <c r="E27" s="70"/>
@@ -8244,7 +9877,7 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C28" s="68" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D28" s="69"/>
       <c r="E28" s="70"/>
@@ -8280,97 +9913,97 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="G32" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U32" s="9"/>
       <c r="W32" s="9"/>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D33" s="21">
         <v>502</v>
       </c>
       <c r="E33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="T33" s="9"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" s="21">
         <v>250</v>
       </c>
       <c r="E34" t="s">
+        <v>263</v>
+      </c>
+      <c r="G34" s="15" t="s">
         <v>264</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>265</v>
       </c>
       <c r="T34" s="9"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D35" s="21">
         <f>D34/1.341</f>
         <v>186.42803877703207</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D36" s="21">
         <v>2080</v>
       </c>
       <c r="E36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D37" s="21">
         <f>D35*0.003412*D36</f>
         <v>1323.0723340790455</v>
       </c>
       <c r="E37" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D38" s="12">
         <f>(D33*D35)/(D37*10^6)</f>
         <v>7.0734511678239686E-5</v>
       </c>
       <c r="E38" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -8412,7 +10045,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -8423,12 +10056,12 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -8436,94 +10069,94 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G5" s="1"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D6">
         <f>AVERAGE(760,1000)</f>
         <v>880</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D7">
         <f>AVERAGE(373.1,597)</f>
         <v>485.05</v>
       </c>
       <c r="E7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D11">
         <f>AVERAGE(975,1200)</f>
         <v>1087.5</v>
       </c>
       <c r="E11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12">
         <f>AVERAGE(1492.5,2238.8)</f>
         <v>1865.65</v>
       </c>
       <c r="E12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D15">
         <v>1.5</v>
       </c>
       <c r="E15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D16">
         <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G18">
         <f>(D6)*(1.5*1000000)</f>
@@ -8532,7 +10165,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G19">
         <f>(1.5*1000000)*(0.7*8760)</f>
@@ -8541,7 +10174,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G20">
         <f>G19*3412</f>
@@ -8550,7 +10183,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G21">
         <f>G18/G20</f>
@@ -8559,7 +10192,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G22">
         <f>(D7*(1.5*1000000))/G20</f>
@@ -8568,7 +10201,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G24">
         <f>(D11)*(1.5*1000000)</f>
@@ -8577,7 +10210,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G25">
         <f>(1.5*1000000)*(0.7*8760)</f>
@@ -8586,7 +10219,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G26">
         <f>G25*3412</f>
@@ -8595,7 +10228,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G27">
         <f>G24/G26</f>
@@ -8604,7 +10237,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G28">
         <f>(D12*(1.5*1000000))/G26</f>
@@ -8613,12 +10246,12 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G32" s="12">
         <f>(G21*0.75)+(G27*0.25)</f>
@@ -8627,7 +10260,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G33" s="9">
         <f>G32*0.6</f>
@@ -8639,7 +10272,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G35" s="9">
         <f>(G22*0.75)+(G28*0.25)</f>
@@ -8652,6 +10285,1006 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1BBBC2-333F-45D7-87D4-C9F757AF344C}">
+  <dimension ref="A1:W39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>453</v>
+      </c>
+      <c r="P1" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F3" t="s">
+        <v>473</v>
+      </c>
+      <c r="G3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H3" t="s">
+        <v>473</v>
+      </c>
+      <c r="I3" t="s">
+        <v>473</v>
+      </c>
+      <c r="J3" t="s">
+        <v>473</v>
+      </c>
+      <c r="K3" t="s">
+        <v>474</v>
+      </c>
+      <c r="L3" t="s">
+        <v>474</v>
+      </c>
+      <c r="M3" t="s">
+        <v>474</v>
+      </c>
+      <c r="N3" t="s">
+        <v>478</v>
+      </c>
+      <c r="O3" t="s">
+        <v>478</v>
+      </c>
+      <c r="P3" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>486</v>
+      </c>
+      <c r="R3" t="s">
+        <v>486</v>
+      </c>
+      <c r="S3" t="s">
+        <v>486</v>
+      </c>
+      <c r="T3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>465</v>
+      </c>
+      <c r="D4" t="s">
+        <v>466</v>
+      </c>
+      <c r="E4" t="s">
+        <v>467</v>
+      </c>
+      <c r="F4" t="s">
+        <v>466</v>
+      </c>
+      <c r="G4" t="s">
+        <v>466</v>
+      </c>
+      <c r="H4" t="s">
+        <v>465</v>
+      </c>
+      <c r="I4" t="s">
+        <v>468</v>
+      </c>
+      <c r="J4" t="s">
+        <v>468</v>
+      </c>
+      <c r="K4" t="s">
+        <v>475</v>
+      </c>
+      <c r="L4" t="s">
+        <v>468</v>
+      </c>
+      <c r="M4" t="s">
+        <v>468</v>
+      </c>
+      <c r="N4" t="s">
+        <v>465</v>
+      </c>
+      <c r="O4" t="s">
+        <v>465</v>
+      </c>
+      <c r="P4" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>465</v>
+      </c>
+      <c r="R4" t="s">
+        <v>465</v>
+      </c>
+      <c r="S4" t="s">
+        <v>490</v>
+      </c>
+      <c r="T4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D5" t="s">
+        <v>458</v>
+      </c>
+      <c r="E5" t="s">
+        <v>459</v>
+      </c>
+      <c r="F5" t="s">
+        <v>460</v>
+      </c>
+      <c r="G5" t="s">
+        <v>461</v>
+      </c>
+      <c r="H5" t="s">
+        <v>462</v>
+      </c>
+      <c r="I5" t="s">
+        <v>464</v>
+      </c>
+      <c r="J5" t="s">
+        <v>469</v>
+      </c>
+      <c r="K5" t="s">
+        <v>471</v>
+      </c>
+      <c r="L5" t="s">
+        <v>476</v>
+      </c>
+      <c r="M5" t="s">
+        <v>477</v>
+      </c>
+      <c r="N5" t="s">
+        <v>479</v>
+      </c>
+      <c r="O5" t="s">
+        <v>479</v>
+      </c>
+      <c r="P5" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>488</v>
+      </c>
+      <c r="R5" t="s">
+        <v>489</v>
+      </c>
+      <c r="S5" t="s">
+        <v>491</v>
+      </c>
+      <c r="T5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B6" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6">
+        <v>1.3</v>
+      </c>
+      <c r="D6">
+        <v>5.15</v>
+      </c>
+      <c r="E6">
+        <v>7.48</v>
+      </c>
+      <c r="F6">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G6">
+        <v>11.84</v>
+      </c>
+      <c r="H6">
+        <f>12.98/4</f>
+        <v>3.2450000000000001</v>
+      </c>
+      <c r="I6">
+        <f>124.94/10</f>
+        <v>12.494</v>
+      </c>
+      <c r="J6">
+        <f>172.75/25</f>
+        <v>6.91</v>
+      </c>
+      <c r="K6">
+        <f>5.21</f>
+        <v>5.21</v>
+      </c>
+      <c r="L6">
+        <f>206.09/40</f>
+        <v>5.1522500000000004</v>
+      </c>
+      <c r="M6">
+        <f>28.85/6</f>
+        <v>4.8083333333333336</v>
+      </c>
+      <c r="N6">
+        <f>16.57/3</f>
+        <v>5.5233333333333334</v>
+      </c>
+      <c r="O6">
+        <f>198.86/12/3</f>
+        <v>5.52388888888889</v>
+      </c>
+      <c r="P6">
+        <v>15.99</v>
+      </c>
+      <c r="Q6">
+        <v>27.95</v>
+      </c>
+      <c r="R6">
+        <v>39.950000000000003</v>
+      </c>
+      <c r="S6">
+        <v>17</v>
+      </c>
+      <c r="T6">
+        <v>12</v>
+      </c>
+      <c r="W6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B7" s="74" t="s">
+        <v>455</v>
+      </c>
+      <c r="C7">
+        <v>40</v>
+      </c>
+      <c r="D7">
+        <v>6.5</v>
+      </c>
+      <c r="E7">
+        <v>7.5</v>
+      </c>
+      <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>15</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>40</v>
+      </c>
+      <c r="J7">
+        <v>11</v>
+      </c>
+      <c r="K7">
+        <v>13</v>
+      </c>
+      <c r="L7">
+        <v>54</v>
+      </c>
+      <c r="M7">
+        <v>32</v>
+      </c>
+      <c r="N7">
+        <v>23</v>
+      </c>
+      <c r="O7">
+        <v>23</v>
+      </c>
+      <c r="P7">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>1000</v>
+      </c>
+      <c r="R7">
+        <v>1000</v>
+      </c>
+      <c r="S7">
+        <v>70</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B8" s="74" t="s">
+        <v>456</v>
+      </c>
+      <c r="C8">
+        <v>225</v>
+      </c>
+      <c r="D8">
+        <v>520</v>
+      </c>
+      <c r="E8">
+        <v>650</v>
+      </c>
+      <c r="F8">
+        <v>1000</v>
+      </c>
+      <c r="G8">
+        <v>1200</v>
+      </c>
+      <c r="H8">
+        <v>800</v>
+      </c>
+      <c r="I8">
+        <v>5500</v>
+      </c>
+      <c r="J8">
+        <v>1800</v>
+      </c>
+      <c r="K8">
+        <v>800</v>
+      </c>
+      <c r="L8">
+        <v>5000</v>
+      </c>
+      <c r="M8">
+        <v>3050</v>
+      </c>
+      <c r="N8">
+        <v>1600</v>
+      </c>
+      <c r="O8">
+        <v>1600</v>
+      </c>
+      <c r="P8">
+        <v>8500</v>
+      </c>
+      <c r="Q8">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B9" s="74" t="s">
+        <v>457</v>
+      </c>
+      <c r="C9">
+        <v>2500</v>
+      </c>
+      <c r="D9">
+        <v>25000</v>
+      </c>
+      <c r="E9">
+        <v>25000</v>
+      </c>
+      <c r="F9">
+        <v>25000</v>
+      </c>
+      <c r="G9">
+        <v>25000</v>
+      </c>
+      <c r="H9">
+        <v>15000</v>
+      </c>
+      <c r="I9">
+        <v>50000</v>
+      </c>
+      <c r="J9">
+        <v>50000</v>
+      </c>
+      <c r="K9">
+        <v>12000</v>
+      </c>
+      <c r="L9">
+        <v>24000</v>
+      </c>
+      <c r="M9">
+        <v>24000</v>
+      </c>
+      <c r="N9">
+        <v>12000</v>
+      </c>
+      <c r="O9">
+        <v>12000</v>
+      </c>
+      <c r="P9">
+        <v>15000</v>
+      </c>
+      <c r="Q9">
+        <v>10000</v>
+      </c>
+      <c r="R9">
+        <v>5000</v>
+      </c>
+      <c r="S9">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B10" s="74" t="s">
+        <v>463</v>
+      </c>
+      <c r="D10">
+        <v>50</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+      <c r="F10">
+        <v>75</v>
+      </c>
+      <c r="G10">
+        <v>90</v>
+      </c>
+      <c r="H10">
+        <v>60</v>
+      </c>
+      <c r="I10">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s">
+        <v>470</v>
+      </c>
+      <c r="N10">
+        <v>100</v>
+      </c>
+      <c r="O10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <f>C6/C7</f>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="D11">
+        <f t="shared" ref="D11:T11" si="0">D6/D7</f>
+        <v>0.79230769230769238</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>0.9973333333333334</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>0.69166666666666676</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>0.78933333333333333</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>0.32450000000000001</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>0.31235000000000002</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>0.62818181818181817</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="0"/>
+        <v>0.40076923076923077</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="0"/>
+        <v>9.5412037037037045E-2</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="0"/>
+        <v>0.15026041666666667</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>0.2401449275362319</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>0.24016908212560392</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>0.15990000000000001</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="0"/>
+        <v>2.7949999999999999E-2</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="0"/>
+        <v>3.9949999999999999E-2</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="0"/>
+        <v>0.24285714285714285</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="0"/>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>497</v>
+      </c>
+      <c r="E14" t="s">
+        <v>498</v>
+      </c>
+      <c r="F14" t="s">
+        <v>455</v>
+      </c>
+      <c r="H14" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B15" s="74" t="s">
+        <v>472</v>
+      </c>
+      <c r="C15" s="34">
+        <f>AVERAGEIFS($C$6:$T$6,$C$3:$T$3,$B15)</f>
+        <v>1.3</v>
+      </c>
+      <c r="D15" s="21">
+        <f>AVERAGEIFS($C$9:$T$9,$C$3:$T$3,$B15)</f>
+        <v>2500</v>
+      </c>
+      <c r="E15" s="21">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B15)*$O$19/1000*$O$21</f>
+        <v>377565.42095238098</v>
+      </c>
+      <c r="F15" s="21">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B15)</f>
+        <v>40</v>
+      </c>
+      <c r="G15" s="21"/>
+      <c r="H15" t="s">
+        <v>473</v>
+      </c>
+      <c r="I15" s="43">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="J15" s="21">
+        <f>I15*D16</f>
+        <v>20025.714285714286</v>
+      </c>
+      <c r="K15" s="21">
+        <f>I15*E16</f>
+        <v>89677.181267918349</v>
+      </c>
+      <c r="L15">
+        <f>C16*I15</f>
+        <v>5.1618839999999997</v>
+      </c>
+      <c r="M15">
+        <f>I15*F16</f>
+        <v>9.500571428571428</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B16" s="74" t="s">
+        <v>473</v>
+      </c>
+      <c r="C16" s="34">
+        <f t="shared" ref="C16:C19" si="1">AVERAGEIFS($C$6:$T$6,$C$3:$T$3,$B16)</f>
+        <v>7.9169999999999998</v>
+      </c>
+      <c r="D16" s="21">
+        <f t="shared" ref="D16:D19" si="2">AVERAGEIFS($C$9:$T$9,$C$3:$T$3,$B16)</f>
+        <v>30714.285714285714</v>
+      </c>
+      <c r="E16" s="21">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B16)*$O$19/1000*$O$21</f>
+        <v>137541.68906122446</v>
+      </c>
+      <c r="F16" s="21">
+        <f t="shared" ref="F16:F19" si="3">AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B16)</f>
+        <v>14.571428571428571</v>
+      </c>
+      <c r="G16" s="21"/>
+      <c r="H16" t="s">
+        <v>482</v>
+      </c>
+      <c r="I16" s="43">
+        <v>0.13650000000000001</v>
+      </c>
+      <c r="J16" s="21">
+        <f>I16*D17</f>
+        <v>2730</v>
+      </c>
+      <c r="K16" s="21">
+        <f>I16*E17</f>
+        <v>42518.585966999999</v>
+      </c>
+      <c r="L16">
+        <f>I16*C17</f>
+        <v>0.69026154166666676</v>
+      </c>
+      <c r="M16">
+        <f>I16*F17</f>
+        <v>4.5045000000000002</v>
+      </c>
+      <c r="O16" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="74" t="s">
+        <v>474</v>
+      </c>
+      <c r="C17" s="34">
+        <f t="shared" si="1"/>
+        <v>5.056861111111111</v>
+      </c>
+      <c r="D17" s="21">
+        <f t="shared" si="2"/>
+        <v>20000</v>
+      </c>
+      <c r="E17" s="21">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B17)*$O$19/1000*$O$21</f>
+        <v>311491.47228571423</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="H17" t="s">
+        <v>483</v>
+      </c>
+      <c r="I17" s="43">
+        <v>0.20050000000000001</v>
+      </c>
+      <c r="J17" s="21">
+        <f>I17*D19</f>
+        <v>1804.5</v>
+      </c>
+      <c r="K17" s="21">
+        <f>I17*E19</f>
+        <v>859216.18932580936</v>
+      </c>
+      <c r="L17">
+        <f>I17*C19</f>
+        <v>4.5268889999999997</v>
+      </c>
+      <c r="M17">
+        <f>I17*F19</f>
+        <v>91.027000000000001</v>
+      </c>
+      <c r="O17">
+        <v>9</v>
+      </c>
+      <c r="P17" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="74" t="s">
+        <v>478</v>
+      </c>
+      <c r="C18" s="34">
+        <f t="shared" si="1"/>
+        <v>5.5236111111111121</v>
+      </c>
+      <c r="D18" s="21">
+        <f t="shared" si="2"/>
+        <v>12000</v>
+      </c>
+      <c r="E18" s="21">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B18)*$O$19/1000*$O$21</f>
+        <v>217100.11704761902</v>
+      </c>
+      <c r="F18" s="21">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="H18" t="s">
+        <v>484</v>
+      </c>
+      <c r="I18" s="43">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="J18" s="21">
+        <f>I18*D16</f>
+        <v>337.85714285714283</v>
+      </c>
+      <c r="K18" s="21">
+        <f>I18*E16</f>
+        <v>1512.9585796734689</v>
+      </c>
+      <c r="L18">
+        <f>I18*C16</f>
+        <v>8.7086999999999998E-2</v>
+      </c>
+      <c r="M18">
+        <f>I18*F16</f>
+        <v>0.16028571428571428</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="74" t="s">
+        <v>486</v>
+      </c>
+      <c r="C19" s="34">
+        <f t="shared" si="1"/>
+        <v>22.577999999999999</v>
+      </c>
+      <c r="D19" s="21">
+        <f t="shared" si="2"/>
+        <v>9000</v>
+      </c>
+      <c r="E19" s="21">
+        <f>AVERAGEIFS($C$7:$T$7,$C$3:$T$3,$B19)*$O$19/1000*$O$21</f>
+        <v>4285367.527809523</v>
+      </c>
+      <c r="F19" s="21">
+        <f t="shared" si="3"/>
+        <v>454</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="J19" s="47">
+        <f>SUM(J15:J18)</f>
+        <v>24898.071428571428</v>
+      </c>
+      <c r="K19" s="47">
+        <f>SUM(K15:K18)</f>
+        <v>992924.91514040111</v>
+      </c>
+      <c r="L19" s="75">
+        <f>SUM(L15:L18)</f>
+        <v>10.466121541666666</v>
+      </c>
+      <c r="M19" s="47">
+        <f>SUM(M15:M18)</f>
+        <v>105.19235714285715</v>
+      </c>
+      <c r="O19" s="47">
+        <f>J19/9</f>
+        <v>2766.4523809523807</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J20" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="L20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O21">
+        <v>3412</v>
+      </c>
+      <c r="P21" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O23" s="76">
+        <f>L19/K19</f>
+        <v>1.0540697873601793E-5</v>
+      </c>
+      <c r="P23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" s="43">
+        <f>0.35</f>
+        <v>0.35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <f>O23*B27</f>
+        <v>3.6892442557606274E-6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>503</v>
+      </c>
+      <c r="C32" t="s">
+        <v>504</v>
+      </c>
+      <c r="D32" t="s">
+        <v>505</v>
+      </c>
+      <c r="E32" t="s">
+        <v>506</v>
+      </c>
+      <c r="F32" t="s">
+        <v>507</v>
+      </c>
+      <c r="G32" t="s">
+        <v>508</v>
+      </c>
+      <c r="H32" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33">
+        <v>3579</v>
+      </c>
+      <c r="C33">
+        <v>649</v>
+      </c>
+      <c r="D33">
+        <v>849</v>
+      </c>
+      <c r="E33">
+        <v>926</v>
+      </c>
+      <c r="F33">
+        <v>399.99</v>
+      </c>
+      <c r="G33">
+        <v>1299</v>
+      </c>
+      <c r="H33">
+        <v>999</v>
+      </c>
+      <c r="I33" s="21">
+        <f>AVERAGE(Lighting!B33:H33)</f>
+        <v>1242.9985714285715</v>
+      </c>
+      <c r="J33" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>455</v>
+      </c>
+      <c r="B34">
+        <v>10000</v>
+      </c>
+      <c r="C34">
+        <v>5300</v>
+      </c>
+      <c r="D34">
+        <v>7500</v>
+      </c>
+      <c r="E34">
+        <v>9500</v>
+      </c>
+      <c r="F34">
+        <v>5600</v>
+      </c>
+      <c r="G34">
+        <v>13000</v>
+      </c>
+      <c r="H34">
+        <f>AVERAGE(10000,8000)</f>
+        <v>9000</v>
+      </c>
+      <c r="I34" s="21">
+        <f>AVERAGE(Lighting!B34:H34)</f>
+        <v>8557.1428571428569</v>
+      </c>
+      <c r="J34" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <f>B33/B34</f>
+        <v>0.3579</v>
+      </c>
+      <c r="C35">
+        <f t="shared" ref="C35:H35" si="4">C33/C34</f>
+        <v>0.12245283018867925</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="4"/>
+        <v>0.1132</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="4"/>
+        <v>9.747368421052631E-2</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="4"/>
+        <v>7.142678571428572E-2</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="4"/>
+        <v>9.992307692307692E-2</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="4"/>
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I37" s="21">
+        <f>I33*M19/I34</f>
+        <v>15.280094283412833</v>
+      </c>
+      <c r="J37" t="s">
+        <v>65</v>
+      </c>
+      <c r="K37" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I38">
+        <f>I37/K19*B27</f>
+        <v>5.3861403995872857E-6</v>
+      </c>
+      <c r="K38" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I39" s="76">
+        <f>I38+B28</f>
+        <v>9.0753846553479132E-6</v>
+      </c>
+      <c r="K39" t="s">
+        <v>515</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5463D77-55A0-4A3F-A167-AF9495B144EE}">
   <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8664,7 +11297,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -8676,184 +11309,184 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E3" s="39">
         <f>2758*1.03</f>
         <v>2840.7400000000002</v>
       </c>
       <c r="F3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E4">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5">
         <f>18*365</f>
         <v>6570</v>
       </c>
       <c r="F5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E7">
         <f>E4*E5</f>
         <v>118260</v>
       </c>
       <c r="F7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E8">
         <f>E7*0.003412</f>
         <v>403.50312000000002</v>
       </c>
       <c r="F8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E9" s="12">
         <f>E3/(E8*10^6)</f>
         <v>7.0401933942914745E-6</v>
       </c>
       <c r="F9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B16" s="8">
         <v>862500</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B17" s="8">
         <v>1500000</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B18" s="8">
         <f>AVERAGE(B16,B17)</f>
         <v>1181250</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="32">
         <v>8760</v>
       </c>
       <c r="C20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B21" s="32">
         <v>6051100</v>
       </c>
       <c r="C21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B23">
         <f>B20*B21</f>
         <v>53007636000</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B24" s="12">
         <f>B18/B23</f>
         <v>2.2284525195577483E-5</v>
       </c>
       <c r="C24" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -8864,448 +11497,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B88B710-1DAB-47E6-AE70-A12C5CA0B896}">
-  <dimension ref="A1:P83"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
-        <v>377</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="54">
-        <v>0.57060049240377109</v>
-      </c>
-      <c r="B2" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="54">
-        <f>4000/15</f>
-        <v>266.66666666666669</v>
-      </c>
-      <c r="B3" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="56">
-        <f>AVERAGE(O29,H39,H83)</f>
-        <v>8.2719018162705823E-4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="56">
-        <f>AVERAGE(O30,H40,H82)</f>
-        <v>3.1381977460259781E-3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
-        <v>382</v>
-      </c>
-      <c r="D28" t="s">
-        <v>384</v>
-      </c>
-      <c r="E28" t="s">
-        <v>385</v>
-      </c>
-      <c r="F28" t="s">
-        <v>386</v>
-      </c>
-      <c r="G28" t="s">
-        <v>387</v>
-      </c>
-      <c r="H28" t="s">
-        <v>391</v>
-      </c>
-      <c r="I28" t="s">
-        <v>409</v>
-      </c>
-      <c r="M28" t="s">
-        <v>413</v>
-      </c>
-      <c r="N28" t="s">
-        <v>414</v>
-      </c>
-      <c r="O28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" t="s">
-        <v>379</v>
-      </c>
-      <c r="C29">
-        <v>17000</v>
-      </c>
-      <c r="D29">
-        <v>7.1</v>
-      </c>
-      <c r="F29">
-        <v>9.5</v>
-      </c>
-      <c r="G29" s="21">
-        <f>D29*About!$A$144</f>
-        <v>983279</v>
-      </c>
-      <c r="H29" s="21">
-        <f>G29/F29</f>
-        <v>103503.05263157895</v>
-      </c>
-      <c r="I29">
-        <v>250</v>
-      </c>
-      <c r="L29" t="s">
-        <v>376</v>
-      </c>
-      <c r="M29">
-        <f>AVERAGE(C29:C31)*About!A149</f>
-        <v>21966.588645333242</v>
-      </c>
-      <c r="N29">
-        <f>AVERAGE(H29:H31)*A3</f>
-        <v>27574616.079328757</v>
-      </c>
-      <c r="O29" s="55">
-        <f>M29/N29</f>
-        <v>7.9662355342094654E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" t="s">
-        <v>380</v>
-      </c>
-      <c r="C30">
-        <v>17000</v>
-      </c>
-      <c r="D30">
-        <v>7.1</v>
-      </c>
-      <c r="F30">
-        <v>10</v>
-      </c>
-      <c r="G30" s="21">
-        <f>D30*About!$A$144</f>
-        <v>983279</v>
-      </c>
-      <c r="H30" s="21">
-        <f t="shared" ref="H30:H31" si="0">G30/F30</f>
-        <v>98327.9</v>
-      </c>
-      <c r="I30">
-        <v>250</v>
-      </c>
-      <c r="L30" t="s">
-        <v>412</v>
-      </c>
-      <c r="M30">
-        <f>C32*About!A149</f>
-        <v>43148.65626761887</v>
-      </c>
-      <c r="N30">
-        <f>N29*(1-A2)</f>
-        <v>11840526.566618824</v>
-      </c>
-      <c r="O30" s="55">
-        <f>M30/N30</f>
-        <v>3.6441501165383038E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>381</v>
-      </c>
-      <c r="C31">
-        <v>50000</v>
-      </c>
-      <c r="D31">
-        <v>18</v>
-      </c>
-      <c r="F31">
-        <v>23</v>
-      </c>
-      <c r="G31" s="21">
-        <f>D31*About!$A$144</f>
-        <v>2492820</v>
-      </c>
-      <c r="H31" s="21">
-        <f t="shared" si="0"/>
-        <v>108383.47826086957</v>
-      </c>
-      <c r="I31">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>383</v>
-      </c>
-      <c r="C32">
-        <v>55000</v>
-      </c>
-      <c r="E32">
-        <v>24</v>
-      </c>
-      <c r="F32">
-        <v>16</v>
-      </c>
-      <c r="G32" s="21">
-        <f>E32*About!$A$146</f>
-        <v>81891.360000000001</v>
-      </c>
-      <c r="H32" s="21"/>
-      <c r="I32">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C33">
-        <f>C32/AVERAGE(C29:C31)</f>
-        <v>1.9642857142857142</v>
-      </c>
-      <c r="H33" s="21"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E34">
-        <f>E32/38.1</f>
-        <v>0.62992125984251968</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C38" t="s">
-        <v>393</v>
-      </c>
-      <c r="D38" t="s">
-        <v>223</v>
-      </c>
-      <c r="E38" t="s">
-        <v>408</v>
-      </c>
-      <c r="F38" t="s">
-        <v>416</v>
-      </c>
-      <c r="G38" t="s">
-        <v>418</v>
-      </c>
-      <c r="H38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>394</v>
-      </c>
-      <c r="C39">
-        <v>2940</v>
-      </c>
-      <c r="D39">
-        <v>545</v>
-      </c>
-      <c r="E39">
-        <f>37500</f>
-        <v>37500</v>
-      </c>
-      <c r="F39" s="21">
-        <f>AVERAGE(60400,120900,214300)</f>
-        <v>131866.66666666666</v>
-      </c>
-      <c r="G39" s="21">
-        <f>F39*$A$3</f>
-        <v>35164444.444444448</v>
-      </c>
-      <c r="H39" s="55">
-        <f>E39*About!$A$150/G39</f>
-        <v>9.0358045924813471E-4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>395</v>
-      </c>
-      <c r="C40">
-        <v>113</v>
-      </c>
-      <c r="D40">
-        <v>995</v>
-      </c>
-      <c r="E40" s="21">
-        <f>AVERAGE(58000,74999)</f>
-        <v>66499.5</v>
-      </c>
-      <c r="F40" s="21">
-        <f>F39*(1-A2)</f>
-        <v>56623.481735022717</v>
-      </c>
-      <c r="G40" s="21">
-        <f>F40*$A$3</f>
-        <v>15099595.129339391</v>
-      </c>
-      <c r="H40" s="55">
-        <f>E40*About!$A$150/G40</f>
-        <v>3.7315769386037706E-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F41" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="24" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C54" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>397</v>
-      </c>
-      <c r="C55" s="19">
-        <v>0.54</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
-        <v>398</v>
-      </c>
-      <c r="C56" s="19">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C57" s="19"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="24" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C81" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B82" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C82">
-        <v>28398</v>
-      </c>
-      <c r="D82">
-        <v>250</v>
-      </c>
-      <c r="G82" s="21">
-        <f>G83*(1-A2)</f>
-        <v>11801531.10292552</v>
-      </c>
-      <c r="H82" s="55">
-        <f>C82*About!$A$150/G82</f>
-        <v>2.0388661829358595E-3</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B83" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C83">
-        <v>25345</v>
-      </c>
-      <c r="D83">
-        <v>250</v>
-      </c>
-      <c r="E83">
-        <f>AVERAGE(144,228.1)</f>
-        <v>186.05</v>
-      </c>
-      <c r="G83" s="21">
-        <f>E83*About!A144*A3/D83</f>
-        <v>27483802.133333337</v>
-      </c>
-      <c r="H83" s="55">
-        <f>C83*About!$A$150/G83</f>
-        <v>7.8136653221209343E-4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" enabled="0" method="" siteId="{c7ef1c8b-ba63-4702-8e74-5094387a97de}" removed="1"/>

--- a/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
+++ b/InputData/indst/IECCpUAEU/Indst Eqpt Cap Cost per Unit Ann E Use.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\IECCpUAEU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code Repositories\eps-us\InputData\indst\IECCpUAEU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{B95E0DDC-D38A-4AEC-9FED-2EF80C57FCC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01430DE3-BD9E-441C-B0DE-36E1FFE3581D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28965" yWindow="-165" windowWidth="29130" windowHeight="17610" tabRatio="762" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
+    <workbookView xWindow="9465" yWindow="555" windowWidth="29820" windowHeight="22665" tabRatio="762" xr2:uid="{6A73F6BA-E2AF-4EFC-B7D0-AD586970A910}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <sheet name="IECCpUAEU-mobile" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -67,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="540">
   <si>
     <t>Sources:</t>
   </si>
@@ -129,18 +128,12 @@
     <t>Industrial heat pumps</t>
   </si>
   <si>
-    <t>Emerson</t>
-  </si>
-  <si>
     <t>Industrial Heat Pumps</t>
   </si>
   <si>
     <t>Industrial heat pumps cost per unit heat delivered</t>
   </si>
   <si>
-    <t>Natural gas boilers</t>
-  </si>
-  <si>
     <t>BTU</t>
   </si>
   <si>
@@ -150,9 +143,6 @@
     <t>Unit:  $/(BTU/yr) - dollars of capital cost for equipment per BTU consumed annually by that equipment</t>
   </si>
   <si>
-    <t>Natural gas boiler costs</t>
-  </si>
-  <si>
     <t>Industrial fossil fuel boilers</t>
   </si>
   <si>
@@ -192,9 +182,6 @@
     <t>Boiler cost ($)</t>
   </si>
   <si>
-    <t>Three fuel type industrial boiler costs</t>
-  </si>
-  <si>
     <t>IRENA</t>
   </si>
   <si>
@@ -204,12 +191,6 @@
     <t>Remap Technology and Performance Assumptions (for year 2030)</t>
   </si>
   <si>
-    <t>We use NREL's natural gas boiler cost rather than IRENA's cost because it is based on precise figures, while IRENA used round numbers</t>
-  </si>
-  <si>
-    <t>for their assumptions.</t>
-  </si>
-  <si>
     <t>Annual heat output</t>
   </si>
   <si>
@@ -889,15 +870,6 @@
   </si>
   <si>
     <t>fire tube boiler</t>
-  </si>
-  <si>
-    <t>average</t>
-  </si>
-  <si>
-    <t>horsepower</t>
-  </si>
-  <si>
-    <t>kW / horsepower</t>
   </si>
   <si>
     <t>annual energy consumption</t>
@@ -1372,12 +1344,6 @@
     <t>Page 16, Figure 1-4</t>
   </si>
   <si>
-    <t>Page 5-7. Capacity factor is based on the average annual operating hours across the three examples, assuming each operates at full capacity.</t>
-  </si>
-  <si>
-    <t>https://web.archive.org/web/20210702173253/https://climate.emerson.com/documents/vilter-heat-pump-white-paper-en-us-5411194.pdf</t>
-  </si>
-  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -1399,9 +1365,6 @@
     <t>Per-BTU/yr CAPEX</t>
   </si>
   <si>
-    <t>$ / power draw</t>
-  </si>
-  <si>
     <t>$ / electricity consumption each year</t>
   </si>
   <si>
@@ -1411,9 +1374,6 @@
     <t>Does not need to be converted using heat pump COP because it is already based on electricity consumption</t>
   </si>
   <si>
-    <t>Cost per annual energy input ($/(BTU/yr))</t>
-  </si>
-  <si>
     <t>Capital cost per BTU energy consumption</t>
   </si>
   <si>
@@ -1637,6 +1597,117 @@
   </si>
   <si>
     <t>total cost per BTU</t>
+  </si>
+  <si>
+    <t>boiler horsepower</t>
+  </si>
+  <si>
+    <t>kW / boiler horsepower</t>
+  </si>
+  <si>
+    <t>Unit conversion ref:</t>
+  </si>
+  <si>
+    <t>https://www.unitconverters.net/power/horsepower-boiler-to-kilowatt.htm</t>
+  </si>
+  <si>
+    <t>2003 USD</t>
+  </si>
+  <si>
+    <t>2003 to 2024 inflation adj.</t>
+  </si>
+  <si>
+    <t>dmnl</t>
+  </si>
+  <si>
+    <t>average cost</t>
+  </si>
+  <si>
+    <t>average cost (inflation adjusted)</t>
+  </si>
+  <si>
+    <t>2024 USD</t>
+  </si>
+  <si>
+    <t>boiler cost</t>
+  </si>
+  <si>
+    <t>2016 USD</t>
+  </si>
+  <si>
+    <t>2016 to 2024 inflation adj.</t>
+  </si>
+  <si>
+    <t>NREL's report was published in 2017. We assume the currency figures are given in 2016 USD, which would have been the latest year for which inflation data were available when the NREL report was published.</t>
+  </si>
+  <si>
+    <t>2015 to 2024 inflation adj.</t>
+  </si>
+  <si>
+    <t>Cost per annual energy input (2024$/(BTU/yr))</t>
+  </si>
+  <si>
+    <t>Cost per annual energy input (2015$/(BTU/yr))</t>
+  </si>
+  <si>
+    <t>NOT USED - State of Michigan 2003 reference for natural gas boiler costs</t>
+  </si>
+  <si>
+    <t>NOT USED - NREL 2017 reference for natural gas boiler costs</t>
+  </si>
+  <si>
+    <t>2024$/(BTU/yr)</t>
+  </si>
+  <si>
+    <t>Three fossil fuel type industrial boiler costs</t>
+  </si>
+  <si>
+    <t>National Renewable Energy Laboratory</t>
+  </si>
+  <si>
+    <t>Electrification Futures Study</t>
+  </si>
+  <si>
+    <t>https://docs.nrel.gov/docs/fy18osti/70485.pdf</t>
+  </si>
+  <si>
+    <t>Page 64, Table 17</t>
+  </si>
+  <si>
+    <t>NOT USED - Included for reference/comparison - natural gas boiler costs</t>
+  </si>
+  <si>
+    <t>Annual operating hours</t>
+  </si>
+  <si>
+    <t>hours / year</t>
+  </si>
+  <si>
+    <t>Copeland (formerly Emerson Climate Technologies)</t>
+  </si>
+  <si>
+    <t>https://media.copeland.com/1da81099-2c21-4ce5-8096-b16d0037b111/VILTER%20Heat%20Pump%20White%20Paper.pdf</t>
+  </si>
+  <si>
+    <t>Page 6-8. Capacity factor is based on the average annual operating hours across the four examples, assuming each operates at full capacity.</t>
+  </si>
+  <si>
+    <t>2024$/kW</t>
+  </si>
+  <si>
+    <t>2024$/(kWh/yr)</t>
+  </si>
+  <si>
+    <t>2024€/kW</t>
+  </si>
+  <si>
+    <t>Currency adj. EUR to USD 2024</t>
+  </si>
+  <si>
+    <t>2024$/2024€</t>
+  </si>
+  <si>
+    <t>€ / power draw</t>
   </si>
 </sst>
 </file>
@@ -1650,10 +1721,10 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="175" formatCode="0.0"/>
-    <numFmt numFmtId="177" formatCode="0.000E+00"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.000E+00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1730,8 +1801,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1806,6 +1883,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1901,7 +1984,7 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2007,6 +2090,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="11" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2016,28 +2120,19 @@
     <xf numFmtId="9" fontId="8" fillId="11" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="8" fillId="11" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="11" borderId="5" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="11" borderId="6" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2208,40 +2303,40 @@
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>3.0882108581950831E-5</c:v>
+                  <c:v>3.6314488500484264E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4986595988547842E-5</c:v>
+                  <c:v>1.9822770514052231E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5989491110961776E-5</c:v>
+                  <c:v>6.9746785142035624E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4986595988547842E-5</c:v>
+                  <c:v>1.9822770514052231E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.3984236666442662E-5</c:v>
+                  <c:v>1.0462017771305345E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.3984236666442662E-5</c:v>
+                  <c:v>1.0462017771305345E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.3984236666442662E-5</c:v>
+                  <c:v>1.0462017771305345E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2327,40 +2422,40 @@
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>3.0882108581950831E-5</c:v>
+                  <c:v>3.6314488500484264E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4986595988547842E-5</c:v>
+                  <c:v>1.9822770514052231E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5989491110961776E-5</c:v>
+                  <c:v>6.9746785142035624E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4986595988547842E-5</c:v>
+                  <c:v>1.9822770514052231E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.3984236666442662E-5</c:v>
+                  <c:v>1.0462017771305345E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.3984236666442662E-5</c:v>
+                  <c:v>1.0462017771305345E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.3984236666442662E-5</c:v>
+                  <c:v>1.0462017771305345E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2577,19 +2672,19 @@
                   <c:v>4.5951806950193628E-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.2230751723262388E-5</c:v>
+                  <c:v>3.7087277295840735E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.2230751723262388E-5</c:v>
+                  <c:v>3.7087277295840735E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.2230751723262388E-5</c:v>
+                  <c:v>3.7087277295840735E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.2230751723262388E-5</c:v>
+                  <c:v>3.7087277295840735E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>3.265784625690839E-5</c:v>
@@ -2711,13 +2806,13 @@
                   <c:v>1.8088159747275158E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.7132239620912736E-5</c:v>
+                  <c:v>2.7132239620912743E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.7132239620912736E-5</c:v>
+                  <c:v>2.7132239620912743E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.7132239620912736E-5</c:v>
+                  <c:v>2.7132239620912743E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2927,28 +3022,28 @@
                   <c:v>7.0401933942914745E-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0886792055175448E-5</c:v>
+                  <c:v>3.1780367029653324E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2.2284525195577483E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.0886792055175448E-5</c:v>
+                  <c:v>3.1780367029653324E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3150943145851209E-5</c:v>
+                  <c:v>3.1780367029653324E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.3150943145851209E-5</c:v>
+                  <c:v>3.1780367029653324E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3150943145851209E-5</c:v>
+                  <c:v>3.1780367029653324E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.3150943145851209E-5</c:v>
+                  <c:v>3.1780367029653324E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>3.3426787793366228E-5</c:v>
@@ -3045,40 +3140,40 @@
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>3.0882108581950831E-5</c:v>
+                  <c:v>3.6314488500484264E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.4986595988547842E-5</c:v>
+                  <c:v>1.9822770514052231E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5989491110961776E-5</c:v>
+                  <c:v>6.9746785142035624E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4986595988547842E-5</c:v>
+                  <c:v>1.9822770514052231E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.436004881678272E-6</c:v>
+                  <c:v>1.248100365699585E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.3984236666442662E-5</c:v>
+                  <c:v>1.0462017771305345E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.3984236666442662E-5</c:v>
+                  <c:v>1.0462017771305345E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.3984236666442662E-5</c:v>
+                  <c:v>1.0462017771305345E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3287,40 +3382,40 @@
                 <c:formatCode>0.000E+00</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>4.3468676250759544E-5</c:v>
+                  <c:v>4.5279469556937371E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.2235575980706048E-5</c:v>
+                  <c:v>2.5058031375260608E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.4517407203745931E-5</c:v>
+                  <c:v>2.1512469671493199E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.2235575980706048E-5</c:v>
+                  <c:v>2.5058031375260608E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.0374236958296052E-5</c:v>
+                  <c:v>2.6221008711888631E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.0374236958296052E-5</c:v>
+                  <c:v>2.6221008711888631E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.0374236958296052E-5</c:v>
+                  <c:v>2.6221008711888631E-5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.0374236958296052E-5</c:v>
+                  <c:v>2.6221008711888631E-5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.0751094114861809E-5</c:v>
+                  <c:v>2.62436878164827E-5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.0751094114861809E-5</c:v>
+                  <c:v>2.62436878164827E-5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.0751094114861809E-5</c:v>
+                  <c:v>2.62436878164827E-5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4078,13 +4173,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>582930</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>192405</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>167640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4139,13 +4234,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>548640</xdr:colOff>
-      <xdr:row>118</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>185146</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4754,7 +4849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC3CA314-6128-4FC9-9CED-BF85AF9DB226}">
-  <dimension ref="A1:B150"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="76.42578125" customWidth="1"/>
@@ -4762,7 +4857,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4770,13 +4865,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4788,19 +4883,19 @@
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="58" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4809,12 +4904,12 @@
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="16" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>20</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4824,543 +4919,575 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>428</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>427</v>
+        <v>533</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
-        <v>27</v>
+        <v>523</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>278</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="13">
-        <v>2003</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>279</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>281</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="81" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="16" t="s">
-        <v>41</v>
+      <c r="B24" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>42</v>
+      <c r="B25" s="13">
+        <v>2003</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="13">
-        <v>2016</v>
+      <c r="B26" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>44</v>
+      <c r="B27" s="15" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>43</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="16" t="s">
-        <v>50</v>
+      <c r="B30" s="81" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>51</v>
+        <v>524</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" t="s">
-        <v>52</v>
+      <c r="B32" s="13">
+        <v>2017</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="14">
-        <v>2020</v>
+      <c r="B33" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="16" t="s">
-        <v>79</v>
+        <v>526</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>527</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>80</v>
+      <c r="B37" s="16" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B42" s="16" t="s">
-        <v>99</v>
+      <c r="B40" s="14">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
-        <v>102</v>
+      <c r="B43" s="16" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" s="16" t="s">
-        <v>257</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
-        <v>244</v>
+      <c r="B49" s="16" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="38">
-        <v>2016</v>
+      <c r="B50" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>245</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="15" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="16" t="s">
-        <v>247</v>
+      <c r="B52" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>248</v>
+      <c r="B55" s="16" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" s="38">
-        <v>2013</v>
+      <c r="B56" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" t="s">
-        <v>249</v>
+      <c r="B57" s="38">
+        <v>2016</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" s="15" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="16" t="s">
-        <v>193</v>
+      <c r="B58" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="15" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" s="1" t="s">
-        <v>204</v>
+      <c r="B61" s="16" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
-        <v>195</v>
+      <c r="B63" s="38">
+        <v>2013</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="13">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B65" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="35" t="s">
-        <v>197</v>
+      <c r="B64" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="15" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="35"/>
+      <c r="B67" s="16" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" t="s">
-        <v>169</v>
+      <c r="B68" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" s="13">
+      <c r="B70" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="13">
         <v>2024</v>
       </c>
     </row>
-    <row r="71" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B71" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B72" s="3" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
     </row>
     <row r="73" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B73" s="35" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B74" s="3"/>
+      <c r="B74" s="35"/>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75" s="3" t="s">
-        <v>201</v>
+      <c r="B75" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" s="3" t="s">
-        <v>182</v>
+      <c r="B76" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="77" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B77" s="36">
+      <c r="B77" s="13">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B78" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="35" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="3"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="36">
         <v>44621</v>
       </c>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" s="36" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B79" s="37" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80" s="37"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="13">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B84" s="15" t="s">
-        <v>220</v>
-      </c>
-    </row>
     <row r="85" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B85" s="15"/>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B86" t="s">
-        <v>241</v>
+      <c r="B85" s="36" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B86" s="37" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" s="13">
-        <v>2024</v>
-      </c>
+      <c r="B87" s="37"/>
     </row>
     <row r="88" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B88" t="s">
-        <v>242</v>
+      <c r="B88" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="89" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>243</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="13">
+        <v>2018</v>
       </c>
     </row>
     <row r="91" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B91" s="1" t="s">
-        <v>304</v>
+      <c r="B91" s="15" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B92" t="s">
-        <v>305</v>
-      </c>
+      <c r="B92" s="15"/>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B93" s="13">
-        <v>2019</v>
+      <c r="B93" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="94" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B94" t="s">
-        <v>306</v>
+      <c r="B94" s="13">
+        <v>2024</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B95" s="15" t="s">
-        <v>301</v>
+      <c r="B95" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>307</v>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="99" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B99" s="31" t="s">
-        <v>205</v>
+      <c r="B99" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B100" s="36" t="s">
-        <v>206</v>
+      <c r="B100" s="13">
+        <v>2019</v>
       </c>
     </row>
     <row r="101" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B101" s="36">
+      <c r="B101" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="15" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="31" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B107" s="36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="36">
         <v>38231</v>
       </c>
     </row>
-    <row r="102" spans="2:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B102" s="36" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B103" s="37" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B104" s="36"/>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B105" s="16" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B106" s="15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B107" s="15" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B108" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B110" t="s">
-        <v>128</v>
+    <row r="109" spans="2:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B109" s="36" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B110" s="37" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="111" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B111" t="s">
-        <v>129</v>
-      </c>
+      <c r="B111" s="36"/>
     </row>
     <row r="112" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B112" s="13">
-        <v>2007</v>
+      <c r="B112" s="16" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
-        <v>130</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B114" s="15" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B116" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B118" s="15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B135" s="16" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B136" s="15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B138" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B139" s="15" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A144">
+      <c r="B118" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B119" s="13">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B120" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B125" s="15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B142" s="16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B143" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151">
         <v>138490</v>
       </c>
-      <c r="B144" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A146">
+      <c r="B151" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153">
         <v>3412.14</v>
       </c>
-      <c r="B146" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A149">
+      <c r="B153" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A156">
         <v>0.78452102304761584</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B156" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>0.84730412960844359</v>
+      </c>
+      <c r="B157" t="s">
         <v>409</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A150">
-        <v>0.84730412960844359</v>
-      </c>
-      <c r="B150" t="s">
-        <v>418</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B106" r:id="rId1" xr:uid="{810625CC-59B0-4E09-BD8A-7942EF52112A}"/>
-    <hyperlink ref="B107" r:id="rId2" xr:uid="{DE5DC99A-D169-4E5D-98F4-A0C74D220DA2}"/>
-    <hyperlink ref="B113" r:id="rId3" xr:uid="{EC39133E-2B1E-4926-9BAB-A0BC92F6703D}"/>
-    <hyperlink ref="B118" r:id="rId4" xr:uid="{5CBB2DBF-381E-4F40-8899-29D4B5FC9B35}"/>
-    <hyperlink ref="B136" r:id="rId5" display="Data from the DOE's Pathways to Commercial Liftoff: Clean Hydrogen (p.13, p.88)" xr:uid="{451B96CC-C781-4216-8C03-8132EE3013B2}"/>
-    <hyperlink ref="B139" r:id="rId6" xr:uid="{8276223D-26B3-43EA-A781-2BDC0C41D374}"/>
-    <hyperlink ref="B66" r:id="rId7" xr:uid="{C723E247-B6C1-46C7-B576-CF146861E8AC}"/>
-    <hyperlink ref="B73" r:id="rId8" xr:uid="{BA83290A-C082-4AAB-AFC4-39DE2DEA36E6}"/>
-    <hyperlink ref="B79" r:id="rId9" xr:uid="{437DE8DA-77A2-48D0-8792-6CEB29629218}"/>
-    <hyperlink ref="B103" r:id="rId10" xr:uid="{8C5AD67E-D9AA-4BD2-BE55-FC759DD68FCE}"/>
-    <hyperlink ref="B84" r:id="rId11" xr:uid="{D30485F8-6CEE-4196-A36A-BE4A2803E3DD}"/>
-    <hyperlink ref="B52" r:id="rId12" xr:uid="{07F897CB-7353-674E-92F0-010511F2EA56}"/>
-    <hyperlink ref="B58" r:id="rId13" xr:uid="{D0781D44-31AC-BC44-B7B2-E83275B62102}"/>
-    <hyperlink ref="B21" r:id="rId14" xr:uid="{27F2C98F-DA26-4901-A0EB-6AC6A38F1C0C}"/>
-    <hyperlink ref="B95" r:id="rId15" xr:uid="{561EFB21-D77A-400A-A718-A022D22539BB}"/>
+    <hyperlink ref="B113" r:id="rId1" xr:uid="{810625CC-59B0-4E09-BD8A-7942EF52112A}"/>
+    <hyperlink ref="B114" r:id="rId2" xr:uid="{DE5DC99A-D169-4E5D-98F4-A0C74D220DA2}"/>
+    <hyperlink ref="B120" r:id="rId3" xr:uid="{EC39133E-2B1E-4926-9BAB-A0BC92F6703D}"/>
+    <hyperlink ref="B125" r:id="rId4" xr:uid="{5CBB2DBF-381E-4F40-8899-29D4B5FC9B35}"/>
+    <hyperlink ref="B143" r:id="rId5" display="Data from the DOE's Pathways to Commercial Liftoff: Clean Hydrogen (p.13, p.88)" xr:uid="{451B96CC-C781-4216-8C03-8132EE3013B2}"/>
+    <hyperlink ref="B146" r:id="rId6" xr:uid="{8276223D-26B3-43EA-A781-2BDC0C41D374}"/>
+    <hyperlink ref="B73" r:id="rId7" xr:uid="{C723E247-B6C1-46C7-B576-CF146861E8AC}"/>
+    <hyperlink ref="B80" r:id="rId8" xr:uid="{BA83290A-C082-4AAB-AFC4-39DE2DEA36E6}"/>
+    <hyperlink ref="B86" r:id="rId9" xr:uid="{437DE8DA-77A2-48D0-8792-6CEB29629218}"/>
+    <hyperlink ref="B110" r:id="rId10" xr:uid="{8C5AD67E-D9AA-4BD2-BE55-FC759DD68FCE}"/>
+    <hyperlink ref="B91" r:id="rId11" xr:uid="{D30485F8-6CEE-4196-A36A-BE4A2803E3DD}"/>
+    <hyperlink ref="B59" r:id="rId12" xr:uid="{07F897CB-7353-674E-92F0-010511F2EA56}"/>
+    <hyperlink ref="B65" r:id="rId13" xr:uid="{D0781D44-31AC-BC44-B7B2-E83275B62102}"/>
+    <hyperlink ref="B27" r:id="rId14" xr:uid="{27F2C98F-DA26-4901-A0EB-6AC6A38F1C0C}"/>
+    <hyperlink ref="B102" r:id="rId15" xr:uid="{561EFB21-D77A-400A-A718-A022D22539BB}"/>
     <hyperlink ref="B7" r:id="rId16" xr:uid="{5D5D64FB-C534-49E1-91CF-E9DAD8703987}"/>
-    <hyperlink ref="B14" r:id="rId17" xr:uid="{3ABDEADB-32F4-4E51-9C94-EFBD3570D876}"/>
+    <hyperlink ref="B21" r:id="rId17" xr:uid="{889A0153-4527-40B1-9E1F-CD0F47C08845}"/>
+    <hyperlink ref="B34" r:id="rId18" xr:uid="{914B6605-732A-4137-9624-39ADEA1A5BC5}"/>
+    <hyperlink ref="B14" r:id="rId19" xr:uid="{A729C781-885E-416E-A374-5F19DB0179E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId18"/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
 
@@ -5380,7 +5507,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
@@ -5403,7 +5530,7 @@
         <v>0.57060049240377109</v>
       </c>
       <c r="B2" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -5412,7 +5539,7 @@
         <v>266.66666666666669</v>
       </c>
       <c r="B3" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -5424,7 +5551,7 @@
         <v>8.2719018162705823E-4</v>
       </c>
       <c r="B5" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -5433,7 +5560,7 @@
         <v>3.1381977460259781E-3</v>
       </c>
       <c r="B6" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -5441,44 +5568,44 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
+        <v>372</v>
+      </c>
+      <c r="D28" t="s">
+        <v>374</v>
+      </c>
+      <c r="E28" t="s">
+        <v>375</v>
+      </c>
+      <c r="F28" t="s">
+        <v>376</v>
+      </c>
+      <c r="G28" t="s">
+        <v>377</v>
+      </c>
+      <c r="H28" t="s">
         <v>381</v>
       </c>
-      <c r="D28" t="s">
-        <v>383</v>
-      </c>
-      <c r="E28" t="s">
-        <v>384</v>
-      </c>
-      <c r="F28" t="s">
-        <v>385</v>
-      </c>
-      <c r="G28" t="s">
-        <v>386</v>
-      </c>
-      <c r="H28" t="s">
-        <v>390</v>
-      </c>
       <c r="I28" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="M28" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="N28" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="O28" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C29">
         <v>17000</v>
@@ -5490,7 +5617,7 @@
         <v>9.5</v>
       </c>
       <c r="G29" s="21">
-        <f>D29*About!$A$144</f>
+        <f>D29*About!$A$151</f>
         <v>983279</v>
       </c>
       <c r="H29" s="21">
@@ -5501,10 +5628,10 @@
         <v>250</v>
       </c>
       <c r="L29" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="M29">
-        <f>AVERAGE(C29:C31)*About!A149</f>
+        <f>AVERAGE(C29:C31)*About!A156</f>
         <v>21966.588645333242</v>
       </c>
       <c r="N29">
@@ -5518,7 +5645,7 @@
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="C30">
         <v>17000</v>
@@ -5530,7 +5657,7 @@
         <v>10</v>
       </c>
       <c r="G30" s="21">
-        <f>D30*About!$A$144</f>
+        <f>D30*About!$A$151</f>
         <v>983279</v>
       </c>
       <c r="H30" s="21">
@@ -5541,10 +5668,10 @@
         <v>250</v>
       </c>
       <c r="L30" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="M30">
-        <f>C32*About!A149</f>
+        <f>C32*About!A156</f>
         <v>43148.65626761887</v>
       </c>
       <c r="N30">
@@ -5558,7 +5685,7 @@
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C31">
         <v>50000</v>
@@ -5570,7 +5697,7 @@
         <v>23</v>
       </c>
       <c r="G31" s="21">
-        <f>D31*About!$A$144</f>
+        <f>D31*About!$A$151</f>
         <v>2492820</v>
       </c>
       <c r="H31" s="21">
@@ -5583,7 +5710,7 @@
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="C32">
         <v>55000</v>
@@ -5595,7 +5722,7 @@
         <v>16</v>
       </c>
       <c r="G32" s="21">
-        <f>E32*About!$A$146</f>
+        <f>E32*About!$A$153</f>
         <v>81891.360000000001</v>
       </c>
       <c r="H32" s="21"/>
@@ -5618,32 +5745,32 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="D38" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E38" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="F38" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="G38" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="H38" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C39">
         <v>2940</v>
@@ -5664,13 +5791,13 @@
         <v>35164444.444444448</v>
       </c>
       <c r="H39" s="55">
-        <f>E39*About!$A$150/G39</f>
+        <f>E39*About!$A$157/G39</f>
         <v>9.0358045924813471E-4</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C40">
         <v>113</v>
@@ -5691,39 +5818,39 @@
         <v>15099595.129339391</v>
       </c>
       <c r="H40" s="55">
-        <f>E40*About!$A$150/G40</f>
+        <f>E40*About!$A$157/G40</f>
         <v>3.7315769386037706E-3</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F41" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="24" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C55" s="19">
         <v>0.54</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C56" s="19">
         <v>0.52</v>
@@ -5734,32 +5861,32 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C81" s="7" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C82">
         <v>28398</v>
@@ -5772,13 +5899,13 @@
         <v>11801531.10292552</v>
       </c>
       <c r="H82" s="55">
-        <f>C82*About!$A$150/G82</f>
+        <f>C82*About!$A$157/G82</f>
         <v>2.0388661829358595E-3</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="C83">
         <v>25345</v>
@@ -5791,11 +5918,11 @@
         <v>186.05</v>
       </c>
       <c r="G83" s="21">
-        <f>E83*About!A144*A3/D83</f>
+        <f>E83*About!A151*A3/D83</f>
         <v>27483802.133333337</v>
       </c>
       <c r="H83" s="55">
-        <f>C83*About!$A$150/G83</f>
+        <f>C83*About!$A$157/G83</f>
         <v>7.8136653221209343E-4</v>
       </c>
     </row>
@@ -5821,7 +5948,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -5854,165 +5981,165 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="78">
-        <f>'Boilers &amp; Heat Pumps'!B13</f>
-        <v>3.0882108581950831E-5</v>
-      </c>
-      <c r="C2" s="78">
-        <f>'Boilers &amp; Heat Pumps'!$G$39</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="D2" s="78">
-        <f>'Boilers &amp; Heat Pumps'!A35</f>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="E2" s="79">
+      <c r="B2" s="69">
+        <f>'Boilers &amp; Heat Pumps'!B15</f>
+        <v>3.6314488500484264E-5</v>
+      </c>
+      <c r="C2" s="69">
+        <f>'Boilers &amp; Heat Pumps'!$H$21</f>
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="D2" s="69">
+        <f>'Boilers &amp; Heat Pumps'!$H$23</f>
+        <v>6.9746785142035624E-6</v>
+      </c>
+      <c r="E2" s="70">
         <f>C2</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="F2" s="78">
-        <f>'Boilers &amp; Heat Pumps'!$G$40</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="G2" s="80">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="F2" s="69">
+        <f>'Boilers &amp; Heat Pumps'!$H$22</f>
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="G2" s="71">
         <v>0</v>
       </c>
-      <c r="H2" s="79">
+      <c r="H2" s="70">
         <f>F2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="I2" s="79">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="I2" s="70">
         <f>F2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="J2" s="79">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="J2" s="70">
         <f>F2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="K2" s="78">
-        <f>'Boilers &amp; Heat Pumps'!A56</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="L2" s="78">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="K2" s="69">
+        <f>'Boilers &amp; Heat Pumps'!A37</f>
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="L2" s="69">
         <f t="shared" ref="L2:M8" si="0">K2</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="M2" s="78">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="M2" s="69">
         <f t="shared" si="0"/>
-        <v>2.3984236666442662E-5</v>
+        <v>1.0462017771305345E-5</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="79">
+      <c r="B3" s="70">
         <f>B2</f>
-        <v>3.0882108581950831E-5</v>
-      </c>
-      <c r="C3" s="79">
+        <v>3.6314488500484264E-5</v>
+      </c>
+      <c r="C3" s="70">
         <f t="shared" ref="C3:K3" si="1">C2</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="D3" s="79">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="D3" s="70">
         <f t="shared" si="1"/>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="E3" s="79">
+        <v>6.9746785142035624E-6</v>
+      </c>
+      <c r="E3" s="70">
         <f t="shared" si="1"/>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="F3" s="79">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="F3" s="70">
         <f t="shared" si="1"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="G3" s="80">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="G3" s="71">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H3" s="79">
+      <c r="H3" s="70">
         <f t="shared" si="1"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="I3" s="79">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="I3" s="70">
         <f t="shared" si="1"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="J3" s="79">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="J3" s="70">
         <f t="shared" si="1"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="K3" s="79">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="K3" s="70">
         <f t="shared" si="1"/>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="L3" s="79">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="L3" s="70">
         <f t="shared" si="0"/>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="M3" s="79">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="M3" s="70">
         <f t="shared" si="0"/>
-        <v>2.3984236666442662E-5</v>
+        <v>1.0462017771305345E-5</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="78">
+      <c r="B4" s="69">
         <f>'NB Medium Temp'!D40</f>
         <v>3.4771933032458345E-5</v>
       </c>
-      <c r="C4" s="79">
+      <c r="C4" s="70">
         <f>D4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="D4" s="78">
+      <c r="D4" s="69">
         <f>'NB Medium Temp'!D41</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="E4" s="79">
+      <c r="E4" s="70">
         <f>C4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="F4" s="79">
+      <c r="F4" s="70">
         <f>D4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="G4" s="80">
+      <c r="G4" s="71">
         <v>0</v>
       </c>
-      <c r="H4" s="79">
+      <c r="H4" s="70">
         <f>F4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="I4" s="79">
+      <c r="I4" s="70">
         <f>F4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="J4" s="79">
+      <c r="J4" s="70">
         <f>F4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="K4" s="79">
+      <c r="K4" s="70">
         <f>D4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="L4" s="79">
+      <c r="L4" s="70">
         <f t="shared" si="0"/>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="M4" s="79">
+      <c r="M4" s="70">
         <f t="shared" si="0"/>
         <v>3.1780367029653324E-5</v>
       </c>
@@ -6021,50 +6148,50 @@
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="78">
+      <c r="B5" s="69">
         <f>'NB High Temp'!F10</f>
         <v>1.7204637228083889E-4</v>
       </c>
-      <c r="C5" s="78">
+      <c r="C5" s="69">
         <f>'NB High Temp'!F45</f>
         <v>4.5951806950193628E-6</v>
       </c>
-      <c r="D5" s="78">
+      <c r="D5" s="69">
         <f>'NB High Temp'!F56</f>
         <v>2.0725243194734525E-5</v>
       </c>
-      <c r="E5" s="79">
+      <c r="E5" s="70">
         <f>C5</f>
         <v>4.5951806950193628E-6</v>
       </c>
-      <c r="F5" s="79">
+      <c r="F5" s="70">
         <f>D5*(F2/D2)</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="G5" s="80">
+        <v>3.7087277295840735E-5</v>
+      </c>
+      <c r="G5" s="71">
         <v>0</v>
       </c>
-      <c r="H5" s="79">
+      <c r="H5" s="70">
         <f>F5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="I5" s="79">
+        <v>3.7087277295840735E-5</v>
+      </c>
+      <c r="I5" s="70">
         <f>F5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="J5" s="79">
+        <v>3.7087277295840735E-5</v>
+      </c>
+      <c r="J5" s="70">
         <f>F5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="K5" s="78">
+        <v>3.7087277295840735E-5</v>
+      </c>
+      <c r="K5" s="69">
         <f>'NB High Temp'!F67</f>
         <v>3.265784625690839E-5</v>
       </c>
-      <c r="L5" s="78">
+      <c r="L5" s="69">
         <f t="shared" si="0"/>
         <v>3.265784625690839E-5</v>
       </c>
-      <c r="M5" s="78">
+      <c r="M5" s="69">
         <f t="shared" si="0"/>
         <v>3.265784625690839E-5</v>
       </c>
@@ -6073,102 +6200,102 @@
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="78">
+      <c r="B6" s="69">
         <f>Cooling!$B$49</f>
         <v>4.4520366169683022E-5</v>
       </c>
-      <c r="C6" s="79">
+      <c r="C6" s="70">
         <f>$D$6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="D6" s="78">
+      <c r="D6" s="69">
         <f>Cooling!$B$27</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="E6" s="79">
+      <c r="E6" s="70">
         <f>$D$6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="F6" s="79">
+      <c r="F6" s="70">
         <f>$D$6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="G6" s="80">
+      <c r="G6" s="71">
         <v>0</v>
       </c>
-      <c r="H6" s="79">
+      <c r="H6" s="70">
         <f>$D$6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="I6" s="79">
+      <c r="I6" s="70">
         <f>$D$6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="J6" s="79">
+      <c r="J6" s="70">
         <f>$D$6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="K6" s="79">
+      <c r="K6" s="70">
         <f>$D$6*(K2/D2)</f>
-        <v>2.7132239620912736E-5</v>
-      </c>
-      <c r="L6" s="79">
+        <v>2.7132239620912743E-5</v>
+      </c>
+      <c r="L6" s="70">
         <f t="shared" si="0"/>
-        <v>2.7132239620912736E-5</v>
-      </c>
-      <c r="M6" s="79">
+        <v>2.7132239620912743E-5</v>
+      </c>
+      <c r="M6" s="70">
         <f t="shared" si="0"/>
-        <v>2.7132239620912736E-5</v>
+        <v>2.7132239620912743E-5</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7" s="69">
         <f>'Machine Drive'!$W$22</f>
         <v>2.9652197760109964E-5</v>
       </c>
-      <c r="C7" s="79">
+      <c r="C7" s="70">
         <f>$F$7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="D7" s="79">
+      <c r="D7" s="70">
         <f>$F$7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="E7" s="79">
+      <c r="E7" s="70">
         <f>$F$7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="F7" s="78">
+      <c r="F7" s="69">
         <f>'Machine Drive'!D38</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="G7" s="80">
+      <c r="G7" s="71">
         <v>0</v>
       </c>
-      <c r="H7" s="79">
+      <c r="H7" s="70">
         <f>$F$7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="I7" s="79">
+      <c r="I7" s="70">
         <f>$F$7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="J7" s="79">
+      <c r="J7" s="70">
         <f>$F$7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="K7" s="79">
+      <c r="K7" s="70">
         <f>$F$7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="L7" s="79">
+      <c r="L7" s="70">
         <f t="shared" si="0"/>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="M7" s="79">
+      <c r="M7" s="70">
         <f t="shared" si="0"/>
         <v>7.0734511678239686E-5</v>
       </c>
@@ -6177,209 +6304,209 @@
       <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="78">
+      <c r="B8" s="69">
         <f>Other!E9</f>
         <v>7.0401933942914745E-6</v>
       </c>
-      <c r="C8" s="79">
-        <f>D8*(C2/D2)</f>
-        <v>2.0886792055175448E-5</v>
-      </c>
-      <c r="D8" s="78">
+      <c r="C8" s="70">
+        <f>C4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="D8" s="69">
         <f>Other!B24</f>
         <v>2.2284525195577483E-5</v>
       </c>
-      <c r="E8" s="79">
+      <c r="E8" s="70">
         <f>C8</f>
-        <v>2.0886792055175448E-5</v>
-      </c>
-      <c r="F8" s="79">
-        <f>D8*(F2/D2)</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="G8" s="80">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="F8" s="70">
+        <f>F4</f>
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="G8" s="71">
         <v>0</v>
       </c>
-      <c r="H8" s="79">
+      <c r="H8" s="70">
         <f>F8</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="I8" s="79">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="I8" s="70">
         <f>F8</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="J8" s="79">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="J8" s="70">
         <f>F8</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="K8" s="79">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="K8" s="70">
         <f>D8*(K2/D2)</f>
         <v>3.3426787793366228E-5</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="70">
         <f t="shared" si="0"/>
         <v>3.3426787793366228E-5</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="70">
         <f>L8</f>
         <v>3.3426787793366228E-5</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="B9" s="79">
+        <v>437</v>
+      </c>
+      <c r="B9" s="70">
         <f>B2</f>
-        <v>3.0882108581950831E-5</v>
-      </c>
-      <c r="C9" s="79">
+        <v>3.6314488500484264E-5</v>
+      </c>
+      <c r="C9" s="70">
         <f t="shared" ref="C9:M9" si="2">C2</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="D9" s="79">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="D9" s="70">
         <f t="shared" si="2"/>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="E9" s="79">
+        <v>6.9746785142035624E-6</v>
+      </c>
+      <c r="E9" s="70">
         <f t="shared" si="2"/>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="F9" s="79">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="F9" s="70">
         <f t="shared" si="2"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="G9" s="80">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="G9" s="71">
         <v>0</v>
       </c>
-      <c r="H9" s="79">
+      <c r="H9" s="70">
         <f t="shared" si="2"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="I9" s="79">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="I9" s="70">
         <f t="shared" si="2"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="J9" s="79">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="J9" s="70">
         <f t="shared" si="2"/>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="K9" s="79">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="K9" s="70">
         <f t="shared" si="2"/>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="L9" s="79">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="L9" s="70">
         <f t="shared" si="2"/>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="M9" s="79">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="M9" s="70">
         <f t="shared" si="2"/>
-        <v>2.3984236666442662E-5</v>
+        <v>1.0462017771305345E-5</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="B10" s="78">
+        <v>438</v>
+      </c>
+      <c r="B10" s="69">
         <f>Lighting!O23</f>
         <v>1.0540697873601793E-5</v>
       </c>
-      <c r="C10" s="79">
-        <f t="shared" ref="C10:E10" si="3">$F$10</f>
+      <c r="C10" s="70">
+        <f t="shared" ref="C10:D10" si="3">$F$10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="D10" s="79">
+      <c r="D10" s="70">
         <f t="shared" si="3"/>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="E10" s="79">
+      <c r="E10" s="70">
         <f>$F$10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="F10" s="78">
+      <c r="F10" s="69">
         <f>Lighting!I39</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="G10" s="80">
+      <c r="G10" s="71">
         <v>0</v>
       </c>
-      <c r="H10" s="79">
+      <c r="H10" s="70">
         <f t="shared" ref="H10:M10" si="4">$F$10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="I10" s="79">
+      <c r="I10" s="70">
         <f t="shared" si="4"/>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="J10" s="79">
+      <c r="J10" s="70">
         <f t="shared" si="4"/>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="K10" s="79">
+      <c r="K10" s="70">
         <f t="shared" si="4"/>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="L10" s="79">
+      <c r="L10" s="70">
         <f t="shared" si="4"/>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="M10" s="79">
+      <c r="M10" s="70">
         <f t="shared" si="4"/>
         <v>9.0753846553479132E-6</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="B11" s="79">
+        <v>439</v>
+      </c>
+      <c r="B11" s="70">
         <f>AVERAGE(B2:B10)</f>
-        <v>4.3468676250759544E-5</v>
-      </c>
-      <c r="C11" s="79">
+        <v>4.5279469556937371E-5</v>
+      </c>
+      <c r="C11" s="70">
         <f t="shared" ref="C11:M11" si="5">AVERAGE(C2:C10)</f>
-        <v>2.2235575980706048E-5</v>
-      </c>
-      <c r="D11" s="79">
+        <v>2.5058031375260608E-5</v>
+      </c>
+      <c r="D11" s="70">
         <f t="shared" si="5"/>
-        <v>2.4517407203745931E-5</v>
-      </c>
-      <c r="E11" s="79">
+        <v>2.1512469671493199E-5</v>
+      </c>
+      <c r="E11" s="70">
         <f t="shared" si="5"/>
-        <v>2.2235575980706048E-5</v>
-      </c>
-      <c r="F11" s="79">
+        <v>2.5058031375260608E-5</v>
+      </c>
+      <c r="F11" s="70">
         <f t="shared" si="5"/>
-        <v>2.0374236958296052E-5</v>
-      </c>
-      <c r="G11" s="77">
+        <v>2.6221008711888631E-5</v>
+      </c>
+      <c r="G11" s="68">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H11" s="79">
+      <c r="H11" s="70">
         <f t="shared" si="5"/>
-        <v>2.0374236958296052E-5</v>
-      </c>
-      <c r="I11" s="79">
+        <v>2.6221008711888631E-5</v>
+      </c>
+      <c r="I11" s="70">
         <f t="shared" si="5"/>
-        <v>2.0374236958296052E-5</v>
-      </c>
-      <c r="J11" s="79">
+        <v>2.6221008711888631E-5</v>
+      </c>
+      <c r="J11" s="70">
         <f t="shared" si="5"/>
-        <v>2.0374236958296052E-5</v>
-      </c>
-      <c r="K11" s="79">
+        <v>2.6221008711888631E-5</v>
+      </c>
+      <c r="K11" s="70">
         <f t="shared" si="5"/>
-        <v>3.0751094114861809E-5</v>
-      </c>
-      <c r="L11" s="79">
+        <v>2.62436878164827E-5</v>
+      </c>
+      <c r="L11" s="70">
         <f t="shared" si="5"/>
-        <v>3.0751094114861809E-5</v>
-      </c>
-      <c r="M11" s="79">
+        <v>2.62436878164827E-5</v>
+      </c>
+      <c r="M11" s="70">
         <f t="shared" si="5"/>
-        <v>3.0751094114861809E-5</v>
+        <v>2.62436878164827E-5</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -6387,32 +6514,32 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -6436,7 +6563,7 @@
   <sheetData>
     <row r="1" spans="1:44" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -6469,10 +6596,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="N1"/>
       <c r="O1"/>
@@ -6510,157 +6637,157 @@
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="81">
+      <c r="B2" s="68">
         <f>Summary!B2</f>
-        <v>3.0882108581950831E-5</v>
-      </c>
-      <c r="C2" s="81">
+        <v>3.6314488500484264E-5</v>
+      </c>
+      <c r="C2" s="68">
         <f>Summary!C2</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="D2" s="81">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="D2" s="68">
         <f>Summary!D2</f>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="E2" s="81">
+        <v>6.9746785142035624E-6</v>
+      </c>
+      <c r="E2" s="68">
         <f>Summary!E2</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="F2" s="81">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="F2" s="68">
         <f>Summary!F2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="G2" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="G2" s="68">
         <f>Summary!G2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="81">
+      <c r="H2" s="68">
         <f>Summary!H2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="I2" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="I2" s="68">
         <f>Summary!I2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="J2" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="J2" s="68">
         <f>Summary!J2</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="K2" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="K2" s="68">
         <f>Summary!K2</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="L2" s="81">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="L2" s="68">
         <f>Summary!L2</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="M2" s="81">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="M2" s="68">
         <f>Summary!M2</f>
-        <v>2.3984236666442662E-5</v>
+        <v>1.0462017771305345E-5</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="81">
+      <c r="B3" s="68">
         <f>Summary!B3</f>
-        <v>3.0882108581950831E-5</v>
-      </c>
-      <c r="C3" s="81">
+        <v>3.6314488500484264E-5</v>
+      </c>
+      <c r="C3" s="68">
         <f>Summary!C3</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="D3" s="81">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="D3" s="68">
         <f>Summary!D3</f>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="E3" s="81">
+        <v>6.9746785142035624E-6</v>
+      </c>
+      <c r="E3" s="68">
         <f>Summary!E3</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="F3" s="81">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="F3" s="68">
         <f>Summary!F3</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="G3" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="G3" s="68">
         <f>Summary!G3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="81">
+      <c r="H3" s="68">
         <f>Summary!H3</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="I3" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="I3" s="68">
         <f>Summary!I3</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="J3" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="J3" s="68">
         <f>Summary!J3</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="K3" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="K3" s="68">
         <f>Summary!K3</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="L3" s="81">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="L3" s="68">
         <f>Summary!L3</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="M3" s="81">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="M3" s="68">
         <f>Summary!M3</f>
-        <v>2.3984236666442662E-5</v>
+        <v>1.0462017771305345E-5</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="81">
+      <c r="B4" s="68">
         <f>Summary!B4</f>
         <v>3.4771933032458345E-5</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="68">
         <f>Summary!C4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="D4" s="81">
+      <c r="D4" s="68">
         <f>Summary!D4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="E4" s="81">
+      <c r="E4" s="68">
         <f>Summary!E4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="F4" s="81">
+      <c r="F4" s="68">
         <f>Summary!F4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="G4" s="81">
+      <c r="G4" s="68">
         <f>Summary!G4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="81">
+      <c r="H4" s="68">
         <f>Summary!H4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="I4" s="81">
+      <c r="I4" s="68">
         <f>Summary!I4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="J4" s="81">
+      <c r="J4" s="68">
         <f>Summary!J4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="K4" s="81">
+      <c r="K4" s="68">
         <f>Summary!K4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="L4" s="81">
+      <c r="L4" s="68">
         <f>Summary!L4</f>
         <v>3.1780367029653324E-5</v>
       </c>
-      <c r="M4" s="81">
+      <c r="M4" s="68">
         <f>Summary!M4</f>
         <v>3.1780367029653324E-5</v>
       </c>
@@ -6669,51 +6796,51 @@
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="81">
+      <c r="B5" s="68">
         <f>Summary!B5</f>
         <v>1.7204637228083889E-4</v>
       </c>
-      <c r="C5" s="81">
+      <c r="C5" s="68">
         <f>Summary!C5</f>
         <v>4.5951806950193628E-6</v>
       </c>
-      <c r="D5" s="81">
+      <c r="D5" s="68">
         <f>Summary!D5</f>
         <v>2.0725243194734525E-5</v>
       </c>
-      <c r="E5" s="81">
+      <c r="E5" s="68">
         <f>Summary!E5</f>
         <v>4.5951806950193628E-6</v>
       </c>
-      <c r="F5" s="81">
+      <c r="F5" s="68">
         <f>Summary!F5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="G5" s="81">
+        <v>3.7087277295840735E-5</v>
+      </c>
+      <c r="G5" s="68">
         <f>Summary!G5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="81">
+      <c r="H5" s="68">
         <f>Summary!H5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="I5" s="81">
+        <v>3.7087277295840735E-5</v>
+      </c>
+      <c r="I5" s="68">
         <f>Summary!I5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="J5" s="81">
+        <v>3.7087277295840735E-5</v>
+      </c>
+      <c r="J5" s="68">
         <f>Summary!J5</f>
-        <v>1.2230751723262388E-5</v>
-      </c>
-      <c r="K5" s="81">
+        <v>3.7087277295840735E-5</v>
+      </c>
+      <c r="K5" s="68">
         <f>Summary!K5</f>
         <v>3.265784625690839E-5</v>
       </c>
-      <c r="L5" s="81">
+      <c r="L5" s="68">
         <f>Summary!L5</f>
         <v>3.265784625690839E-5</v>
       </c>
-      <c r="M5" s="81">
+      <c r="M5" s="68">
         <f>Summary!M5</f>
         <v>3.265784625690839E-5</v>
       </c>
@@ -6722,104 +6849,104 @@
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="81">
+      <c r="B6" s="68">
         <f>Summary!B6</f>
         <v>4.4520366169683022E-5</v>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="68">
         <f>Summary!C6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="68">
         <f>Summary!D6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="68">
         <f>Summary!E6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="F6" s="81">
+      <c r="F6" s="68">
         <f>Summary!F6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="G6" s="81">
+      <c r="G6" s="68">
         <f>Summary!G6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="81">
+      <c r="H6" s="68">
         <f>Summary!H6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="I6" s="81">
+      <c r="I6" s="68">
         <f>Summary!I6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="J6" s="81">
+      <c r="J6" s="68">
         <f>Summary!J6</f>
         <v>1.8088159747275158E-5</v>
       </c>
-      <c r="K6" s="81">
+      <c r="K6" s="68">
         <f>Summary!K6</f>
-        <v>2.7132239620912736E-5</v>
-      </c>
-      <c r="L6" s="81">
+        <v>2.7132239620912743E-5</v>
+      </c>
+      <c r="L6" s="68">
         <f>Summary!L6</f>
-        <v>2.7132239620912736E-5</v>
-      </c>
-      <c r="M6" s="81">
+        <v>2.7132239620912743E-5</v>
+      </c>
+      <c r="M6" s="68">
         <f>Summary!M6</f>
-        <v>2.7132239620912736E-5</v>
+        <v>2.7132239620912743E-5</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="81">
+      <c r="B7" s="68">
         <f>Summary!B7</f>
         <v>2.9652197760109964E-5</v>
       </c>
-      <c r="C7" s="81">
+      <c r="C7" s="68">
         <f>Summary!C7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="D7" s="81">
+      <c r="D7" s="68">
         <f>Summary!D7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="68">
         <f>Summary!E7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="F7" s="81">
+      <c r="F7" s="68">
         <f>Summary!F7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="G7" s="81">
+      <c r="G7" s="68">
         <f>Summary!G7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="81">
+      <c r="H7" s="68">
         <f>Summary!H7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="I7" s="81">
+      <c r="I7" s="68">
         <f>Summary!I7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="J7" s="81">
+      <c r="J7" s="68">
         <f>Summary!J7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="K7" s="81">
+      <c r="K7" s="68">
         <f>Summary!K7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="L7" s="81">
+      <c r="L7" s="68">
         <f>Summary!L7</f>
         <v>7.0734511678239686E-5</v>
       </c>
-      <c r="M7" s="81">
+      <c r="M7" s="68">
         <f>Summary!M7</f>
         <v>7.0734511678239686E-5</v>
       </c>
@@ -6828,212 +6955,212 @@
       <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="81">
+      <c r="B8" s="68">
         <f>Summary!B8</f>
         <v>7.0401933942914745E-6</v>
       </c>
-      <c r="C8" s="81">
+      <c r="C8" s="68">
         <f>Summary!C8</f>
-        <v>2.0886792055175448E-5</v>
-      </c>
-      <c r="D8" s="81">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="D8" s="68">
         <f>Summary!D8</f>
         <v>2.2284525195577483E-5</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="68">
         <f>Summary!E8</f>
-        <v>2.0886792055175448E-5</v>
-      </c>
-      <c r="F8" s="81">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="F8" s="68">
         <f>Summary!F8</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="G8" s="81">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="G8" s="68">
         <f>Summary!G8</f>
         <v>0</v>
       </c>
-      <c r="H8" s="81">
+      <c r="H8" s="68">
         <f>Summary!H8</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="I8" s="81">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="I8" s="68">
         <f>Summary!I8</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="J8" s="81">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="J8" s="68">
         <f>Summary!J8</f>
-        <v>1.3150943145851209E-5</v>
-      </c>
-      <c r="K8" s="81">
+        <v>3.1780367029653324E-5</v>
+      </c>
+      <c r="K8" s="68">
         <f>Summary!K8</f>
         <v>3.3426787793366228E-5</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="68">
         <f>Summary!L8</f>
         <v>3.3426787793366228E-5</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="68">
         <f>Summary!M8</f>
         <v>3.3426787793366228E-5</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="B9" s="81">
+        <v>437</v>
+      </c>
+      <c r="B9" s="68">
         <f>Summary!B9</f>
-        <v>3.0882108581950831E-5</v>
-      </c>
-      <c r="C9" s="81">
+        <v>3.6314488500484264E-5</v>
+      </c>
+      <c r="C9" s="68">
         <f>Summary!C9</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="D9" s="81">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="D9" s="68">
         <f>Summary!D9</f>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="E9" s="81">
+        <v>6.9746785142035624E-6</v>
+      </c>
+      <c r="E9" s="68">
         <f>Summary!E9</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-      <c r="F9" s="81">
+        <v>1.9822770514052231E-5</v>
+      </c>
+      <c r="F9" s="68">
         <f>Summary!F9</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="G9" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="G9" s="68">
         <f>Summary!G9</f>
         <v>0</v>
       </c>
-      <c r="H9" s="81">
+      <c r="H9" s="68">
         <f>Summary!H9</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="I9" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="I9" s="68">
         <f>Summary!I9</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="J9" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="J9" s="68">
         <f>Summary!J9</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-      <c r="K9" s="81">
+        <v>1.248100365699585E-5</v>
+      </c>
+      <c r="K9" s="68">
         <f>Summary!K9</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="L9" s="81">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="L9" s="68">
         <f>Summary!L9</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="M9" s="81">
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="M9" s="68">
         <f>Summary!M9</f>
-        <v>2.3984236666442662E-5</v>
+        <v>1.0462017771305345E-5</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="B10" s="81">
+        <v>438</v>
+      </c>
+      <c r="B10" s="68">
         <f>Summary!B10</f>
         <v>1.0540697873601793E-5</v>
       </c>
-      <c r="C10" s="81">
+      <c r="C10" s="68">
         <f>Summary!C10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="68">
         <f>Summary!D10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="68">
         <f>Summary!E10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="F10" s="81">
+      <c r="F10" s="68">
         <f>Summary!F10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="G10" s="81">
+      <c r="G10" s="68">
         <f>Summary!G10</f>
         <v>0</v>
       </c>
-      <c r="H10" s="81">
+      <c r="H10" s="68">
         <f>Summary!H10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="I10" s="81">
+      <c r="I10" s="68">
         <f>Summary!I10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="J10" s="81">
+      <c r="J10" s="68">
         <f>Summary!J10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="K10" s="81">
+      <c r="K10" s="68">
         <f>Summary!K10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="L10" s="81">
+      <c r="L10" s="68">
         <f>Summary!L10</f>
         <v>9.0753846553479132E-6</v>
       </c>
-      <c r="M10" s="81">
+      <c r="M10" s="68">
         <f>Summary!M10</f>
         <v>9.0753846553479132E-6</v>
       </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="B11" s="81">
+        <v>439</v>
+      </c>
+      <c r="B11" s="68">
         <f>Summary!B11</f>
-        <v>4.3468676250759544E-5</v>
-      </c>
-      <c r="C11" s="81">
+        <v>4.5279469556937371E-5</v>
+      </c>
+      <c r="C11" s="68">
         <f>Summary!C11</f>
-        <v>2.2235575980706048E-5</v>
-      </c>
-      <c r="D11" s="81">
+        <v>2.5058031375260608E-5</v>
+      </c>
+      <c r="D11" s="68">
         <f>Summary!D11</f>
-        <v>2.4517407203745931E-5</v>
-      </c>
-      <c r="E11" s="81">
+        <v>2.1512469671493199E-5</v>
+      </c>
+      <c r="E11" s="68">
         <f>Summary!E11</f>
-        <v>2.2235575980706048E-5</v>
-      </c>
-      <c r="F11" s="81">
+        <v>2.5058031375260608E-5</v>
+      </c>
+      <c r="F11" s="68">
         <f>Summary!F11</f>
-        <v>2.0374236958296052E-5</v>
-      </c>
-      <c r="G11" s="81">
+        <v>2.6221008711888631E-5</v>
+      </c>
+      <c r="G11" s="68">
         <f>Summary!G11</f>
         <v>0</v>
       </c>
-      <c r="H11" s="81">
+      <c r="H11" s="68">
         <f>Summary!H11</f>
-        <v>2.0374236958296052E-5</v>
-      </c>
-      <c r="I11" s="81">
+        <v>2.6221008711888631E-5</v>
+      </c>
+      <c r="I11" s="68">
         <f>Summary!I11</f>
-        <v>2.0374236958296052E-5</v>
-      </c>
-      <c r="J11" s="81">
+        <v>2.6221008711888631E-5</v>
+      </c>
+      <c r="J11" s="68">
         <f>Summary!J11</f>
-        <v>2.0374236958296052E-5</v>
-      </c>
-      <c r="K11" s="81">
+        <v>2.6221008711888631E-5</v>
+      </c>
+      <c r="K11" s="68">
         <f>Summary!K11</f>
-        <v>3.0751094114861809E-5</v>
-      </c>
-      <c r="L11" s="81">
+        <v>2.62436878164827E-5</v>
+      </c>
+      <c r="L11" s="68">
         <f>Summary!L11</f>
-        <v>3.0751094114861809E-5</v>
-      </c>
-      <c r="M11" s="81">
+        <v>2.62436878164827E-5</v>
+      </c>
+      <c r="M11" s="68">
         <f>Summary!M11</f>
-        <v>3.0751094114861809E-5</v>
+        <v>2.62436878164827E-5</v>
       </c>
     </row>
   </sheetData>
@@ -7055,7 +7182,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7161,7 +7288,7 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B12" s="10">
         <f>B11</f>
@@ -7170,7 +7297,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="B13" s="10">
         <f>B12</f>
@@ -7184,7 +7311,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F78C19FD-7E25-465C-BF9B-84ECCFD8C3AD}">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.42578125" customWidth="1"/>
@@ -7194,10 +7321,10 @@
     <col min="5" max="5" width="18.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.28515625" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>19</v>
       </c>
@@ -7205,433 +7332,653 @@
       <c r="C1" s="18"/>
       <c r="D1" s="18"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B5" s="60" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C5" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="64"/>
+    </row>
+    <row r="6" spans="1:4" s="86" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>419</v>
+      </c>
+      <c r="B6" s="87">
+        <v>600</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>536</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="86" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>537</v>
+      </c>
+      <c r="B7" s="87">
+        <v>1.0822000000000001</v>
+      </c>
+      <c r="C7" s="62" t="s">
+        <v>538</v>
+      </c>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B8">
+        <f>B6*B7</f>
+        <v>649.32000000000005</v>
+      </c>
+      <c r="C8" s="62" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9">
+        <v>8760</v>
+      </c>
+      <c r="C9" s="62" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="62"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B10" s="19">
+        <f>AVERAGE(5944,2503,6257,6257)/B9</f>
+        <v>0.5982020547945206</v>
+      </c>
+      <c r="C10" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="62"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>423</v>
+      </c>
+      <c r="B11" s="63">
+        <f>B8/(B9*B10)</f>
+        <v>0.12391011879204238</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>535</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13">
+        <v>3412.14</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>424</v>
+      </c>
+      <c r="B15" s="12">
+        <f>B11/B13</f>
+        <v>3.6314488500484264E-5</v>
+      </c>
+      <c r="C15" s="62" t="s">
+        <v>522</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="D16" s="24" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="1:8" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="64"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B6">
-        <v>600</v>
-      </c>
-      <c r="C6" s="62" t="s">
-        <v>143</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>431</v>
-      </c>
-      <c r="B7">
-        <v>8760</v>
-      </c>
-      <c r="C7" s="62" t="s">
-        <v>432</v>
-      </c>
-      <c r="D7" s="62"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>433</v>
-      </c>
-      <c r="B8" s="19">
-        <v>0.65</v>
-      </c>
-      <c r="C8" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="D8" s="62"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>434</v>
-      </c>
-      <c r="B9" s="63">
-        <f>B6/(B7*B8)</f>
-        <v>0.10537407797681771</v>
-      </c>
-      <c r="C9" s="62" t="s">
-        <v>287</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="E20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21">
+        <v>2000</v>
+      </c>
+      <c r="C21">
+        <v>300</v>
+      </c>
+      <c r="D21">
+        <f>B21*C21</f>
+        <v>600000</v>
+      </c>
+      <c r="E21" s="19">
+        <v>0.9</v>
+      </c>
+      <c r="F21">
+        <f>$B$29/E21</f>
+        <v>40035776000</v>
+      </c>
+      <c r="G21" s="82">
+        <f>D21/F21</f>
+        <v>1.4986595988547842E-5</v>
+      </c>
+      <c r="H21" s="12">
+        <f>G21*$B$30</f>
+        <v>1.9822770514052231E-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22">
+        <v>2000</v>
+      </c>
+      <c r="C22">
+        <v>200</v>
+      </c>
+      <c r="D22">
+        <f>B22*C22</f>
+        <v>400000</v>
+      </c>
+      <c r="E22" s="19">
+        <v>0.85</v>
+      </c>
+      <c r="F22">
+        <f>$B$29/E22</f>
+        <v>42390821647.058823</v>
+      </c>
+      <c r="G22" s="82">
+        <f>D22/F22</f>
+        <v>9.436004881678272E-6</v>
+      </c>
+      <c r="H22" s="12">
+        <f>G22*$B$30</f>
+        <v>1.248100365699585E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
+        <v>2000</v>
+      </c>
+      <c r="C23">
+        <v>100</v>
+      </c>
+      <c r="D23">
+        <f>B23*C23</f>
+        <v>200000</v>
+      </c>
+      <c r="E23" s="19">
+        <v>0.95</v>
+      </c>
+      <c r="F23">
+        <f>$B$29/E23</f>
+        <v>37928629894.736847</v>
+      </c>
+      <c r="G23" s="9">
+        <f>D23/F23</f>
+        <v>5.2730615515260925E-6</v>
+      </c>
+      <c r="H23" s="12">
+        <f>G23*$B$30</f>
+        <v>6.9746785142035624E-6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="B11">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>529</v>
+      </c>
+      <c r="B26" s="84">
+        <v>5280</v>
+      </c>
+      <c r="C26" s="85" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27">
+        <f>B21*B26</f>
+        <v>10560000</v>
+      </c>
+      <c r="C27" s="62" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28">
         <v>3412.14</v>
       </c>
-      <c r="C11" s="62" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>435</v>
-      </c>
-      <c r="B13" s="12">
-        <f>B9/B11</f>
-        <v>3.0882108581950831E-5</v>
-      </c>
-      <c r="C13" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="D14" s="24" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>272</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="C28" s="62" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29">
+        <f>B27*B28</f>
+        <v>36032198400</v>
+      </c>
+      <c r="C29" s="62" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>517</v>
+      </c>
+      <c r="B30">
+        <v>1.3227</v>
+      </c>
+      <c r="C30" s="62" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="8"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="20"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="12">
+        <f>H23*1.5</f>
+        <v>1.0462017771305345E-5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="81" t="s">
+        <v>520</v>
+      </c>
+      <c r="B40" s="83"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>266</v>
+      </c>
+      <c r="B44" s="8">
         <v>80375</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>273</v>
-      </c>
-      <c r="B21" s="8">
+      <c r="C44" s="62" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>267</v>
+      </c>
+      <c r="B45" s="8">
         <v>91475</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>274</v>
-      </c>
-      <c r="B22" s="8">
-        <f>AVERAGE(B20:B21)</f>
+      <c r="C45" s="62" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>510</v>
+      </c>
+      <c r="B46" s="8">
+        <f>AVERAGE(B44:B45)</f>
         <v>85925</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>275</v>
-      </c>
-      <c r="B24">
+      <c r="C46" s="62" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>508</v>
+      </c>
+      <c r="B48">
+        <v>1.7041999999999999</v>
+      </c>
+      <c r="C48" s="62" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>511</v>
+      </c>
+      <c r="B50" s="25">
+        <f>B46*B48</f>
+        <v>146433.38499999998</v>
+      </c>
+      <c r="C50" s="62" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>503</v>
+      </c>
+      <c r="B52">
         <v>400</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>276</v>
-      </c>
-      <c r="B25">
-        <v>0.74570000000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26">
-        <f>B24*B25</f>
-        <v>298.28000000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="22">
-        <v>5280</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>277</v>
-      </c>
-      <c r="B30">
-        <f>B26*B28</f>
-        <v>1574918.4000000001</v>
-      </c>
-      <c r="C30" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31">
-        <v>3412.14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>277</v>
-      </c>
-      <c r="B32">
-        <f>B30*B31</f>
-        <v>5373842069.3760004</v>
-      </c>
-      <c r="C32" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
-        <f>B22/B32</f>
-        <v>1.5989491110961776E-5</v>
-      </c>
-      <c r="B35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-    </row>
-    <row r="38" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B38" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="G38" s="23" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B39">
-        <v>2000</v>
-      </c>
-      <c r="C39">
-        <v>300</v>
-      </c>
-      <c r="D39">
-        <f>B39*C39</f>
-        <v>600000</v>
-      </c>
-      <c r="E39" s="19">
-        <v>0.9</v>
-      </c>
-      <c r="F39">
-        <f>$B$46/E39</f>
-        <v>40035776000</v>
-      </c>
-      <c r="G39" s="12">
-        <f>D39/F39</f>
-        <v>1.4986595988547842E-5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40">
-        <v>2000</v>
-      </c>
-      <c r="C40">
-        <v>200</v>
-      </c>
-      <c r="D40">
-        <f>B40*C40</f>
-        <v>400000</v>
-      </c>
-      <c r="E40" s="19">
-        <v>0.85</v>
-      </c>
-      <c r="F40">
-        <f>$B$46/E40</f>
-        <v>42390821647.058823</v>
-      </c>
-      <c r="G40" s="12">
-        <f>D40/F40</f>
-        <v>9.436004881678272E-6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41">
-        <v>2000</v>
-      </c>
-      <c r="C41">
-        <v>100</v>
-      </c>
-      <c r="D41">
-        <f>B41*C41</f>
-        <v>200000</v>
-      </c>
-      <c r="E41" s="19">
-        <v>0.95</v>
-      </c>
-      <c r="F41">
-        <f>$B$46/E41</f>
-        <v>37928629894.736847</v>
-      </c>
-      <c r="G41" s="9">
-        <f>D41/F41</f>
-        <v>5.2730615515260925E-6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B43" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>47</v>
-      </c>
-      <c r="B44">
-        <f>B39*B28</f>
-        <v>10560000</v>
-      </c>
-      <c r="C44" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45">
-        <v>3412.14</v>
-      </c>
-      <c r="C45" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46">
-        <f>B44*B45</f>
-        <v>36032198400</v>
-      </c>
-      <c r="C46" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="18"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="18"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53" s="8"/>
+        <v>504</v>
+      </c>
+      <c r="B53">
+        <v>9.8094999999999999</v>
+      </c>
+      <c r="C53" s="65" t="s">
+        <v>505</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54" s="20"/>
+        <v>90</v>
+      </c>
+      <c r="B54">
+        <f>B52*B53</f>
+        <v>3923.8</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="12">
-        <f>A35*1.5</f>
-        <v>2.3984236666442662E-5</v>
-      </c>
-      <c r="B56" t="s">
-        <v>25</v>
+      <c r="A56" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" s="22">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>268</v>
+      </c>
+      <c r="B58">
+        <f>B54*B56</f>
+        <v>20717664</v>
+      </c>
+      <c r="C58" s="62" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>31</v>
+      </c>
+      <c r="B59">
+        <v>3412.14</v>
+      </c>
+      <c r="C59" s="62" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>268</v>
+      </c>
+      <c r="B60">
+        <f>B58*B59</f>
+        <v>70691570040.959991</v>
+      </c>
+      <c r="C60" s="62" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="12">
+        <f>B50/B60</f>
+        <v>2.0714405538758552E-6</v>
+      </c>
+      <c r="B63" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="81" t="s">
+        <v>521</v>
+      </c>
+      <c r="B66" s="83"/>
+      <c r="C66" s="83"/>
+      <c r="D66" s="83"/>
+      <c r="E66" s="83"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>513</v>
+      </c>
+      <c r="B68" s="8">
+        <v>87540</v>
+      </c>
+      <c r="C68" s="62" t="s">
+        <v>514</v>
+      </c>
+      <c r="D68" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>515</v>
+      </c>
+      <c r="B69">
+        <v>1.3062</v>
+      </c>
+      <c r="C69" s="62" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>513</v>
+      </c>
+      <c r="B70" s="25">
+        <f>B68*B69</f>
+        <v>114344.74800000001</v>
+      </c>
+      <c r="C70" s="62" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>503</v>
+      </c>
+      <c r="B72">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>504</v>
+      </c>
+      <c r="B73">
+        <v>9.8094999999999999</v>
+      </c>
+      <c r="C73" s="65" t="s">
+        <v>505</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74">
+        <f>B72*B73</f>
+        <v>980.95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B76" s="22">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>268</v>
+      </c>
+      <c r="B78">
+        <f>B74*B76</f>
+        <v>5179416</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79">
+        <v>3412.14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>268</v>
+      </c>
+      <c r="B80">
+        <f>B78*B79</f>
+        <v>17672892510.239998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="12">
+        <f>B70/B80</f>
+        <v>6.4700641354405657E-6</v>
+      </c>
+      <c r="B83" t="s">
+        <v>522</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D53" r:id="rId1" xr:uid="{A6DC4AC4-74B1-4E7B-BA41-28F0B5652653}"/>
+    <hyperlink ref="D73" r:id="rId2" xr:uid="{710D1754-3D51-4D73-AC41-A0B063FC700A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7647,330 +7994,330 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B5" s="8">
         <v>307500</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B6">
         <v>4000</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B8" s="8">
         <v>75863</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B9" s="8">
         <v>6226</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B11" s="25">
         <v>0.45</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B12" s="25">
         <v>0.15</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B14" s="21">
         <f>B8/B11</f>
         <v>168584.44444444444</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B15" s="21">
         <f>B9/B12</f>
         <v>41506.666666666672</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>100000</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B18">
         <v>3412.14</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B20" s="9">
         <f>B14*B17</f>
         <v>16858444444.444445</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B21" s="9">
         <f>B15*B18</f>
         <v>141626557.60000002</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B26" s="9">
         <f>SUM(B20:B21)</f>
         <v>17000071002.044445</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B27" s="12">
         <f>B5/B26</f>
         <v>1.8088159747275158E-5</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B32" s="8">
         <v>200</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B33" s="8">
         <v>500</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B34" s="8">
         <f>AVERAGE(B32:B33)</f>
         <v>350</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B36">
         <v>500</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B38" s="8">
         <f>B34*B36</f>
         <v>175000</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B41">
         <v>0.57599999999999996</v>
       </c>
       <c r="C41" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B42">
         <f>B41*B36</f>
         <v>288</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B44">
         <f>B6</f>
         <v>4000</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D44" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B46">
         <f>B42*B44</f>
         <v>1152000</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B47" s="9">
         <f>B46*B18</f>
         <v>3930785280</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B49" s="12">
         <f>B38/B47</f>
         <v>4.4520366169683022E-5</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -7994,7 +8341,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -8002,25 +8349,25 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B3" s="42"/>
       <c r="C3" s="11" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B5">
         <v>492000</v>
@@ -8029,7 +8376,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="B6">
         <v>135000</v>
@@ -8038,7 +8385,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B7">
         <v>474000</v>
@@ -8047,7 +8394,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B8">
         <v>70000</v>
@@ -8056,7 +8403,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B9">
         <v>22000</v>
@@ -8065,7 +8412,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B10">
         <v>18000</v>
@@ -8074,7 +8421,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B11">
         <v>216000</v>
@@ -8083,7 +8430,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B12">
         <v>51000</v>
@@ -8092,7 +8439,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B13">
         <v>125000</v>
@@ -8101,24 +8448,24 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="11" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B17" s="20">
         <v>13400</v>
@@ -8126,7 +8473,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B18" s="20">
         <v>5300</v>
@@ -8134,7 +8481,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="B19" s="20">
         <v>13600</v>
@@ -8142,32 +8489,32 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B21" s="42"/>
       <c r="C21" s="42"/>
       <c r="D21" s="42"/>
       <c r="E21" s="11" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B23">
         <v>4380</v>
@@ -8178,7 +8525,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B24">
         <v>4380</v>
@@ -8189,7 +8536,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="40"/>
@@ -8197,47 +8544,47 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B33" s="1">
-        <f>'Boilers &amp; Heat Pumps'!B28</f>
+        <f>'Boilers &amp; Heat Pumps'!B56</f>
         <v>5280</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B36" s="46">
         <v>3412.14</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -8245,7 +8592,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="45" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B38" s="44"/>
       <c r="C38" s="44"/>
@@ -8253,21 +8600,21 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B40">
         <f>$B$33*D23*B36</f>
@@ -8284,7 +8631,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B41">
         <f>$B$33*C24</f>
@@ -8301,33 +8648,33 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B51" s="42"/>
       <c r="C51" s="42"/>
       <c r="D51" s="11" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B53">
         <v>722000</v>
@@ -8339,7 +8686,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B54">
         <v>882000</v>
@@ -8367,7 +8714,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -8378,12 +8725,12 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I2" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C3" s="25"/>
       <c r="F3" s="25">
@@ -8391,107 +8738,107 @@
         <v>264.16000000000003</v>
       </c>
       <c r="G3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F4">
         <v>450</v>
       </c>
       <c r="G4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C5" s="32"/>
       <c r="F5" s="32">
         <v>800000</v>
       </c>
       <c r="G5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="F7">
         <f>F4*F5</f>
         <v>360000000</v>
       </c>
       <c r="G7" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="F8">
         <f>F7*0.003412</f>
         <v>1228320</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F9" s="25">
         <f>F3*F5</f>
         <v>211328000.00000003</v>
       </c>
       <c r="G9" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F10" s="12">
         <f>F9/(F8*10^6)</f>
         <v>1.7204637228083889E-4</v>
       </c>
       <c r="G10" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E12">
         <f>8760*155</f>
         <v>1357800</v>
       </c>
       <c r="F12" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -8502,13 +8849,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="F16" s="20">
         <v>170</v>
       </c>
       <c r="G16" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -8517,7 +8864,7 @@
         <v>26.356589147286826</v>
       </c>
       <c r="G17" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -8526,7 +8873,7 @@
         <v>9.4883645023316546E-2</v>
       </c>
       <c r="G18" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -8535,80 +8882,80 @@
         <v>2.7808805692648461E-5</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F21">
         <v>36000000</v>
       </c>
       <c r="G21" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F22" s="20">
         <f>F21*0.14</f>
         <v>5040000.0000000009</v>
       </c>
       <c r="G22" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I22" s="15"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F23">
         <f>AVERAGE(5.1,7.8)</f>
         <v>6.4499999999999993</v>
       </c>
       <c r="G23" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="I23" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="F24">
         <v>8000</v>
       </c>
       <c r="G24" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F25">
         <v>600</v>
       </c>
       <c r="G25" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -8617,7 +8964,7 @@
         <v>3869.9999999999995</v>
       </c>
       <c r="G26" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="I26" s="15"/>
     </row>
@@ -8627,95 +8974,95 @@
         <v>1289999.9999999998</v>
       </c>
       <c r="G27" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="I27" s="15"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="F28">
         <f>F27*277.778</f>
         <v>358333619.99999994</v>
       </c>
       <c r="G28" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I28" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="F29">
         <f>F28*0.003412</f>
         <v>1222634.3114399998</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F30" s="12">
         <f>(F21*0.14)/(F29*10^6)</f>
         <v>4.1222464909102436E-6</v>
       </c>
       <c r="G30" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I30" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F34">
         <v>21.08</v>
       </c>
       <c r="G34" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="I34" s="15" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="F35">
         <v>0.76</v>
       </c>
       <c r="G35" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I35" s="15" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F36" s="34">
         <f>F34*F35</f>
         <v>16.020799999999998</v>
       </c>
       <c r="G36" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -8723,7 +9070,7 @@
         <v>1.3284</v>
       </c>
       <c r="G37" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -8732,7 +9079,7 @@
         <v>21.282030719999998</v>
       </c>
       <c r="G38" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -8740,7 +9087,7 @@
         <v>1.32</v>
       </c>
       <c r="G39" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -8749,7 +9096,7 @@
         <v>28.092280550399998</v>
       </c>
       <c r="G40" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -8758,7 +9105,7 @@
         <v>4.3553923333953488</v>
       </c>
       <c r="G41" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -8766,7 +9113,7 @@
         <v>277.77800000000002</v>
       </c>
       <c r="G42" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -8775,7 +9122,7 @@
         <v>1.5679399856703368E-2</v>
       </c>
       <c r="G43" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -8783,7 +9130,7 @@
         <v>3412.14</v>
       </c>
       <c r="G44" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -8792,12 +9139,12 @@
         <v>4.5951806950193628E-6</v>
       </c>
       <c r="G45" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="18"/>
@@ -8808,99 +9155,99 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F49" s="32">
         <v>6000000</v>
       </c>
       <c r="G49" s="33" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F50">
         <v>300</v>
       </c>
       <c r="G50" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F51">
         <v>8760</v>
       </c>
       <c r="G51" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I51" s="15" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F52">
         <v>1100</v>
       </c>
       <c r="G52" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I52" s="15" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="F54">
         <f>(F3*365)*F52</f>
         <v>106060240.00000001</v>
       </c>
       <c r="G54" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="F55" s="34">
         <f>F54*0.003412</f>
         <v>361877.53888000007</v>
       </c>
       <c r="G55" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F56" s="12">
         <f>(F49*1.25)/(F55*10^6)</f>
         <v>2.0725243194734525E-5</v>
       </c>
       <c r="G56" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
@@ -8911,90 +9258,90 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F60">
         <f>574-184</f>
         <v>390</v>
       </c>
       <c r="G60" s="33" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F61">
         <v>3500</v>
       </c>
       <c r="G61" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F62" s="32">
         <v>1500000</v>
       </c>
       <c r="G62" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="I62" s="15" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="F64">
         <f>F61*F62</f>
         <v>5250000000</v>
       </c>
       <c r="G64" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="F65">
         <f>F64*0.003412</f>
         <v>17913000</v>
       </c>
       <c r="G65" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F66" s="25">
         <f>F60*F62</f>
         <v>585000000</v>
       </c>
       <c r="G66" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F67" s="12">
         <f>F66/(F65*10^6)</f>
         <v>3.265784625690839E-5</v>
       </c>
       <c r="G67" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -9034,67 +9381,67 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H8" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="I8" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>121</v>
-      </c>
       <c r="J8" s="30" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K8" s="27"/>
       <c r="L8" s="29" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="M8" s="27"/>
       <c r="N8" s="28" t="s">
@@ -9102,28 +9449,28 @@
       </c>
       <c r="O8" s="27"/>
       <c r="P8" s="29" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="Q8" s="27"/>
       <c r="R8" s="29" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="S8" s="27"/>
       <c r="T8" s="29" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="U8" s="27"/>
       <c r="V8" s="27"/>
       <c r="W8" s="29" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D9">
         <v>0.3</v>
@@ -9173,10 +9520,10 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -9226,10 +9573,10 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D11">
         <v>350</v>
@@ -9279,10 +9626,10 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D12">
         <v>500</v>
@@ -9332,10 +9679,10 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D13">
         <v>0.35</v>
@@ -9385,10 +9732,10 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D14">
         <v>1.8</v>
@@ -9438,10 +9785,10 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D15">
         <v>0.35</v>
@@ -9491,10 +9838,10 @@
     </row>
     <row r="16" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -9544,10 +9891,10 @@
     </row>
     <row r="17" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D17">
         <v>50</v>
@@ -9597,10 +9944,10 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -9650,10 +9997,10 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C19" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D19">
         <v>180</v>
@@ -9706,7 +10053,7 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="N21" s="21"/>
       <c r="P21" s="21"/>
@@ -9722,7 +10069,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="N22" s="21"/>
       <c r="P22" s="21"/>
@@ -9740,49 +10087,49 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C23" s="49" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="49" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="G23" s="49"/>
       <c r="H23" s="49"/>
       <c r="I23" s="49" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="J23" s="49"/>
       <c r="K23" s="49"/>
       <c r="L23" s="49"/>
       <c r="M23" s="49"/>
       <c r="N23" s="50" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
       <c r="T23" s="21"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C24" s="68" t="s">
-        <v>364</v>
-      </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="65">
+      <c r="C24" s="75" t="s">
+        <v>355</v>
+      </c>
+      <c r="D24" s="76"/>
+      <c r="E24" s="77"/>
+      <c r="F24" s="78">
         <f>0.048/0.581</f>
         <v>8.2616179001721177E-2</v>
       </c>
-      <c r="G24" s="66"/>
-      <c r="H24" s="67"/>
-      <c r="I24" s="71">
+      <c r="G24" s="79"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="72">
         <f>((T13+T15)/2)</f>
         <v>23.414850000000001</v>
       </c>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="73"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="74"/>
       <c r="N24" s="51">
         <f>((W13+W15)/2)</f>
         <v>2.2407199119595664E-4</v>
@@ -9792,25 +10139,25 @@
       <c r="T24" s="21"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C25" s="68" t="s">
-        <v>365</v>
-      </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="65">
+      <c r="C25" s="75" t="s">
+        <v>356</v>
+      </c>
+      <c r="D25" s="76"/>
+      <c r="E25" s="77"/>
+      <c r="F25" s="78">
         <f>0.104/0.581</f>
         <v>0.17900172117039587</v>
       </c>
-      <c r="G25" s="66"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="71">
+      <c r="G25" s="79"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="72">
         <f>T14</f>
         <v>97.18877280000001</v>
       </c>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="73"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="74"/>
       <c r="N25" s="51">
         <f>W14</f>
         <v>3.3521233224690123E-5</v>
@@ -9820,25 +10167,25 @@
       <c r="T25" s="21"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C26" s="68" t="s">
-        <v>363</v>
-      </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="65">
+      <c r="C26" s="75" t="s">
+        <v>354</v>
+      </c>
+      <c r="D26" s="76"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="78">
         <f>0.127/0.581</f>
         <v>0.21858864027538727</v>
       </c>
-      <c r="G26" s="66"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="71">
+      <c r="G26" s="79"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="72">
         <f>T16</f>
         <v>319.17554000000001</v>
       </c>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="73"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="74"/>
       <c r="N26" s="51">
         <f>W16</f>
         <v>1.1301491868138288E-5</v>
@@ -9848,25 +10195,25 @@
       <c r="T26" s="21"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C27" s="68" t="s">
-        <v>362</v>
-      </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="65">
+      <c r="C27" s="75" t="s">
+        <v>353</v>
+      </c>
+      <c r="D27" s="76"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="78">
         <f>0.144/0.581</f>
         <v>0.24784853700516352</v>
       </c>
-      <c r="G27" s="66"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="71">
+      <c r="G27" s="79"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="72">
         <f>((T10+T18)/2)</f>
         <v>1214.1039020000001</v>
       </c>
-      <c r="J27" s="72"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="72"/>
-      <c r="M27" s="73"/>
+      <c r="J27" s="73"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="73"/>
+      <c r="M27" s="74"/>
       <c r="N27" s="51">
         <f>((W10+W18)/2)</f>
         <v>5.481183696812177E-6</v>
@@ -9876,25 +10223,25 @@
       <c r="T27" s="21"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="C28" s="68" t="s">
-        <v>366</v>
-      </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="65">
+      <c r="C28" s="75" t="s">
+        <v>357</v>
+      </c>
+      <c r="D28" s="76"/>
+      <c r="E28" s="77"/>
+      <c r="F28" s="78">
         <f>0.157/0.581</f>
         <v>0.27022375215146299</v>
       </c>
-      <c r="G28" s="66"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="71">
+      <c r="G28" s="79"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="72">
         <f>((T9+T11+T12+T17+T19)/5)</f>
         <v>49678.416604960003</v>
       </c>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="73"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="73"/>
+      <c r="M28" s="74"/>
       <c r="N28" s="51">
         <f>((W9+W11+W12+W17+W19)/5)</f>
         <v>4.8514850079979492E-6</v>
@@ -9913,116 +10260,116 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="G32" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="U32" s="9"/>
       <c r="W32" s="9"/>
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D33" s="21">
         <v>502</v>
       </c>
       <c r="E33" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="T33" s="9"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D34" s="21">
         <v>250</v>
       </c>
       <c r="E34" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="T34" s="9"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D35" s="21">
         <f>D34/1.341</f>
         <v>186.42803877703207</v>
       </c>
       <c r="E35" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D36" s="21">
         <v>2080</v>
       </c>
       <c r="E36" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="D37" s="21">
         <f>D35*0.003412*D36</f>
         <v>1323.0723340790455</v>
       </c>
       <c r="E37" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D38" s="12">
         <f>(D33*D35)/(D37*10^6)</f>
         <v>7.0734511678239686E-5</v>
       </c>
       <c r="E38" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
     <mergeCell ref="I24:M24"/>
     <mergeCell ref="I25:M25"/>
     <mergeCell ref="I26:M26"/>
     <mergeCell ref="I27:M27"/>
     <mergeCell ref="I28:M28"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G33" r:id="rId1" xr:uid="{89D540DE-65F8-419E-8E02-FD08F0D4350B}"/>
@@ -10045,7 +10392,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -10056,12 +10403,12 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -10069,94 +10416,94 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="G5" s="1"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D6">
         <f>AVERAGE(760,1000)</f>
         <v>880</v>
       </c>
       <c r="E6" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D7">
         <f>AVERAGE(373.1,597)</f>
         <v>485.05</v>
       </c>
       <c r="E7" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D11">
         <f>AVERAGE(975,1200)</f>
         <v>1087.5</v>
       </c>
       <c r="E11" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D12">
         <f>AVERAGE(1492.5,2238.8)</f>
         <v>1865.65</v>
       </c>
       <c r="E12" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D15">
         <v>1.5</v>
       </c>
       <c r="E15" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D16">
         <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G18">
         <f>(D6)*(1.5*1000000)</f>
@@ -10165,7 +10512,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="G19">
         <f>(1.5*1000000)*(0.7*8760)</f>
@@ -10174,7 +10521,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="G20">
         <f>G19*3412</f>
@@ -10183,7 +10530,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G21">
         <f>G18/G20</f>
@@ -10192,7 +10539,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G22">
         <f>(D7*(1.5*1000000))/G20</f>
@@ -10201,7 +10548,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G24">
         <f>(D11)*(1.5*1000000)</f>
@@ -10210,7 +10557,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="G25">
         <f>(1.5*1000000)*(0.7*8760)</f>
@@ -10219,7 +10566,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="G26">
         <f>G25*3412</f>
@@ -10228,7 +10575,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G27">
         <f>G24/G26</f>
@@ -10237,7 +10584,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G28">
         <f>(D12*(1.5*1000000))/G26</f>
@@ -10246,12 +10593,12 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G32" s="12">
         <f>(G21*0.75)+(G27*0.25)</f>
@@ -10260,7 +10607,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G33" s="9">
         <f>G32*0.6</f>
@@ -10272,7 +10619,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="G35" s="9">
         <f>(G22*0.75)+(G28*0.25)</f>
@@ -10298,183 +10645,183 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="P1" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="D3" t="s">
+        <v>460</v>
+      </c>
+      <c r="E3" t="s">
+        <v>460</v>
+      </c>
+      <c r="F3" t="s">
+        <v>460</v>
+      </c>
+      <c r="G3" t="s">
+        <v>460</v>
+      </c>
+      <c r="H3" t="s">
+        <v>460</v>
+      </c>
+      <c r="I3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J3" t="s">
+        <v>460</v>
+      </c>
+      <c r="K3" t="s">
+        <v>461</v>
+      </c>
+      <c r="L3" t="s">
+        <v>461</v>
+      </c>
+      <c r="M3" t="s">
+        <v>461</v>
+      </c>
+      <c r="N3" t="s">
+        <v>465</v>
+      </c>
+      <c r="O3" t="s">
+        <v>465</v>
+      </c>
+      <c r="P3" t="s">
         <v>473</v>
       </c>
-      <c r="E3" t="s">
+      <c r="Q3" t="s">
         <v>473</v>
       </c>
-      <c r="F3" t="s">
+      <c r="R3" t="s">
         <v>473</v>
       </c>
-      <c r="G3" t="s">
+      <c r="S3" t="s">
         <v>473</v>
       </c>
-      <c r="H3" t="s">
+      <c r="T3" t="s">
         <v>473</v>
-      </c>
-      <c r="I3" t="s">
-        <v>473</v>
-      </c>
-      <c r="J3" t="s">
-        <v>473</v>
-      </c>
-      <c r="K3" t="s">
-        <v>474</v>
-      </c>
-      <c r="L3" t="s">
-        <v>474</v>
-      </c>
-      <c r="M3" t="s">
-        <v>474</v>
-      </c>
-      <c r="N3" t="s">
-        <v>478</v>
-      </c>
-      <c r="O3" t="s">
-        <v>478</v>
-      </c>
-      <c r="P3" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>486</v>
-      </c>
-      <c r="R3" t="s">
-        <v>486</v>
-      </c>
-      <c r="S3" t="s">
-        <v>486</v>
-      </c>
-      <c r="T3" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="D4" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="E4" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="F4" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="G4" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="H4" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="I4" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="J4" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="K4" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="L4" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="M4" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="N4" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="O4" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="P4" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="Q4" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="R4" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="S4" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="T4" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="D5" t="s">
+        <v>445</v>
+      </c>
+      <c r="E5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5" t="s">
+        <v>447</v>
+      </c>
+      <c r="G5" t="s">
+        <v>448</v>
+      </c>
+      <c r="H5" t="s">
+        <v>449</v>
+      </c>
+      <c r="I5" t="s">
+        <v>451</v>
+      </c>
+      <c r="J5" t="s">
+        <v>456</v>
+      </c>
+      <c r="K5" t="s">
         <v>458</v>
       </c>
-      <c r="E5" t="s">
-        <v>459</v>
-      </c>
-      <c r="F5" t="s">
-        <v>460</v>
-      </c>
-      <c r="G5" t="s">
-        <v>461</v>
-      </c>
-      <c r="H5" t="s">
-        <v>462</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
+        <v>463</v>
+      </c>
+      <c r="M5" t="s">
         <v>464</v>
       </c>
-      <c r="J5" t="s">
-        <v>469</v>
-      </c>
-      <c r="K5" t="s">
-        <v>471</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
+        <v>466</v>
+      </c>
+      <c r="O5" t="s">
+        <v>466</v>
+      </c>
+      <c r="P5" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>475</v>
+      </c>
+      <c r="R5" t="s">
         <v>476</v>
       </c>
-      <c r="M5" t="s">
-        <v>477</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="S5" t="s">
+        <v>478</v>
+      </c>
+      <c r="T5" t="s">
         <v>479</v>
       </c>
-      <c r="O5" t="s">
-        <v>479</v>
-      </c>
-      <c r="P5" t="s">
-        <v>487</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>488</v>
-      </c>
-      <c r="R5" t="s">
-        <v>489</v>
-      </c>
-      <c r="S5" t="s">
-        <v>491</v>
-      </c>
-      <c r="T5" t="s">
-        <v>492</v>
-      </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B6" s="74" t="s">
-        <v>65</v>
+      <c r="B6" s="65" t="s">
+        <v>59</v>
       </c>
       <c r="C6">
         <v>1.3</v>
@@ -10539,12 +10886,12 @@
         <v>12</v>
       </c>
       <c r="W6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
-        <v>455</v>
+      <c r="B7" s="65" t="s">
+        <v>442</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -10602,8 +10949,8 @@
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B8" s="74" t="s">
-        <v>456</v>
+      <c r="B8" s="65" t="s">
+        <v>443</v>
       </c>
       <c r="C8">
         <v>225</v>
@@ -10652,8 +10999,8 @@
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B9" s="74" t="s">
-        <v>457</v>
+      <c r="B9" s="65" t="s">
+        <v>444</v>
       </c>
       <c r="C9">
         <v>2500</v>
@@ -10708,8 +11055,8 @@
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B10" s="74" t="s">
-        <v>463</v>
+      <c r="B10" s="65" t="s">
+        <v>450</v>
       </c>
       <c r="D10">
         <v>50</v>
@@ -10730,7 +11077,7 @@
         <v>59</v>
       </c>
       <c r="J10" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -10815,29 +11162,29 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="E14" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="F14" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="H14" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B15" s="74" t="s">
-        <v>472</v>
+      <c r="B15" s="65" t="s">
+        <v>459</v>
       </c>
       <c r="C15" s="34">
         <f>AVERAGEIFS($C$6:$T$6,$C$3:$T$3,$B15)</f>
@@ -10857,7 +11204,7 @@
       </c>
       <c r="G15" s="21"/>
       <c r="H15" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="I15" s="43">
         <v>0.65200000000000002</v>
@@ -10880,8 +11227,8 @@
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B16" s="74" t="s">
-        <v>473</v>
+      <c r="B16" s="65" t="s">
+        <v>460</v>
       </c>
       <c r="C16" s="34">
         <f t="shared" ref="C16:C19" si="1">AVERAGEIFS($C$6:$T$6,$C$3:$T$3,$B16)</f>
@@ -10901,7 +11248,7 @@
       </c>
       <c r="G16" s="21"/>
       <c r="H16" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="I16" s="43">
         <v>0.13650000000000001</v>
@@ -10923,12 +11270,12 @@
         <v>4.5045000000000002</v>
       </c>
       <c r="O16" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B17" s="74" t="s">
-        <v>474</v>
+      <c r="B17" s="65" t="s">
+        <v>461</v>
       </c>
       <c r="C17" s="34">
         <f t="shared" si="1"/>
@@ -10948,7 +11295,7 @@
       </c>
       <c r="G17" s="21"/>
       <c r="H17" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="I17" s="43">
         <v>0.20050000000000001</v>
@@ -10973,12 +11320,12 @@
         <v>9</v>
       </c>
       <c r="P17" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B18" s="74" t="s">
-        <v>478</v>
+      <c r="B18" s="65" t="s">
+        <v>465</v>
       </c>
       <c r="C18" s="34">
         <f t="shared" si="1"/>
@@ -10998,7 +11345,7 @@
       </c>
       <c r="G18" s="21"/>
       <c r="H18" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="I18" s="43">
         <v>1.0999999999999999E-2</v>
@@ -11021,8 +11368,8 @@
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B19" s="74" t="s">
-        <v>486</v>
+      <c r="B19" s="65" t="s">
+        <v>473</v>
       </c>
       <c r="C19" s="34">
         <f t="shared" si="1"/>
@@ -11049,7 +11396,7 @@
         <f>SUM(K15:K18)</f>
         <v>992924.91514040111</v>
       </c>
-      <c r="L19" s="75">
+      <c r="L19" s="66">
         <f>SUM(L15:L18)</f>
         <v>10.466121541666666</v>
       </c>
@@ -11062,21 +11409,21 @@
         <v>2766.4523809523807</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="J20" s="1" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="L20" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.25">
@@ -11084,26 +11431,26 @@
         <v>3412</v>
       </c>
       <c r="P21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="O23" s="76">
+      <c r="O23" s="67">
         <f>L19/K19</f>
         <v>1.0540697873601793E-5</v>
       </c>
       <c r="P23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
@@ -11112,7 +11459,7 @@
         <v>0.35</v>
       </c>
       <c r="C27" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
@@ -11121,40 +11468,40 @@
         <v>3.6892442557606274E-6</v>
       </c>
       <c r="C28" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="C32" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="D32" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="E32" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="F32" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="G32" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="H32" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B33">
         <v>3579</v>
@@ -11182,12 +11529,12 @@
         <v>1242.9985714285715</v>
       </c>
       <c r="J33" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="B34">
         <v>10000</v>
@@ -11216,7 +11563,7 @@
         <v>8557.1428571428569</v>
       </c>
       <c r="J34" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -11255,10 +11602,10 @@
         <v>15.280094283412833</v>
       </c>
       <c r="J37" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="K37" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -11267,16 +11614,16 @@
         <v>5.3861403995872857E-6</v>
       </c>
       <c r="K38" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I39" s="76">
+      <c r="I39" s="67">
         <f>I38+B28</f>
         <v>9.0753846553479132E-6</v>
       </c>
       <c r="K39" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -11297,7 +11644,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -11309,184 +11656,184 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E3" s="39">
         <f>2758*1.03</f>
         <v>2840.7400000000002</v>
       </c>
       <c r="F3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="H3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E4">
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E5">
         <f>18*365</f>
         <v>6570</v>
       </c>
       <c r="F5" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H5" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="E7">
         <f>E4*E5</f>
         <v>118260</v>
       </c>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="E8">
         <f>E7*0.003412</f>
         <v>403.50312000000002</v>
       </c>
       <c r="F8" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E9" s="12">
         <f>E3/(E8*10^6)</f>
         <v>7.0401933942914745E-6</v>
       </c>
       <c r="F9" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B16" s="8">
         <v>862500</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B17" s="8">
         <v>1500000</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B18" s="8">
         <f>AVERAGE(B16,B17)</f>
         <v>1181250</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B20" s="32">
         <v>8760</v>
       </c>
       <c r="C20" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B21" s="32">
         <v>6051100</v>
       </c>
       <c r="C21" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B23">
         <f>B20*B21</f>
         <v>53007636000</v>
       </c>
       <c r="C23" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B24" s="12">
         <f>B18/B23</f>
         <v>2.2284525195577483E-5</v>
       </c>
       <c r="C24" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
